--- a/input/reg_retirement.xlsx
+++ b/input/reg_retirement.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="57">
   <si>
     <t>Description:</t>
   </si>
@@ -141,7 +141,7 @@
     <t>demRgnUKN</t>
   </si>
   <si>
-    <t>demYear</t>
+    <t>demYearTransformed</t>
   </si>
   <si>
     <t>demYear2020</t>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>demPensAgeFlag_NotEmployedL1</t>
+  </si>
+  <si>
+    <t>labStatusPartnerC3NotEmployedL1</t>
   </si>
   <si>
     <t>demPensPartnerAgeFlag</t>
@@ -452,13 +455,13 @@
         <v>49</v>
       </c>
       <c r="B4">
-        <v>0.22360293032095857</v>
+        <v>0.22250921804627743</v>
       </c>
       <c r="E4" t="s">
         <v>51</v>
       </c>
       <c r="F4">
-        <v>1642.3904182861502</v>
+        <v>1642.7081619963692</v>
       </c>
     </row>
     <row r="5">
@@ -466,18 +469,18 @@
         <v>50</v>
       </c>
       <c r="B5">
-        <v>26049</v>
+        <v>26159</v>
       </c>
       <c r="E5" t="s">
         <v>52</v>
       </c>
       <c r="F5">
-        <v>-3444311.4487916338</v>
+        <v>-3449306.3533617309</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -485,13 +488,13 @@
         <v>49</v>
       </c>
       <c r="B8">
-        <v>0.19287232505327556</v>
+        <v>0.19955270749928211</v>
       </c>
       <c r="E8" t="s">
         <v>51</v>
       </c>
       <c r="F8">
-        <v>2919.9245903985934</v>
+        <v>3031.9477253780969</v>
       </c>
     </row>
     <row r="9">
@@ -499,13 +502,13 @@
         <v>50</v>
       </c>
       <c r="B9">
-        <v>60682</v>
+        <v>60543</v>
       </c>
       <c r="E9" t="s">
         <v>52</v>
       </c>
       <c r="F9">
-        <v>-9240935.1954658255</v>
+        <v>-9142194.1513341088</v>
       </c>
     </row>
   </sheetData>
@@ -626,103 +629,103 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>0.099434588094419477</v>
+        <v>0.10737056546630433</v>
       </c>
       <c r="C2">
-        <v>0.0016629497963847476</v>
+        <v>0.0016857460054973059</v>
       </c>
       <c r="D2">
-        <v>-9.6895402767480934e-005</v>
+        <v>-0.00012153515528117795</v>
       </c>
       <c r="E2">
-        <v>6.4249078647221115e-007</v>
+        <v>8.2154031494949387e-007</v>
       </c>
       <c r="F2">
-        <v>-0.00043165231900619151</v>
+        <v>-0.00040469963868103613</v>
       </c>
       <c r="G2">
-        <v>-0.0005166722221013624</v>
+        <v>-0.000554382860836604</v>
       </c>
       <c r="H2">
-        <v>9.0127911432751333e-006</v>
+        <v>8.4260365890866294e-006</v>
       </c>
       <c r="I2">
-        <v>-2.6616265918286003e-006</v>
+        <v>-4.4386836146786797e-006</v>
       </c>
       <c r="J2">
-        <v>0.00046113977968170825</v>
+        <v>0.00047725993084746373</v>
       </c>
       <c r="K2">
-        <v>-0.00038161684614405552</v>
+        <v>-0.00044952064074734355</v>
       </c>
       <c r="L2">
-        <v>0.00025693072709294889</v>
+        <v>0.00016805615926366674</v>
       </c>
       <c r="M2">
-        <v>1.1194587586794286e-006</v>
+        <v>-8.3083020343160388e-005</v>
       </c>
       <c r="N2">
-        <v>-0.00017151022915099521</v>
+        <v>-0.00024956895152148761</v>
       </c>
       <c r="O2">
-        <v>-0.0011780319955238283</v>
+        <v>-0.0012617963506765587</v>
       </c>
       <c r="P2">
-        <v>0.00039186888805799094</v>
+        <v>0.0004119258562408155</v>
       </c>
       <c r="Q2">
-        <v>-0.0012482389807207369</v>
+        <v>-0.0012400506007801957</v>
       </c>
       <c r="R2">
-        <v>-0.001798117669387117</v>
+        <v>-0.001752979235595681</v>
       </c>
       <c r="S2">
-        <v>-0.0011046076567213512</v>
+        <v>-0.0011044162876284705</v>
       </c>
       <c r="T2">
-        <v>-0.0014137203807011096</v>
+        <v>-0.0013855037154989363</v>
       </c>
       <c r="U2">
-        <v>-0.00090248496756083142</v>
+        <v>-0.0009235843618826305</v>
       </c>
       <c r="V2">
-        <v>-0.0010485859972540238</v>
+        <v>-0.0010197156011623847</v>
       </c>
       <c r="W2">
-        <v>-0.0011651105472551329</v>
+        <v>-0.0011201294848247753</v>
       </c>
       <c r="X2">
-        <v>-0.0012504886266040162</v>
+        <v>-0.0012167530673551398</v>
       </c>
       <c r="Y2">
-        <v>-0.0012029536687807746</v>
+        <v>-0.0011614333715447708</v>
       </c>
       <c r="Z2">
-        <v>-0.0012696358973717128</v>
+        <v>-0.0012249991792923562</v>
       </c>
       <c r="AA2">
-        <v>-0.0013049396121498627</v>
+        <v>-0.00076383403049597003</v>
       </c>
       <c r="AB2">
-        <v>-1.0837861626690709e-005</v>
+        <v>-4.8573611273204685e-006</v>
       </c>
       <c r="AC2">
-        <v>0.00020769286537899762</v>
+        <v>0.00016564790831333394</v>
       </c>
       <c r="AD2">
-        <v>0.00028285768138087476</v>
+        <v>0.00020477687701145266</v>
       </c>
       <c r="AE2">
-        <v>-0.00023457975492527968</v>
+        <v>-0.00020770196617954243</v>
       </c>
       <c r="AF2">
-        <v>-0.0043188796947387226</v>
+        <v>-0.0042528204499786039</v>
       </c>
       <c r="AG2">
-        <v>-0.00046669018835589996</v>
+        <v>-0.00047613401370413984</v>
       </c>
       <c r="AH2">
-        <v>0.0043810667284545184</v>
+        <v>0.0052508962944459517</v>
       </c>
     </row>
     <row r="3">
@@ -730,103 +733,103 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>0.52640160153851789</v>
+        <v>0.52454491039570772</v>
       </c>
       <c r="C3">
-        <v>-9.6895402767480934e-005</v>
+        <v>-0.00012153515528117795</v>
       </c>
       <c r="D3">
-        <v>0.0018074662691370518</v>
+        <v>0.0018044389694833371</v>
       </c>
       <c r="E3">
-        <v>-1.4110168855055266e-005</v>
+        <v>-1.4071896125540558e-005</v>
       </c>
       <c r="F3">
-        <v>-8.6253147339246383e-006</v>
+        <v>-1.7717214786619473e-005</v>
       </c>
       <c r="G3">
-        <v>-6.2013399504901034e-005</v>
+        <v>-3.5713878286720846e-005</v>
       </c>
       <c r="H3">
-        <v>9.6848060760358189e-007</v>
+        <v>5.671585134038289e-007</v>
       </c>
       <c r="I3">
-        <v>6.192343336845253e-007</v>
+        <v>1.8990723777065333e-006</v>
       </c>
       <c r="J3">
-        <v>-0.00016935528366010186</v>
+        <v>-0.00019329990415892576</v>
       </c>
       <c r="K3">
-        <v>0.00087707850052367101</v>
+        <v>0.00089292078514432299</v>
       </c>
       <c r="L3">
-        <v>0.00022464660251491665</v>
+        <v>0.00027499527210212999</v>
       </c>
       <c r="M3">
-        <v>0.00035905792485447716</v>
+        <v>0.00040311869606346473</v>
       </c>
       <c r="N3">
-        <v>0.00038156023466717759</v>
+        <v>0.00042373908339480085</v>
       </c>
       <c r="O3">
-        <v>0.00048707247315912805</v>
+        <v>0.00054067845796331587</v>
       </c>
       <c r="P3">
-        <v>-0.00037931576460976252</v>
+        <v>-0.00037847685750770632</v>
       </c>
       <c r="Q3">
-        <v>0.00020278560873141643</v>
+        <v>0.00019799251474569152</v>
       </c>
       <c r="R3">
-        <v>0.00020182335764576398</v>
+        <v>0.00020179938610083437</v>
       </c>
       <c r="S3">
-        <v>6.9546401326808782e-005</v>
+        <v>5.3164751290087076e-005</v>
       </c>
       <c r="T3">
-        <v>8.1373291788984503e-005</v>
+        <v>7.9164708423541674e-005</v>
       </c>
       <c r="U3">
-        <v>0.00013802259772046147</v>
+        <v>0.00017724003109485797</v>
       </c>
       <c r="V3">
-        <v>0.00012918642618203746</v>
+        <v>0.00012868067162564306</v>
       </c>
       <c r="W3">
-        <v>0.00024540354067589115</v>
+        <v>0.00023916827055788653</v>
       </c>
       <c r="X3">
-        <v>0.00019990819128574977</v>
+        <v>0.00018580140151630564</v>
       </c>
       <c r="Y3">
-        <v>0.0002419916374485423</v>
+        <v>0.00022742005357321432</v>
       </c>
       <c r="Z3">
-        <v>0.0002018661999080365</v>
+        <v>0.00019214793354959542</v>
       </c>
       <c r="AA3">
-        <v>0.0002354384379023057</v>
+        <v>0.00010339785869942913</v>
       </c>
       <c r="AB3">
-        <v>-6.3558936205868055e-006</v>
+        <v>-7.6627498660202659e-006</v>
       </c>
       <c r="AC3">
-        <v>-4.0861739681288117e-005</v>
+        <v>-6.2915257272328634e-005</v>
       </c>
       <c r="AD3">
-        <v>7.7681341943691695e-007</v>
+        <v>-8.3291934343046603e-006</v>
       </c>
       <c r="AE3">
-        <v>-0.00019995005730219159</v>
+        <v>-0.00022987420629791422</v>
       </c>
       <c r="AF3">
-        <v>8.3309638002571074e-005</v>
+        <v>8.9560178830605519e-005</v>
       </c>
       <c r="AG3">
-        <v>-3.7550285830118923e-005</v>
+        <v>-3.2768084042065945e-005</v>
       </c>
       <c r="AH3">
-        <v>-0.05782008561684393</v>
+        <v>-0.057821831566868792</v>
       </c>
     </row>
     <row r="4">
@@ -834,103 +837,103 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>-0.0036952242809840472</v>
+        <v>-0.0036750678807111335</v>
       </c>
       <c r="C4">
-        <v>6.4249078647221115e-007</v>
+        <v>8.2154031494949387e-007</v>
       </c>
       <c r="D4">
-        <v>-1.4110168855055266e-005</v>
+        <v>-1.4071896125540558e-005</v>
       </c>
       <c r="E4">
-        <v>1.1148024672744636e-007</v>
+        <v>1.1106873763433133e-007</v>
       </c>
       <c r="F4">
-        <v>-1.0682960655986973e-008</v>
+        <v>4.6151066510557396e-008</v>
       </c>
       <c r="G4">
-        <v>2.3522409323562671e-007</v>
+        <v>4.484265427376604e-008</v>
       </c>
       <c r="H4">
-        <v>-2.7371813060983062e-009</v>
+        <v>2.6807243763485447e-010</v>
       </c>
       <c r="I4">
-        <v>-1.2069981822217435e-008</v>
+        <v>-2.0981996045777586e-008</v>
       </c>
       <c r="J4">
-        <v>-2.3105015469423204e-007</v>
+        <v>-5.4191886436613982e-008</v>
       </c>
       <c r="K4">
-        <v>-7.5915009952358728e-006</v>
+        <v>-7.6806941235559771e-006</v>
       </c>
       <c r="L4">
-        <v>-2.2060743086697103e-006</v>
+        <v>-2.5428085678137749e-006</v>
       </c>
       <c r="M4">
-        <v>-3.3038463342143453e-006</v>
+        <v>-3.6054997783705205e-006</v>
       </c>
       <c r="N4">
-        <v>-3.3716399276370092e-006</v>
+        <v>-3.6614599165258883e-006</v>
       </c>
       <c r="O4">
-        <v>-4.328734355233798e-006</v>
+        <v>-4.6943075489085334e-006</v>
       </c>
       <c r="P4">
-        <v>3.6110292346240428e-006</v>
+        <v>3.5999995982966774e-006</v>
       </c>
       <c r="Q4">
-        <v>-1.518344352639334e-006</v>
+        <v>-1.4852569616151975e-006</v>
       </c>
       <c r="R4">
-        <v>-1.8756847454518867e-006</v>
+        <v>-1.8791101348170514e-006</v>
       </c>
       <c r="S4">
-        <v>-6.6729025364022695e-007</v>
+        <v>-5.5109245810546414e-007</v>
       </c>
       <c r="T4">
-        <v>-6.5716702936661955e-007</v>
+        <v>-6.4763107066723559e-007</v>
       </c>
       <c r="U4">
-        <v>-1.1848409301943696e-006</v>
+        <v>-1.4451342233057392e-006</v>
       </c>
       <c r="V4">
-        <v>-1.0858822021280888e-006</v>
+        <v>-1.0873565336841796e-006</v>
       </c>
       <c r="W4">
-        <v>-1.8458183713621523e-006</v>
+        <v>-1.8055250574175344e-006</v>
       </c>
       <c r="X4">
-        <v>-1.6632847674714316e-006</v>
+        <v>-1.5645936441537598e-006</v>
       </c>
       <c r="Y4">
-        <v>-2.3368852439077182e-006</v>
+        <v>-2.2392598663084477e-006</v>
       </c>
       <c r="Z4">
-        <v>-1.6745406098061188e-006</v>
+        <v>-1.6148000120130043e-006</v>
       </c>
       <c r="AA4">
-        <v>-2.0653474351856711e-006</v>
+        <v>-1.1530581094514351e-006</v>
       </c>
       <c r="AB4">
-        <v>-7.1470426814859407e-009</v>
+        <v>3.2748816361093287e-009</v>
       </c>
       <c r="AC4">
-        <v>4.1900366571780514e-007</v>
+        <v>5.9240493379726514e-007</v>
       </c>
       <c r="AD4">
-        <v>-4.8021962463094987e-008</v>
+        <v>2.3104758815428814e-008</v>
       </c>
       <c r="AE4">
-        <v>1.8416255608731604e-006</v>
+        <v>2.0589366338626049e-006</v>
       </c>
       <c r="AF4">
-        <v>-1.5878217143900503e-006</v>
+        <v>-1.616362332871029e-006</v>
       </c>
       <c r="AG4">
-        <v>2.0702006994601949e-007</v>
+        <v>1.6358384404463319e-007</v>
       </c>
       <c r="AH4">
-        <v>0.0004486540895328444</v>
+        <v>0.0004481165238095768</v>
       </c>
     </row>
     <row r="5">
@@ -938,103 +941,103 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>-0.04896915781487008</v>
+        <v>-0.056978641891232473</v>
       </c>
       <c r="C5">
-        <v>-0.00043165231900619151</v>
+        <v>-0.00040469963868103613</v>
       </c>
       <c r="D5">
-        <v>-8.6253147339246383e-006</v>
+        <v>-1.7717214786619473e-005</v>
       </c>
       <c r="E5">
-        <v>-1.0682960655986973e-008</v>
+        <v>4.6151066510557396e-008</v>
       </c>
       <c r="F5">
-        <v>0.0028582426146525983</v>
+        <v>0.0028659181502856206</v>
       </c>
       <c r="G5">
-        <v>0.002302987327204198</v>
+        <v>0.0022682912610287303</v>
       </c>
       <c r="H5">
-        <v>-2.8609118928811698e-005</v>
+        <v>-2.8680903795445361e-005</v>
       </c>
       <c r="I5">
-        <v>-1.6000473221173835e-005</v>
+        <v>-1.6226729905685057e-005</v>
       </c>
       <c r="J5">
-        <v>0.00019684768490389382</v>
+        <v>0.00021226453854740392</v>
       </c>
       <c r="K5">
-        <v>0.00061883766474309532</v>
+        <v>0.00059022742568829519</v>
       </c>
       <c r="L5">
-        <v>-0.00028371327553128225</v>
+        <v>-0.00031295893523244076</v>
       </c>
       <c r="M5">
-        <v>0.00034395122624735375</v>
+        <v>0.0003352963146669699</v>
       </c>
       <c r="N5">
-        <v>0.0005897194008889292</v>
+        <v>0.00055659138931980626</v>
       </c>
       <c r="O5">
-        <v>0.0022548327163898845</v>
+        <v>0.0022267248504982684</v>
       </c>
       <c r="P5">
-        <v>-0.00086474991207307304</v>
+        <v>-0.00081718167609216223</v>
       </c>
       <c r="Q5">
-        <v>0.0012678231689615444</v>
+        <v>0.0012931939006853746</v>
       </c>
       <c r="R5">
-        <v>0.0027009654577510637</v>
+        <v>0.0027084558375285411</v>
       </c>
       <c r="S5">
-        <v>0.0017820943783218948</v>
+        <v>0.0017761513120647533</v>
       </c>
       <c r="T5">
-        <v>0.001449276149188898</v>
+        <v>0.0014529282599344687</v>
       </c>
       <c r="U5">
-        <v>0.0011820816616825002</v>
+        <v>0.0011663657908983381</v>
       </c>
       <c r="V5">
-        <v>0.0013068593400176074</v>
+        <v>0.001335661274960275</v>
       </c>
       <c r="W5">
-        <v>0.0016368364146086846</v>
+        <v>0.0016427530023333783</v>
       </c>
       <c r="X5">
-        <v>0.0016565600036729299</v>
+        <v>0.0016618138205497365</v>
       </c>
       <c r="Y5">
-        <v>0.0017337842293381077</v>
+        <v>0.0017502671913798978</v>
       </c>
       <c r="Z5">
-        <v>0.0015005973632072228</v>
+        <v>0.0014903046442211864</v>
       </c>
       <c r="AA5">
-        <v>0.0017652699745315682</v>
+        <v>0.0020919809217895286</v>
       </c>
       <c r="AB5">
-        <v>3.1309100577320867e-005</v>
+        <v>3.5848400819587806e-005</v>
       </c>
       <c r="AC5">
-        <v>-0.00013298564714476807</v>
+        <v>-0.00018710326232145697</v>
       </c>
       <c r="AD5">
-        <v>-9.0621451984107624e-005</v>
+        <v>-0.00011999236476008452</v>
       </c>
       <c r="AE5">
-        <v>0.00058694872452894596</v>
+        <v>0.00062365683926954925</v>
       </c>
       <c r="AF5">
-        <v>0.0075775285857005679</v>
+        <v>0.0076051332064854694</v>
       </c>
       <c r="AG5">
-        <v>0.00038629382029089918</v>
+        <v>0.00038684777698520909</v>
       </c>
       <c r="AH5">
-        <v>-0.0021060024442011351</v>
+        <v>-0.001819257928147436</v>
       </c>
     </row>
     <row r="6">
@@ -1042,103 +1045,103 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>-0.075174852032846906</v>
+        <v>-0.081493431594563098</v>
       </c>
       <c r="C6">
-        <v>-0.0005166722221013624</v>
+        <v>-0.000554382860836604</v>
       </c>
       <c r="D6">
-        <v>-6.2013399504901034e-005</v>
+        <v>-3.5713878286720846e-005</v>
       </c>
       <c r="E6">
-        <v>2.3522409323562671e-007</v>
+        <v>4.484265427376604e-008</v>
       </c>
       <c r="F6">
-        <v>0.002302987327204198</v>
+        <v>0.0022682912610287303</v>
       </c>
       <c r="G6">
-        <v>0.0036734311635296911</v>
+        <v>0.003688295125003304</v>
       </c>
       <c r="H6">
-        <v>-2.0333309727415136e-005</v>
+        <v>-1.9994871302973556e-005</v>
       </c>
       <c r="I6">
-        <v>-8.9742621527388928e-006</v>
+        <v>-7.2654009765892114e-006</v>
       </c>
       <c r="J6">
-        <v>0.00039481893604807267</v>
+        <v>0.00037334999079887684</v>
       </c>
       <c r="K6">
-        <v>0.00067276222119696443</v>
+        <v>0.00070777474133876511</v>
       </c>
       <c r="L6">
-        <v>-4.0870241315141379e-005</v>
+        <v>4.1664123801558428e-005</v>
       </c>
       <c r="M6">
-        <v>0.00069966620911873366</v>
+        <v>0.00078198695814193898</v>
       </c>
       <c r="N6">
-        <v>0.0010442452935745755</v>
+        <v>0.0011166743283140415</v>
       </c>
       <c r="O6">
-        <v>0.0026409873422621171</v>
+        <v>0.0027102445330310443</v>
       </c>
       <c r="P6">
-        <v>-0.0007308270268661576</v>
+        <v>-0.00072765040284540898</v>
       </c>
       <c r="Q6">
-        <v>0.0009789783747621403</v>
+        <v>0.00098886710158728485</v>
       </c>
       <c r="R6">
-        <v>0.0022101295935046234</v>
+        <v>0.0021788963811873209</v>
       </c>
       <c r="S6">
-        <v>0.0014905784533018381</v>
+        <v>0.0015132251795556386</v>
       </c>
       <c r="T6">
-        <v>0.0010197147105967526</v>
+        <v>0.0010013006414027656</v>
       </c>
       <c r="U6">
-        <v>0.00092552016326934053</v>
+        <v>0.00098877265442824441</v>
       </c>
       <c r="V6">
-        <v>0.0010845009162291275</v>
+        <v>0.0010799635905759455</v>
       </c>
       <c r="W6">
-        <v>0.0011853874084692369</v>
+        <v>0.0011602300072375798</v>
       </c>
       <c r="X6">
-        <v>0.0012776578192823657</v>
+        <v>0.0012500570311553977</v>
       </c>
       <c r="Y6">
-        <v>0.0011113993454440962</v>
+        <v>0.0010840893212601536</v>
       </c>
       <c r="Z6">
-        <v>0.0011640497673458096</v>
+        <v>0.0011387451358837071</v>
       </c>
       <c r="AA6">
-        <v>0.0010530299387262443</v>
+        <v>0.00062501823023430685</v>
       </c>
       <c r="AB6">
-        <v>5.694834711565558e-005</v>
+        <v>5.1210280682712145e-005</v>
       </c>
       <c r="AC6">
-        <v>-7.7838087593856751e-005</v>
+        <v>-7.4405674213434475e-005</v>
       </c>
       <c r="AD6">
-        <v>0.00013103166652587701</v>
+        <v>0.00020963647012249478</v>
       </c>
       <c r="AE6">
-        <v>9.2320897361204994e-005</v>
+        <v>0.00010525128930708783</v>
       </c>
       <c r="AF6">
-        <v>0.0068878668341587606</v>
+        <v>0.0068419731188036279</v>
       </c>
       <c r="AG6">
-        <v>0.00050513243106583465</v>
+        <v>0.00052570244195466618</v>
       </c>
       <c r="AH6">
-        <v>-0.001022178401688883</v>
+        <v>-0.0019271281527377549</v>
       </c>
     </row>
     <row r="7">
@@ -1146,103 +1149,103 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>-0.00348109094630574</v>
+        <v>-0.0037952887242513442</v>
       </c>
       <c r="C7">
-        <v>9.0127911432751333e-006</v>
+        <v>8.4260365890866294e-006</v>
       </c>
       <c r="D7">
-        <v>9.6848060760358189e-007</v>
+        <v>5.671585134038289e-007</v>
       </c>
       <c r="E7">
-        <v>-2.7371813060983062e-009</v>
+        <v>2.6807243763485447e-010</v>
       </c>
       <c r="F7">
-        <v>-2.8609118928811698e-005</v>
+        <v>-2.8680903795445361e-005</v>
       </c>
       <c r="G7">
-        <v>-2.0333309727415136e-005</v>
+        <v>-1.9994871302973556e-005</v>
       </c>
       <c r="H7">
-        <v>4.029661698966354e-006</v>
+        <v>4.0379346545997794e-006</v>
       </c>
       <c r="I7">
-        <v>6.7928305069548333e-007</v>
+        <v>6.3229310787963879e-007</v>
       </c>
       <c r="J7">
-        <v>-7.8589468340471455e-006</v>
+        <v>-7.5256200605295937e-006</v>
       </c>
       <c r="K7">
-        <v>-2.152480900076409e-007</v>
+        <v>-2.0794992174394189e-006</v>
       </c>
       <c r="L7">
-        <v>3.8758185245631847e-006</v>
+        <v>1.0574195319817663e-006</v>
       </c>
       <c r="M7">
-        <v>-1.4942099765312731e-005</v>
+        <v>-1.7869099562342042e-005</v>
       </c>
       <c r="N7">
-        <v>-1.3638483366695527e-005</v>
+        <v>-1.5708443498070563e-005</v>
       </c>
       <c r="O7">
-        <v>-6.801652700813965e-005</v>
+        <v>-7.1170358320208165e-005</v>
       </c>
       <c r="P7">
-        <v>6.7408978623315809e-005</v>
+        <v>6.4334052587983025e-005</v>
       </c>
       <c r="Q7">
-        <v>-5.9544585261490812e-005</v>
+        <v>-6.0411349233727184e-005</v>
       </c>
       <c r="R7">
-        <v>-0.00010637674473827733</v>
+        <v>-0.00010723041299715182</v>
       </c>
       <c r="S7">
-        <v>-5.4008570628612764e-005</v>
+        <v>-5.3994170794658674e-005</v>
       </c>
       <c r="T7">
-        <v>-6.1718224007096978e-005</v>
+        <v>-6.2662108654399908e-005</v>
       </c>
       <c r="U7">
-        <v>-4.4872511312121522e-005</v>
+        <v>-4.7611169507052317e-005</v>
       </c>
       <c r="V7">
-        <v>-5.7256347867970861e-005</v>
+        <v>-5.8374011667969319e-005</v>
       </c>
       <c r="W7">
-        <v>-5.0885448607049699e-005</v>
+        <v>-5.1738093082695304e-005</v>
       </c>
       <c r="X7">
-        <v>-6.5752791562152376e-005</v>
+        <v>-6.6547871275548953e-005</v>
       </c>
       <c r="Y7">
-        <v>-7.1502558393846618e-005</v>
+        <v>-7.2590005614538925e-005</v>
       </c>
       <c r="Z7">
-        <v>-6.6562227124323977e-005</v>
+        <v>-6.9044194975464822e-005</v>
       </c>
       <c r="AA7">
-        <v>-7.1446983365581042e-005</v>
+        <v>-8.3551933869536037e-005</v>
       </c>
       <c r="AB7">
-        <v>-8.1645105238659646e-007</v>
+        <v>-1.0073425169862895e-006</v>
       </c>
       <c r="AC7">
-        <v>1.3799175931375203e-005</v>
+        <v>1.3133144856997245e-005</v>
       </c>
       <c r="AD7">
-        <v>1.1788040590183195e-005</v>
+        <v>1.3482190978086173e-005</v>
       </c>
       <c r="AE7">
-        <v>-2.1357885612250776e-005</v>
+        <v>-2.0425349189083405e-005</v>
       </c>
       <c r="AF7">
-        <v>-0.00027252299930161919</v>
+        <v>-0.00027453029369290424</v>
       </c>
       <c r="AG7">
-        <v>-1.1968489229544372e-005</v>
+        <v>-1.1501145960016873e-005</v>
       </c>
       <c r="AH7">
-        <v>-0.00016605042849654169</v>
+        <v>-0.00014289522462295205</v>
       </c>
     </row>
     <row r="8">
@@ -1250,103 +1253,103 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>-0.0010947337587404028</v>
+        <v>-0.00051167218877561191</v>
       </c>
       <c r="C8">
-        <v>-2.6616265918286003e-006</v>
+        <v>-4.4386836146786797e-006</v>
       </c>
       <c r="D8">
-        <v>6.192343336845253e-007</v>
+        <v>1.8990723777065333e-006</v>
       </c>
       <c r="E8">
-        <v>-1.2069981822217435e-008</v>
+        <v>-2.0981996045777586e-008</v>
       </c>
       <c r="F8">
-        <v>-1.6000473221173835e-005</v>
+        <v>-1.6226729905685057e-005</v>
       </c>
       <c r="G8">
-        <v>-8.9742621527388928e-006</v>
+        <v>-7.2654009765892114e-006</v>
       </c>
       <c r="H8">
-        <v>6.7928305069548333e-007</v>
+        <v>6.3229310787963879e-007</v>
       </c>
       <c r="I8">
-        <v>3.3098915926479915e-006</v>
+        <v>3.3365310498027725e-006</v>
       </c>
       <c r="J8">
-        <v>-1.0739423817207383e-005</v>
+        <v>-1.1991324996026463e-005</v>
       </c>
       <c r="K8">
-        <v>-9.0875233293764596e-006</v>
+        <v>-6.6390678359438412e-006</v>
       </c>
       <c r="L8">
-        <v>6.5828502303485272e-006</v>
+        <v>9.0905796791849017e-006</v>
       </c>
       <c r="M8">
-        <v>-1.5327664702895113e-005</v>
+        <v>-1.3565676684350734e-005</v>
       </c>
       <c r="N8">
-        <v>-1.9402600518642762e-005</v>
+        <v>-1.6173409185683054e-005</v>
       </c>
       <c r="O8">
-        <v>-2.9285254367743924e-005</v>
+        <v>-2.6029853321370451e-005</v>
       </c>
       <c r="P8">
-        <v>3.254227219035355e-005</v>
+        <v>2.9861717096366903e-005</v>
       </c>
       <c r="Q8">
-        <v>-2.1584697735086222e-005</v>
+        <v>-2.3195700718175647e-005</v>
       </c>
       <c r="R8">
-        <v>-3.2517523830927284e-005</v>
+        <v>-3.1988711752045098e-005</v>
       </c>
       <c r="S8">
-        <v>-2.3772167478817722e-005</v>
+        <v>-2.2160396650339328e-005</v>
       </c>
       <c r="T8">
-        <v>-3.1965461776069974e-005</v>
+        <v>-3.2324372041095181e-005</v>
       </c>
       <c r="U8">
-        <v>-2.5328070113640451e-005</v>
+        <v>-2.2342797700022625e-005</v>
       </c>
       <c r="V8">
-        <v>-2.7985663601264594e-005</v>
+        <v>-2.9586486678764018e-005</v>
       </c>
       <c r="W8">
-        <v>-2.5793474328901394e-005</v>
+        <v>-2.6505567544639002e-005</v>
       </c>
       <c r="X8">
-        <v>-3.0154905424974887e-005</v>
+        <v>-3.0681303364604311e-005</v>
       </c>
       <c r="Y8">
-        <v>-3.1306668815971953e-005</v>
+        <v>-3.2401057453457197e-005</v>
       </c>
       <c r="Z8">
-        <v>-2.8200401075967056e-005</v>
+        <v>-2.8728158133201981e-005</v>
       </c>
       <c r="AA8">
-        <v>-3.2663576085892628e-005</v>
+        <v>-5.1641255890111471e-005</v>
       </c>
       <c r="AB8">
-        <v>1.5297573586457972e-006</v>
+        <v>1.341448928771049e-006</v>
       </c>
       <c r="AC8">
-        <v>2.5734666512751886e-006</v>
+        <v>3.7435135247499801e-006</v>
       </c>
       <c r="AD8">
-        <v>-6.4819221573405e-007</v>
+        <v>9.2191196015677795e-007</v>
       </c>
       <c r="AE8">
-        <v>-1.8547965668594483e-005</v>
+        <v>-1.8325109982247564e-005</v>
       </c>
       <c r="AF8">
-        <v>-4.4471930840121049e-005</v>
+        <v>-4.1991523566367898e-005</v>
       </c>
       <c r="AG8">
-        <v>-2.5297699455864014e-006</v>
+        <v>-2.2058161436405055e-006</v>
       </c>
       <c r="AH8">
-        <v>-0.00015490633307661469</v>
+        <v>-0.00019698256871113987</v>
       </c>
     </row>
     <row r="9">
@@ -1354,103 +1357,103 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>0.7879937078052992</v>
+        <v>0.77485627980638583</v>
       </c>
       <c r="C9">
-        <v>0.00046113977968170825</v>
+        <v>0.00047725993084746373</v>
       </c>
       <c r="D9">
-        <v>-0.00016935528366010186</v>
+        <v>-0.00019329990415892576</v>
       </c>
       <c r="E9">
-        <v>-2.3105015469423204e-007</v>
+        <v>-5.4191886436613982e-008</v>
       </c>
       <c r="F9">
-        <v>0.00019684768490389382</v>
+        <v>0.00021226453854740392</v>
       </c>
       <c r="G9">
-        <v>0.00039481893604807267</v>
+        <v>0.00037334999079887684</v>
       </c>
       <c r="H9">
-        <v>-7.8589468340471455e-006</v>
+        <v>-7.5256200605295937e-006</v>
       </c>
       <c r="I9">
-        <v>-1.0739423817207383e-005</v>
+        <v>-1.1991324996026463e-005</v>
       </c>
       <c r="J9">
-        <v>0.0036779577433725271</v>
+        <v>0.0036900126391394414</v>
       </c>
       <c r="K9">
-        <v>0.0010899395426433953</v>
+        <v>0.0010268076378352111</v>
       </c>
       <c r="L9">
-        <v>0.00014521787306799637</v>
+        <v>7.7120558748386501e-005</v>
       </c>
       <c r="M9">
-        <v>0.00048961560424530016</v>
+        <v>0.00043651690373588091</v>
       </c>
       <c r="N9">
-        <v>0.00060278299249896632</v>
+        <v>0.00055115819974678459</v>
       </c>
       <c r="O9">
-        <v>0.00052055810864666888</v>
+        <v>0.00045876997706611501</v>
       </c>
       <c r="P9">
-        <v>-0.00047864906084510352</v>
+        <v>-0.0004550469522437749</v>
       </c>
       <c r="Q9">
-        <v>-0.00011629761732184253</v>
+        <v>-0.00012226850758766811</v>
       </c>
       <c r="R9">
-        <v>-4.8797097044146753e-005</v>
+        <v>-5.6157094869523083e-005</v>
       </c>
       <c r="S9">
-        <v>0.00044812905603462162</v>
+        <v>0.00042123989987186659</v>
       </c>
       <c r="T9">
-        <v>0.00010950324896031975</v>
+        <v>0.00010328307391924488</v>
       </c>
       <c r="U9">
-        <v>0.0003005749943901237</v>
+        <v>0.00022656234990201841</v>
       </c>
       <c r="V9">
-        <v>0.00022916510365353533</v>
+        <v>0.00024471973266321917</v>
       </c>
       <c r="W9">
-        <v>-0.00025162216464428427</v>
+        <v>-0.00023721702735280542</v>
       </c>
       <c r="X9">
-        <v>-3.1429110547969569e-005</v>
+        <v>-4.134004719650794e-005</v>
       </c>
       <c r="Y9">
-        <v>0.00029756224487297554</v>
+        <v>0.00030256220723831433</v>
       </c>
       <c r="Z9">
-        <v>0.00011721754681596683</v>
+        <v>0.00014507101567056736</v>
       </c>
       <c r="AA9">
-        <v>3.9340367327285464e-005</v>
+        <v>0.00029511794419327143</v>
       </c>
       <c r="AB9">
-        <v>6.8203794438068035e-005</v>
+        <v>6.8971472579786638e-005</v>
       </c>
       <c r="AC9">
-        <v>3.0286637043717285e-005</v>
+        <v>2.0365020453267171e-005</v>
       </c>
       <c r="AD9">
-        <v>0.00049079255918923169</v>
+        <v>0.0004645467348695833</v>
       </c>
       <c r="AE9">
-        <v>-0.00010350597873122654</v>
+        <v>-0.00010236073386521785</v>
       </c>
       <c r="AF9">
-        <v>-0.00081374103940801135</v>
+        <v>-0.00087972050124497658</v>
       </c>
       <c r="AG9">
-        <v>0.00052771063862498983</v>
+        <v>0.00053942006835001194</v>
       </c>
       <c r="AH9">
-        <v>0.0085750512075545987</v>
+        <v>0.0094577726647311899</v>
       </c>
     </row>
     <row r="10">
@@ -1458,103 +1461,103 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>0.61508376459223724</v>
+        <v>0.62918171366625486</v>
       </c>
       <c r="C10">
-        <v>-0.00038161684614405552</v>
+        <v>-0.00044952064074734355</v>
       </c>
       <c r="D10">
-        <v>0.00087707850052367101</v>
+        <v>0.00089292078514432299</v>
       </c>
       <c r="E10">
-        <v>-7.5915009952358728e-006</v>
+        <v>-7.6806941235559771e-006</v>
       </c>
       <c r="F10">
-        <v>0.00061883766474309532</v>
+        <v>0.00059022742568829519</v>
       </c>
       <c r="G10">
-        <v>0.00067276222119696443</v>
+        <v>0.00070777474133876511</v>
       </c>
       <c r="H10">
-        <v>-2.152480900076409e-007</v>
+        <v>-2.0794992174394189e-006</v>
       </c>
       <c r="I10">
-        <v>-9.0875233293764596e-006</v>
+        <v>-6.6390678359438412e-006</v>
       </c>
       <c r="J10">
-        <v>0.0010899395426433953</v>
+        <v>0.0010268076378352111</v>
       </c>
       <c r="K10">
-        <v>0.0089568691368832592</v>
+        <v>0.0089660276791694825</v>
       </c>
       <c r="L10">
-        <v>0.0016981060027267815</v>
+        <v>0.0017141716509632473</v>
       </c>
       <c r="M10">
-        <v>0.0070029815061413868</v>
+        <v>0.0070405851016975716</v>
       </c>
       <c r="N10">
-        <v>0.0073887281743416251</v>
+        <v>0.0074754929104369656</v>
       </c>
       <c r="O10">
-        <v>0.007487946082805598</v>
+        <v>0.0075868447877514289</v>
       </c>
       <c r="P10">
-        <v>-0.0018542544752586237</v>
+        <v>-0.0018494852122553484</v>
       </c>
       <c r="Q10">
-        <v>0.0012744319912726017</v>
+        <v>0.0013157310960095134</v>
       </c>
       <c r="R10">
-        <v>0.00130330502007895</v>
+        <v>0.0013591066915692798</v>
       </c>
       <c r="S10">
-        <v>0.0011717461708624088</v>
+        <v>0.0011618053842550637</v>
       </c>
       <c r="T10">
-        <v>0.0011921242473710153</v>
+        <v>0.0012447900965659349</v>
       </c>
       <c r="U10">
-        <v>0.0014449802089700776</v>
+        <v>0.0016174661195236476</v>
       </c>
       <c r="V10">
-        <v>0.0013933537367824961</v>
+        <v>0.0014262037967384157</v>
       </c>
       <c r="W10">
-        <v>0.0013676514308236208</v>
+        <v>0.0014231163195223169</v>
       </c>
       <c r="X10">
-        <v>0.0012894169114943572</v>
+        <v>0.0012965759536112224</v>
       </c>
       <c r="Y10">
-        <v>0.0020648885878674743</v>
+        <v>0.0020974415751864976</v>
       </c>
       <c r="Z10">
-        <v>0.0012435662337985237</v>
+        <v>0.001289816876460053</v>
       </c>
       <c r="AA10">
-        <v>0.0012135917085831661</v>
+        <v>0.00094623897970569359</v>
       </c>
       <c r="AB10">
-        <v>-3.4244604967317675e-005</v>
+        <v>-3.7619499609088496e-005</v>
       </c>
       <c r="AC10">
-        <v>0.00024969659377241209</v>
+        <v>0.0002425105784918842</v>
       </c>
       <c r="AD10">
-        <v>0.00050336235269359333</v>
+        <v>0.00048964008701457909</v>
       </c>
       <c r="AE10">
-        <v>-0.00020574904950041405</v>
+        <v>-0.00022052215545302796</v>
       </c>
       <c r="AF10">
-        <v>-0.00098769602388937283</v>
+        <v>-0.00085812201510315766</v>
       </c>
       <c r="AG10">
-        <v>0.00024197441592081851</v>
+        <v>0.00028076574634784143</v>
       </c>
       <c r="AH10">
-        <v>-0.033470072417077432</v>
+        <v>-0.03412094008345555</v>
       </c>
     </row>
     <row r="11">
@@ -1562,103 +1565,103 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>0.058665273203727747</v>
+        <v>0.074549858318754617</v>
       </c>
       <c r="C11">
-        <v>0.00025693072709294889</v>
+        <v>0.00016805615926366674</v>
       </c>
       <c r="D11">
-        <v>0.00022464660251491665</v>
+        <v>0.00027499527210212999</v>
       </c>
       <c r="E11">
-        <v>-2.2060743086697103e-006</v>
+        <v>-2.5428085678137749e-006</v>
       </c>
       <c r="F11">
-        <v>-0.00028371327553128225</v>
+        <v>-0.00031295893523244076</v>
       </c>
       <c r="G11">
-        <v>-4.0870241315141379e-005</v>
+        <v>4.1664123801558428e-005</v>
       </c>
       <c r="H11">
-        <v>3.8758185245631847e-006</v>
+        <v>1.0574195319817663e-006</v>
       </c>
       <c r="I11">
-        <v>6.5828502303485272e-006</v>
+        <v>9.0905796791849017e-006</v>
       </c>
       <c r="J11">
-        <v>0.00014521787306799637</v>
+        <v>7.7120558748386501e-005</v>
       </c>
       <c r="K11">
-        <v>0.0016981060027267815</v>
+        <v>0.0017141716509632473</v>
       </c>
       <c r="L11">
-        <v>0.004278428956861877</v>
+        <v>0.0043672175594218245</v>
       </c>
       <c r="M11">
-        <v>0.0031935615362995405</v>
+        <v>0.0032305340721186775</v>
       </c>
       <c r="N11">
-        <v>0.0030718270632416884</v>
+        <v>0.0031371758163413325</v>
       </c>
       <c r="O11">
-        <v>0.0027372201845838537</v>
+        <v>0.0028322877684086338</v>
       </c>
       <c r="P11">
-        <v>0.00013025983685797287</v>
+        <v>7.8825359195115741e-005</v>
       </c>
       <c r="Q11">
-        <v>-0.00072700096737488614</v>
+        <v>-0.00073305771019248431</v>
       </c>
       <c r="R11">
-        <v>-0.000770074414017035</v>
+        <v>-0.00076691698080166328</v>
       </c>
       <c r="S11">
-        <v>-0.00076873718275365446</v>
+        <v>-0.00070918957247108165</v>
       </c>
       <c r="T11">
-        <v>-0.0010520590389728429</v>
+        <v>-0.0010254101384211986</v>
       </c>
       <c r="U11">
-        <v>-0.0010658879746510614</v>
+        <v>-0.00082881089801290332</v>
       </c>
       <c r="V11">
-        <v>-0.0010404921779257671</v>
+        <v>-0.0010346571724181948</v>
       </c>
       <c r="W11">
-        <v>-0.0010354109631354447</v>
+        <v>-0.0010613829057752305</v>
       </c>
       <c r="X11">
-        <v>-0.00087222441246262742</v>
+        <v>-0.00087709621284273774</v>
       </c>
       <c r="Y11">
-        <v>-0.00021856463567221721</v>
+        <v>-0.00023091163573465013</v>
       </c>
       <c r="Z11">
-        <v>-0.00058302623406248245</v>
+        <v>-0.00058363907789705464</v>
       </c>
       <c r="AA11">
-        <v>-0.00080385573704642955</v>
+        <v>-0.0014329705759947844</v>
       </c>
       <c r="AB11">
-        <v>4.432464497316959e-005</v>
+        <v>3.9903478823300875e-005</v>
       </c>
       <c r="AC11">
-        <v>-0.0001081662740168637</v>
+        <v>-0.00013441061572493041</v>
       </c>
       <c r="AD11">
-        <v>-2.018571901147171e-005</v>
+        <v>4.5915408693277676e-005</v>
       </c>
       <c r="AE11">
-        <v>-0.00049334544350259019</v>
+        <v>-0.00053505122811268449</v>
       </c>
       <c r="AF11">
-        <v>-0.0019950893497531486</v>
+        <v>-0.001920108174969952</v>
       </c>
       <c r="AG11">
-        <v>-0.00095763343029728885</v>
+        <v>-0.00096384816120811435</v>
       </c>
       <c r="AH11">
-        <v>-0.008934837231091286</v>
+        <v>-0.010667054868792623</v>
       </c>
     </row>
     <row r="12">
@@ -1666,103 +1669,103 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <v>0.048976984310005293</v>
+        <v>0.070393091359041607</v>
       </c>
       <c r="C12">
-        <v>1.1194587586794286e-006</v>
+        <v>-8.3083020343160388e-005</v>
       </c>
       <c r="D12">
-        <v>0.00035905792485447716</v>
+        <v>0.00040311869606346473</v>
       </c>
       <c r="E12">
-        <v>-3.3038463342143453e-006</v>
+        <v>-3.6054997783705205e-006</v>
       </c>
       <c r="F12">
-        <v>0.00034395122624735375</v>
+        <v>0.0003352963146669699</v>
       </c>
       <c r="G12">
-        <v>0.00069966620911873366</v>
+        <v>0.00078198695814193898</v>
       </c>
       <c r="H12">
-        <v>-1.4942099765312731e-005</v>
+        <v>-1.7869099562342042e-005</v>
       </c>
       <c r="I12">
-        <v>-1.5327664702895113e-005</v>
+        <v>-1.3565676684350734e-005</v>
       </c>
       <c r="J12">
-        <v>0.00048961560424530016</v>
+        <v>0.00043651690373588091</v>
       </c>
       <c r="K12">
-        <v>0.0070029815061413868</v>
+        <v>0.0070405851016975716</v>
       </c>
       <c r="L12">
-        <v>0.0031935615362995405</v>
+        <v>0.0032305340721186775</v>
       </c>
       <c r="M12">
-        <v>0.010426672997778845</v>
+        <v>0.010473604107478433</v>
       </c>
       <c r="N12">
-        <v>0.0089506280860677401</v>
+        <v>0.0090469323202690237</v>
       </c>
       <c r="O12">
-        <v>0.008920826602297531</v>
+        <v>0.0090642255094086615</v>
       </c>
       <c r="P12">
-        <v>0.00060789300630228072</v>
+        <v>0.00055750987780650747</v>
       </c>
       <c r="Q12">
-        <v>0.00031624139637334743</v>
+        <v>0.00034027327611498362</v>
       </c>
       <c r="R12">
-        <v>0.00030022020225984464</v>
+        <v>0.00035296343526014171</v>
       </c>
       <c r="S12">
-        <v>0.00023180649026834348</v>
+        <v>0.0002977723015135424</v>
       </c>
       <c r="T12">
-        <v>0.00026374764745727263</v>
+        <v>0.00031847121522002655</v>
       </c>
       <c r="U12">
-        <v>0.00052477564631155365</v>
+        <v>0.00070564701151809225</v>
       </c>
       <c r="V12">
-        <v>0.00047173691168150497</v>
+        <v>0.00049057592197365111</v>
       </c>
       <c r="W12">
-        <v>0.00041492168375960401</v>
+        <v>0.00042688798961256109</v>
       </c>
       <c r="X12">
-        <v>0.0007216616119481772</v>
+        <v>0.00072513678301753919</v>
       </c>
       <c r="Y12">
-        <v>0.00098612231806366902</v>
+        <v>0.0010010173519954353</v>
       </c>
       <c r="Z12">
-        <v>0.00057370392540132681</v>
+        <v>0.00060840625022605746</v>
       </c>
       <c r="AA12">
-        <v>0.00053580282559772966</v>
+        <v>-1.1198313090052606e-005</v>
       </c>
       <c r="AB12">
-        <v>-3.4328722333352773e-005</v>
+        <v>-3.8332909936400397e-005</v>
       </c>
       <c r="AC12">
-        <v>0.00042182770516867567</v>
+        <v>0.00039491453755743401</v>
       </c>
       <c r="AD12">
-        <v>0.0004898049848146846</v>
+        <v>0.00054097880569752791</v>
       </c>
       <c r="AE12">
-        <v>0.00010409762927640533</v>
+        <v>7.0063799912934918e-005</v>
       </c>
       <c r="AF12">
-        <v>-0.001281286184342173</v>
+        <v>-0.0010449402298654681</v>
       </c>
       <c r="AG12">
-        <v>-0.00067480927845559274</v>
+        <v>-0.00067502637613636664</v>
       </c>
       <c r="AH12">
-        <v>-0.017424527311906225</v>
+        <v>-0.018937269770477341</v>
       </c>
     </row>
     <row r="13">
@@ -1770,103 +1773,103 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>0.096089185886595957</v>
+        <v>0.11449327643682537</v>
       </c>
       <c r="C13">
-        <v>-0.00017151022915099521</v>
+        <v>-0.00024956895152148761</v>
       </c>
       <c r="D13">
-        <v>0.00038156023466717759</v>
+        <v>0.00042373908339480085</v>
       </c>
       <c r="E13">
-        <v>-3.3716399276370092e-006</v>
+        <v>-3.6614599165258883e-006</v>
       </c>
       <c r="F13">
-        <v>0.0005897194008889292</v>
+        <v>0.00055659138931980626</v>
       </c>
       <c r="G13">
-        <v>0.0010442452935745755</v>
+        <v>0.0011166743283140415</v>
       </c>
       <c r="H13">
-        <v>-1.3638483366695527e-005</v>
+        <v>-1.5708443498070563e-005</v>
       </c>
       <c r="I13">
-        <v>-1.9402600518642762e-005</v>
+        <v>-1.6173409185683054e-005</v>
       </c>
       <c r="J13">
-        <v>0.00060278299249896632</v>
+        <v>0.00055115819974678459</v>
       </c>
       <c r="K13">
-        <v>0.0073887281743416251</v>
+        <v>0.0074754929104369656</v>
       </c>
       <c r="L13">
-        <v>0.0030718270632416884</v>
+        <v>0.0031371758163413325</v>
       </c>
       <c r="M13">
-        <v>0.0089506280860677401</v>
+        <v>0.0090469323202690237</v>
       </c>
       <c r="N13">
-        <v>0.01079720295039269</v>
+        <v>0.010912631658165771</v>
       </c>
       <c r="O13">
-        <v>0.0093843671443571801</v>
+        <v>0.0095794160971254295</v>
       </c>
       <c r="P13">
-        <v>0.00055165386863527139</v>
+        <v>0.00053117604113520501</v>
       </c>
       <c r="Q13">
-        <v>0.0010650335271226996</v>
+        <v>0.0010900050903671615</v>
       </c>
       <c r="R13">
-        <v>0.00096137583163681539</v>
+        <v>0.0010192459785653488</v>
       </c>
       <c r="S13">
-        <v>0.0010463899130441837</v>
+        <v>0.0011163844476582904</v>
       </c>
       <c r="T13">
-        <v>0.00075531605947502713</v>
+        <v>0.00080666957241464117</v>
       </c>
       <c r="U13">
-        <v>0.001031100805219955</v>
+        <v>0.0011847738146300094</v>
       </c>
       <c r="V13">
-        <v>0.0011255887985924442</v>
+        <v>0.0011480010080196033</v>
       </c>
       <c r="W13">
-        <v>0.0012271860738223995</v>
+        <v>0.0012347180459704159</v>
       </c>
       <c r="X13">
-        <v>0.0011229311005690121</v>
+        <v>0.0011256431567068272</v>
       </c>
       <c r="Y13">
-        <v>0.0013446081250018602</v>
+        <v>0.001362299134006496</v>
       </c>
       <c r="Z13">
-        <v>0.00095035372269357959</v>
+        <v>0.00098301849700627338</v>
       </c>
       <c r="AA13">
-        <v>0.0011291507480810621</v>
+        <v>0.00056322843189569871</v>
       </c>
       <c r="AB13">
-        <v>-5.9135188897123077e-005</v>
+        <v>-6.322045254284858e-005</v>
       </c>
       <c r="AC13">
-        <v>0.00050957952120194577</v>
+        <v>0.00049785346587575066</v>
       </c>
       <c r="AD13">
-        <v>0.00061444039903969534</v>
+        <v>0.00069399055150901404</v>
       </c>
       <c r="AE13">
-        <v>0.00030036812255119713</v>
+        <v>0.00026871663783613244</v>
       </c>
       <c r="AF13">
-        <v>-0.00098828629553988911</v>
+        <v>-0.0007280852468784238</v>
       </c>
       <c r="AG13">
-        <v>-0.00040193203087650835</v>
+        <v>-0.00039519406770707364</v>
       </c>
       <c r="AH13">
-        <v>-0.019071146873178395</v>
+        <v>-0.020667478881348733</v>
       </c>
     </row>
     <row r="14">
@@ -1874,103 +1877,103 @@
         <v>28</v>
       </c>
       <c r="B14">
-        <v>0.29195639026946402</v>
+        <v>0.31890394871273253</v>
       </c>
       <c r="C14">
-        <v>-0.0011780319955238283</v>
+        <v>-0.0012617963506765587</v>
       </c>
       <c r="D14">
-        <v>0.00048707247315912805</v>
+        <v>0.00054067845796331587</v>
       </c>
       <c r="E14">
-        <v>-4.328734355233798e-006</v>
+        <v>-4.6943075489085334e-006</v>
       </c>
       <c r="F14">
-        <v>0.0022548327163898845</v>
+        <v>0.0022267248504982684</v>
       </c>
       <c r="G14">
-        <v>0.0026409873422621171</v>
+        <v>0.0027102445330310443</v>
       </c>
       <c r="H14">
-        <v>-6.801652700813965e-005</v>
+        <v>-7.1170358320208165e-005</v>
       </c>
       <c r="I14">
-        <v>-2.9285254367743924e-005</v>
+        <v>-2.6029853321370451e-005</v>
       </c>
       <c r="J14">
-        <v>0.00052055810864666888</v>
+        <v>0.00045876997706611501</v>
       </c>
       <c r="K14">
-        <v>0.007487946082805598</v>
+        <v>0.0075868447877514289</v>
       </c>
       <c r="L14">
-        <v>0.0027372201845838537</v>
+        <v>0.0028322877684086338</v>
       </c>
       <c r="M14">
-        <v>0.008920826602297531</v>
+        <v>0.0090642255094086615</v>
       </c>
       <c r="N14">
-        <v>0.0093843671443571801</v>
+        <v>0.0095794160971254295</v>
       </c>
       <c r="O14">
-        <v>0.013721329961602994</v>
+        <v>0.013938592499293828</v>
       </c>
       <c r="P14">
-        <v>-0.00064222549665253481</v>
+        <v>-0.00065499803455654031</v>
       </c>
       <c r="Q14">
-        <v>0.0043875812855136507</v>
+        <v>0.0043594579022992637</v>
       </c>
       <c r="R14">
-        <v>0.007209588814057262</v>
+        <v>0.007212897992822577</v>
       </c>
       <c r="S14">
-        <v>0.0041158501298124237</v>
+        <v>0.004135257681008371</v>
       </c>
       <c r="T14">
-        <v>0.0043667658360469139</v>
+        <v>0.0043917173449964583</v>
       </c>
       <c r="U14">
-        <v>0.0035966742704601224</v>
+        <v>0.0038166728555616217</v>
       </c>
       <c r="V14">
-        <v>0.0038981577274536227</v>
+        <v>0.0039131701462424562</v>
       </c>
       <c r="W14">
-        <v>0.0040970792814516224</v>
+        <v>0.0040911048381736606</v>
       </c>
       <c r="X14">
-        <v>0.0047392744176341962</v>
+        <v>0.00471880520951839</v>
       </c>
       <c r="Y14">
-        <v>0.0049851303247434794</v>
+        <v>0.0049570218174363589</v>
       </c>
       <c r="Z14">
-        <v>0.0043684391398301145</v>
+        <v>0.0044140177512378333</v>
       </c>
       <c r="AA14">
-        <v>0.0048157892808533284</v>
+        <v>0.0041347556970880491</v>
       </c>
       <c r="AB14">
-        <v>3.390097998296317e-005</v>
+        <v>2.7354484483296197e-005</v>
       </c>
       <c r="AC14">
-        <v>-0.00020927582428525125</v>
+        <v>-0.00020327894263164753</v>
       </c>
       <c r="AD14">
-        <v>-0.00014234426927734779</v>
+        <v>-4.3574259696491091e-005</v>
       </c>
       <c r="AE14">
-        <v>0.0013181510702984841</v>
+        <v>0.0012673440062318762</v>
       </c>
       <c r="AF14">
-        <v>0.015616497237342264</v>
+        <v>0.015763465662252951</v>
       </c>
       <c r="AG14">
-        <v>0.00014464836782914422</v>
+        <v>0.0001392365592525401</v>
       </c>
       <c r="AH14">
-        <v>-0.025086934273075026</v>
+        <v>-0.027016199687477531</v>
       </c>
     </row>
     <row r="15">
@@ -1978,103 +1981,103 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <v>-0.15686314940574092</v>
+        <v>-0.15047232073835276</v>
       </c>
       <c r="C15">
-        <v>0.00039186888805799094</v>
+        <v>0.0004119258562408155</v>
       </c>
       <c r="D15">
-        <v>-0.00037931576460976252</v>
+        <v>-0.00037847685750770632</v>
       </c>
       <c r="E15">
-        <v>3.6110292346240428e-006</v>
+        <v>3.5999995982966774e-006</v>
       </c>
       <c r="F15">
-        <v>-0.00086474991207307304</v>
+        <v>-0.00081718167609216223</v>
       </c>
       <c r="G15">
-        <v>-0.0007308270268661576</v>
+        <v>-0.00072765040284540898</v>
       </c>
       <c r="H15">
-        <v>6.7408978623315809e-005</v>
+        <v>6.4334052587983025e-005</v>
       </c>
       <c r="I15">
-        <v>3.254227219035355e-005</v>
+        <v>2.9861717096366903e-005</v>
       </c>
       <c r="J15">
-        <v>-0.00047864906084510352</v>
+        <v>-0.0004550469522437749</v>
       </c>
       <c r="K15">
-        <v>-0.0018542544752586237</v>
+        <v>-0.0018494852122553484</v>
       </c>
       <c r="L15">
-        <v>0.00013025983685797287</v>
+        <v>7.8825359195115741e-005</v>
       </c>
       <c r="M15">
-        <v>0.00060789300630228072</v>
+        <v>0.00055750987780650747</v>
       </c>
       <c r="N15">
-        <v>0.00055165386863527139</v>
+        <v>0.00053117604113520501</v>
       </c>
       <c r="O15">
-        <v>-0.00064222549665253481</v>
+        <v>-0.00065499803455654031</v>
       </c>
       <c r="P15">
-        <v>0.0052249703920062398</v>
+        <v>0.0051450197233989846</v>
       </c>
       <c r="Q15">
-        <v>-0.0015134808542326622</v>
+        <v>-0.0015696245248767613</v>
       </c>
       <c r="R15">
-        <v>-0.0027056846440324141</v>
+        <v>-0.0027290039204053845</v>
       </c>
       <c r="S15">
-        <v>-0.0016278516966598761</v>
+        <v>-0.0015959901550381961</v>
       </c>
       <c r="T15">
-        <v>-0.0016973612219495504</v>
+        <v>-0.0017383869107770828</v>
       </c>
       <c r="U15">
-        <v>-0.0012542789211089202</v>
+        <v>-0.0012153357764700216</v>
       </c>
       <c r="V15">
-        <v>-0.0015659852000441885</v>
+        <v>-0.0016097379399711894</v>
       </c>
       <c r="W15">
-        <v>-0.0013723409077312882</v>
+        <v>-0.0014207856719574349</v>
       </c>
       <c r="X15">
-        <v>-0.0016076731414765072</v>
+        <v>-0.0016299775716921185</v>
       </c>
       <c r="Y15">
-        <v>-0.0023205645084261334</v>
+        <v>-0.0023684915857274521</v>
       </c>
       <c r="Z15">
-        <v>-0.001815047162828101</v>
+        <v>-0.0018724375429985248</v>
       </c>
       <c r="AA15">
-        <v>-0.0020488255113744647</v>
+        <v>-0.0018284355101627035</v>
       </c>
       <c r="AB15">
-        <v>-6.2284167361647885e-005</v>
+        <v>-5.6782142819483466e-005</v>
       </c>
       <c r="AC15">
-        <v>0.00064173792130792304</v>
+        <v>0.00056465180211935032</v>
       </c>
       <c r="AD15">
-        <v>0.00051835601033677937</v>
+        <v>0.00051581357157254488</v>
       </c>
       <c r="AE15">
-        <v>-8.5373684195128637e-005</v>
+        <v>-0.00010233236484238862</v>
       </c>
       <c r="AF15">
-        <v>-0.0060385525283479166</v>
+        <v>-0.0060385697317993231</v>
       </c>
       <c r="AG15">
-        <v>-0.00029551308040687632</v>
+        <v>-0.00036435477695407822</v>
       </c>
       <c r="AH15">
-        <v>0.0075078597127437932</v>
+        <v>0.0076964253134643376</v>
       </c>
     </row>
     <row r="16">
@@ -2082,103 +2085,103 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>0.21212702538377706</v>
+        <v>0.19498921207128844</v>
       </c>
       <c r="C16">
-        <v>-0.0012482389807207369</v>
+        <v>-0.0012400506007801957</v>
       </c>
       <c r="D16">
-        <v>0.00020278560873141643</v>
+        <v>0.00019799251474569152</v>
       </c>
       <c r="E16">
-        <v>-1.518344352639334e-006</v>
+        <v>-1.4852569616151975e-006</v>
       </c>
       <c r="F16">
-        <v>0.0012678231689615444</v>
+        <v>0.0012931939006853746</v>
       </c>
       <c r="G16">
-        <v>0.0009789783747621403</v>
+        <v>0.00098886710158728485</v>
       </c>
       <c r="H16">
-        <v>-5.9544585261490812e-005</v>
+        <v>-6.0411349233727184e-005</v>
       </c>
       <c r="I16">
-        <v>-2.1584697735086222e-005</v>
+        <v>-2.3195700718175647e-005</v>
       </c>
       <c r="J16">
-        <v>-0.00011629761732184253</v>
+        <v>-0.00012226850758766811</v>
       </c>
       <c r="K16">
-        <v>0.0012744319912726017</v>
+        <v>0.0013157310960095134</v>
       </c>
       <c r="L16">
-        <v>-0.00072700096737488614</v>
+        <v>-0.00073305771019248431</v>
       </c>
       <c r="M16">
-        <v>0.00031624139637334743</v>
+        <v>0.00034027327611498362</v>
       </c>
       <c r="N16">
-        <v>0.0010650335271226996</v>
+        <v>0.0010900050903671615</v>
       </c>
       <c r="O16">
-        <v>0.0043875812855136507</v>
+        <v>0.0043594579022992637</v>
       </c>
       <c r="P16">
-        <v>-0.0015134808542326622</v>
+        <v>-0.0015696245248767613</v>
       </c>
       <c r="Q16">
-        <v>0.014652530737041657</v>
+        <v>0.014709475549306926</v>
       </c>
       <c r="R16">
-        <v>0.011679015097436712</v>
+        <v>0.011660165653103207</v>
       </c>
       <c r="S16">
-        <v>0.0085532056821676743</v>
+        <v>0.0085439320330676881</v>
       </c>
       <c r="T16">
-        <v>0.0088529644522631849</v>
+        <v>0.0088590655845805066</v>
       </c>
       <c r="U16">
-        <v>0.0078624246105244711</v>
+        <v>0.0078502257147677387</v>
       </c>
       <c r="V16">
-        <v>0.0083139227913300983</v>
+        <v>0.0083434891310330619</v>
       </c>
       <c r="W16">
-        <v>0.0084933485540305415</v>
+        <v>0.0084876444549209541</v>
       </c>
       <c r="X16">
-        <v>0.0089773806356036809</v>
+        <v>0.0089912499719344494</v>
       </c>
       <c r="Y16">
-        <v>0.008804808177287321</v>
+        <v>0.0087842592744820421</v>
       </c>
       <c r="Z16">
-        <v>0.0089473005451822518</v>
+        <v>0.0089666734127294128</v>
       </c>
       <c r="AA16">
-        <v>0.009205031423763629</v>
+        <v>0.0091152761538063325</v>
       </c>
       <c r="AB16">
-        <v>3.0831965482488598e-005</v>
+        <v>2.7597326924099202e-005</v>
       </c>
       <c r="AC16">
-        <v>-0.00061133373139175308</v>
+        <v>-0.00059094316174897838</v>
       </c>
       <c r="AD16">
-        <v>-0.00018762069956654087</v>
+        <v>-0.0001330654733918404</v>
       </c>
       <c r="AE16">
-        <v>0.0032216873693846175</v>
+        <v>0.0032543053553938822</v>
       </c>
       <c r="AF16">
-        <v>0.021014660821962704</v>
+        <v>0.020985920751230513</v>
       </c>
       <c r="AG16">
-        <v>0.0019943273614936663</v>
+        <v>0.001923505930538397</v>
       </c>
       <c r="AH16">
-        <v>-0.013885936811091605</v>
+        <v>-0.013568023619253699</v>
       </c>
     </row>
     <row r="17">
@@ -2186,103 +2189,103 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>0.22485453915387196</v>
+        <v>0.22919334068716524</v>
       </c>
       <c r="C17">
-        <v>-0.001798117669387117</v>
+        <v>-0.001752979235595681</v>
       </c>
       <c r="D17">
-        <v>0.00020182335764576398</v>
+        <v>0.00020179938610083437</v>
       </c>
       <c r="E17">
-        <v>-1.8756847454518867e-006</v>
+        <v>-1.8791101348170514e-006</v>
       </c>
       <c r="F17">
-        <v>0.0027009654577510637</v>
+        <v>0.0027084558375285411</v>
       </c>
       <c r="G17">
-        <v>0.0022101295935046234</v>
+        <v>0.0021788963811873209</v>
       </c>
       <c r="H17">
-        <v>-0.00010637674473827733</v>
+        <v>-0.00010723041299715182</v>
       </c>
       <c r="I17">
-        <v>-3.2517523830927284e-005</v>
+        <v>-3.1988711752045098e-005</v>
       </c>
       <c r="J17">
-        <v>-4.8797097044146753e-005</v>
+        <v>-5.6157094869523083e-005</v>
       </c>
       <c r="K17">
-        <v>0.00130330502007895</v>
+        <v>0.0013591066915692798</v>
       </c>
       <c r="L17">
-        <v>-0.000770074414017035</v>
+        <v>-0.00076691698080166328</v>
       </c>
       <c r="M17">
-        <v>0.00030022020225984464</v>
+        <v>0.00035296343526014171</v>
       </c>
       <c r="N17">
-        <v>0.00096137583163681539</v>
+        <v>0.0010192459785653488</v>
       </c>
       <c r="O17">
-        <v>0.007209588814057262</v>
+        <v>0.007212897992822577</v>
       </c>
       <c r="P17">
-        <v>-0.0027056846440324141</v>
+        <v>-0.0027290039204053845</v>
       </c>
       <c r="Q17">
-        <v>0.011679015097436712</v>
+        <v>0.011660165653103207</v>
       </c>
       <c r="R17">
-        <v>0.019632675472434486</v>
+        <v>0.019562179373491501</v>
       </c>
       <c r="S17">
-        <v>0.011263903484521503</v>
+        <v>0.011230377153280161</v>
       </c>
       <c r="T17">
-        <v>0.011672223152543123</v>
+        <v>0.011666140138059035</v>
       </c>
       <c r="U17">
-        <v>0.010134802071205292</v>
+        <v>0.010122770688945001</v>
       </c>
       <c r="V17">
-        <v>0.010869404466323286</v>
+        <v>0.010907253458070101</v>
       </c>
       <c r="W17">
-        <v>0.011109024813614896</v>
+        <v>0.011094008077860644</v>
       </c>
       <c r="X17">
-        <v>0.01202524052817433</v>
+        <v>0.012031490949979514</v>
       </c>
       <c r="Y17">
-        <v>0.011870620532578998</v>
+        <v>0.011823294663066334</v>
       </c>
       <c r="Z17">
-        <v>0.011894128707734463</v>
+        <v>0.011906488608960587</v>
       </c>
       <c r="AA17">
-        <v>0.012545731900847099</v>
+        <v>0.012389215922052992</v>
       </c>
       <c r="AB17">
-        <v>0.00016871306860602388</v>
+        <v>0.00016233642999001073</v>
       </c>
       <c r="AC17">
-        <v>-0.0015532990440511401</v>
+        <v>-0.001522242615115345</v>
       </c>
       <c r="AD17">
-        <v>-0.0013019315159191807</v>
+        <v>-0.0012373644160117835</v>
       </c>
       <c r="AE17">
-        <v>0.0038605855805602671</v>
+        <v>0.0038934851761684352</v>
       </c>
       <c r="AF17">
-        <v>0.037669316020384661</v>
+        <v>0.037532000438459528</v>
       </c>
       <c r="AG17">
-        <v>0.0021365357945701989</v>
+        <v>0.0020953449363210735</v>
       </c>
       <c r="AH17">
-        <v>-0.016202331294311794</v>
+        <v>-0.016097737061240205</v>
       </c>
     </row>
     <row r="18">
@@ -2290,103 +2293,103 @@
         <v>32</v>
       </c>
       <c r="B18">
-        <v>0.12520833027084741</v>
+        <v>0.11364634617343179</v>
       </c>
       <c r="C18">
-        <v>-0.0011046076567213512</v>
+        <v>-0.0011044162876284705</v>
       </c>
       <c r="D18">
-        <v>6.9546401326808782e-005</v>
+        <v>5.3164751290087076e-005</v>
       </c>
       <c r="E18">
-        <v>-6.6729025364022695e-007</v>
+        <v>-5.5109245810546414e-007</v>
       </c>
       <c r="F18">
-        <v>0.0017820943783218948</v>
+        <v>0.0017761513120647533</v>
       </c>
       <c r="G18">
-        <v>0.0014905784533018381</v>
+        <v>0.0015132251795556386</v>
       </c>
       <c r="H18">
-        <v>-5.4008570628612764e-005</v>
+        <v>-5.3994170794658674e-005</v>
       </c>
       <c r="I18">
-        <v>-2.3772167478817722e-005</v>
+        <v>-2.2160396650339328e-005</v>
       </c>
       <c r="J18">
-        <v>0.00044812905603462162</v>
+        <v>0.00042123989987186659</v>
       </c>
       <c r="K18">
-        <v>0.0011717461708624088</v>
+        <v>0.0011618053842550637</v>
       </c>
       <c r="L18">
-        <v>-0.00076873718275365446</v>
+        <v>-0.00070918957247108165</v>
       </c>
       <c r="M18">
-        <v>0.00023180649026834348</v>
+        <v>0.0002977723015135424</v>
       </c>
       <c r="N18">
-        <v>0.0010463899130441837</v>
+        <v>0.0011163844476582904</v>
       </c>
       <c r="O18">
-        <v>0.0041158501298124237</v>
+        <v>0.004135257681008371</v>
       </c>
       <c r="P18">
-        <v>-0.0016278516966598761</v>
+        <v>-0.0015959901550381961</v>
       </c>
       <c r="Q18">
-        <v>0.0085532056821676743</v>
+        <v>0.0085439320330676881</v>
       </c>
       <c r="R18">
-        <v>0.011263903484521503</v>
+        <v>0.011230377153280161</v>
       </c>
       <c r="S18">
-        <v>0.012326127258251749</v>
+        <v>0.012404247068863406</v>
       </c>
       <c r="T18">
-        <v>0.0085918616422893113</v>
+        <v>0.0085880419554335702</v>
       </c>
       <c r="U18">
-        <v>0.0076667288851367948</v>
+        <v>0.0076828668700668675</v>
       </c>
       <c r="V18">
-        <v>0.008067908033058218</v>
+        <v>0.0080970320675001449</v>
       </c>
       <c r="W18">
-        <v>0.0082513825735067246</v>
+        <v>0.0082495293725753111</v>
       </c>
       <c r="X18">
-        <v>0.0087158000702584858</v>
+        <v>0.0087195192111342804</v>
       </c>
       <c r="Y18">
-        <v>0.0085625338330146995</v>
+        <v>0.008546995349838736</v>
       </c>
       <c r="Z18">
-        <v>0.0086982243194381921</v>
+        <v>0.0087146935578089578</v>
       </c>
       <c r="AA18">
-        <v>0.0089432727769642121</v>
+        <v>0.0088718148999862891</v>
       </c>
       <c r="AB18">
-        <v>2.3182877259147333e-005</v>
+        <v>2.2288423146303452e-005</v>
       </c>
       <c r="AC18">
-        <v>-0.00031360940995009282</v>
+        <v>-0.00034140819334361767</v>
       </c>
       <c r="AD18">
-        <v>0.00019241120015423517</v>
+        <v>0.00017778054945115536</v>
       </c>
       <c r="AE18">
-        <v>0.00314865639819504</v>
+        <v>0.003179388566618575</v>
       </c>
       <c r="AF18">
-        <v>0.019905540736617506</v>
+        <v>0.019783038964295299</v>
       </c>
       <c r="AG18">
-        <v>0.0018563111679848674</v>
+        <v>0.0018357515653340852</v>
       </c>
       <c r="AH18">
-        <v>-0.0092483266386816643</v>
+        <v>-0.0087718687944399049</v>
       </c>
     </row>
     <row r="19">
@@ -2394,103 +2397,103 @@
         <v>33</v>
       </c>
       <c r="B19">
-        <v>0.17014067074141453</v>
+        <v>0.18008110954421672</v>
       </c>
       <c r="C19">
-        <v>-0.0014137203807011096</v>
+        <v>-0.0013855037154989363</v>
       </c>
       <c r="D19">
-        <v>8.1373291788984503e-005</v>
+        <v>7.9164708423541674e-005</v>
       </c>
       <c r="E19">
-        <v>-6.5716702936661955e-007</v>
+        <v>-6.4763107066723559e-007</v>
       </c>
       <c r="F19">
-        <v>0.001449276149188898</v>
+        <v>0.0014529282599344687</v>
       </c>
       <c r="G19">
-        <v>0.0010197147105967526</v>
+        <v>0.0010013006414027656</v>
       </c>
       <c r="H19">
-        <v>-6.1718224007096978e-005</v>
+        <v>-6.2662108654399908e-005</v>
       </c>
       <c r="I19">
-        <v>-3.1965461776069974e-005</v>
+        <v>-3.2324372041095181e-005</v>
       </c>
       <c r="J19">
-        <v>0.00010950324896031975</v>
+        <v>0.00010328307391924488</v>
       </c>
       <c r="K19">
-        <v>0.0011921242473710153</v>
+        <v>0.0012447900965659349</v>
       </c>
       <c r="L19">
-        <v>-0.0010520590389728429</v>
+        <v>-0.0010254101384211986</v>
       </c>
       <c r="M19">
-        <v>0.00026374764745727263</v>
+        <v>0.00031847121522002655</v>
       </c>
       <c r="N19">
-        <v>0.00075531605947502713</v>
+        <v>0.00080666957241464117</v>
       </c>
       <c r="O19">
-        <v>0.0043667658360469139</v>
+        <v>0.0043917173449964583</v>
       </c>
       <c r="P19">
-        <v>-0.0016973612219495504</v>
+        <v>-0.0017383869107770828</v>
       </c>
       <c r="Q19">
-        <v>0.0088529644522631849</v>
+        <v>0.0088590655845805066</v>
       </c>
       <c r="R19">
-        <v>0.011672223152543123</v>
+        <v>0.011666140138059035</v>
       </c>
       <c r="S19">
-        <v>0.0085918616422893113</v>
+        <v>0.0085880419554335702</v>
       </c>
       <c r="T19">
-        <v>0.013450377083368673</v>
+        <v>0.013379832213021548</v>
       </c>
       <c r="U19">
-        <v>0.0079380446401318382</v>
+        <v>0.0079463148224715504</v>
       </c>
       <c r="V19">
-        <v>0.008385861923436105</v>
+        <v>0.0084250071033311388</v>
       </c>
       <c r="W19">
-        <v>0.0085193590334098762</v>
+        <v>0.0085313157182222883</v>
       </c>
       <c r="X19">
-        <v>0.0090585285026948594</v>
+        <v>0.0090796609549258153</v>
       </c>
       <c r="Y19">
-        <v>0.0089336617462161625</v>
+        <v>0.0089297023710487346</v>
       </c>
       <c r="Z19">
-        <v>0.0090220954611212548</v>
+        <v>0.0090523164493679052</v>
       </c>
       <c r="AA19">
-        <v>0.0093464410830742216</v>
+        <v>0.0092788070255344305</v>
       </c>
       <c r="AB19">
-        <v>4.5157096031500773e-005</v>
+        <v>4.3108872346140888e-005</v>
       </c>
       <c r="AC19">
-        <v>-0.00067196870663709671</v>
+        <v>-0.00063878496559814039</v>
       </c>
       <c r="AD19">
-        <v>-0.00062754395268585419</v>
+        <v>-0.00060311079026196786</v>
       </c>
       <c r="AE19">
-        <v>0.00299342701996571</v>
+        <v>0.0030237732805300432</v>
       </c>
       <c r="AF19">
-        <v>0.020798059725050666</v>
+        <v>0.020772277039572795</v>
       </c>
       <c r="AG19">
-        <v>0.0020747033550684245</v>
+        <v>0.0020354251848845708</v>
       </c>
       <c r="AH19">
-        <v>-0.0092911804881646021</v>
+        <v>-0.0091502308541321978</v>
       </c>
     </row>
     <row r="20">
@@ -2498,103 +2501,103 @@
         <v>34</v>
       </c>
       <c r="B20">
-        <v>0.034857116150862122</v>
+        <v>0.051314653015136477</v>
       </c>
       <c r="C20">
-        <v>-0.00090248496756083142</v>
+        <v>-0.0009235843618826305</v>
       </c>
       <c r="D20">
-        <v>0.00013802259772046147</v>
+        <v>0.00017724003109485797</v>
       </c>
       <c r="E20">
-        <v>-1.1848409301943696e-006</v>
+        <v>-1.4451342233057392e-006</v>
       </c>
       <c r="F20">
-        <v>0.0011820816616825002</v>
+        <v>0.0011663657908983381</v>
       </c>
       <c r="G20">
-        <v>0.00092552016326934053</v>
+        <v>0.00098877265442824441</v>
       </c>
       <c r="H20">
-        <v>-4.4872511312121522e-005</v>
+        <v>-4.7611169507052317e-005</v>
       </c>
       <c r="I20">
-        <v>-2.5328070113640451e-005</v>
+        <v>-2.2342797700022625e-005</v>
       </c>
       <c r="J20">
-        <v>0.0003005749943901237</v>
+        <v>0.00022656234990201841</v>
       </c>
       <c r="K20">
-        <v>0.0014449802089700776</v>
+        <v>0.0016174661195236476</v>
       </c>
       <c r="L20">
-        <v>-0.0010658879746510614</v>
+        <v>-0.00082881089801290332</v>
       </c>
       <c r="M20">
-        <v>0.00052477564631155365</v>
+        <v>0.00070564701151809225</v>
       </c>
       <c r="N20">
-        <v>0.001031100805219955</v>
+        <v>0.0011847738146300094</v>
       </c>
       <c r="O20">
-        <v>0.0035966742704601224</v>
+        <v>0.0038166728555616217</v>
       </c>
       <c r="P20">
-        <v>-0.0012542789211089202</v>
+        <v>-0.0012153357764700216</v>
       </c>
       <c r="Q20">
-        <v>0.0078624246105244711</v>
+        <v>0.0078502257147677387</v>
       </c>
       <c r="R20">
-        <v>0.010134802071205292</v>
+        <v>0.010122770688945001</v>
       </c>
       <c r="S20">
-        <v>0.0076667288851367948</v>
+        <v>0.0076828668700668675</v>
       </c>
       <c r="T20">
-        <v>0.0079380446401318382</v>
+        <v>0.0079463148224715504</v>
       </c>
       <c r="U20">
-        <v>0.011792401451708569</v>
+        <v>0.011864612924827038</v>
       </c>
       <c r="V20">
-        <v>0.0075187466428319194</v>
+        <v>0.0075531615113648013</v>
       </c>
       <c r="W20">
-        <v>0.0076730695107854498</v>
+        <v>0.0076839211716017821</v>
       </c>
       <c r="X20">
-        <v>0.0080821693311308521</v>
+        <v>0.0080999325576045951</v>
       </c>
       <c r="Y20">
-        <v>0.0078746817836951814</v>
+        <v>0.0078663495401524383</v>
       </c>
       <c r="Z20">
-        <v>0.007994618366927022</v>
+        <v>0.0080194259064245797</v>
       </c>
       <c r="AA20">
-        <v>0.0082109669940288663</v>
+        <v>0.0081321525518787564</v>
       </c>
       <c r="AB20">
-        <v>9.4632973192917188e-006</v>
+        <v>1.5008214711442584e-005</v>
       </c>
       <c r="AC20">
-        <v>-4.8071714685039672e-005</v>
+        <v>-6.9585107433313594e-005</v>
       </c>
       <c r="AD20">
-        <v>-0.00014633647626009424</v>
+        <v>-0.00018372963733182066</v>
       </c>
       <c r="AE20">
-        <v>0.0024561704045603992</v>
+        <v>0.0024432313578488505</v>
       </c>
       <c r="AF20">
-        <v>0.016818532466912884</v>
+        <v>0.016749424720029788</v>
       </c>
       <c r="AG20">
-        <v>0.0014406140864632289</v>
+        <v>0.0013971580225515111</v>
       </c>
       <c r="AH20">
-        <v>-0.010566928649782013</v>
+        <v>-0.012308891839938624</v>
       </c>
     </row>
     <row r="21">
@@ -2602,103 +2605,103 @@
         <v>35</v>
       </c>
       <c r="B21">
-        <v>0.18387346542896454</v>
+        <v>0.19316226955733787</v>
       </c>
       <c r="C21">
-        <v>-0.0010485859972540238</v>
+        <v>-0.0010197156011623847</v>
       </c>
       <c r="D21">
-        <v>0.00012918642618203746</v>
+        <v>0.00012868067162564306</v>
       </c>
       <c r="E21">
-        <v>-1.0858822021280888e-006</v>
+        <v>-1.0873565336841796e-006</v>
       </c>
       <c r="F21">
-        <v>0.0013068593400176074</v>
+        <v>0.001335661274960275</v>
       </c>
       <c r="G21">
-        <v>0.0010845009162291275</v>
+        <v>0.0010799635905759455</v>
       </c>
       <c r="H21">
-        <v>-5.7256347867970861e-005</v>
+        <v>-5.8374011667969319e-005</v>
       </c>
       <c r="I21">
-        <v>-2.7985663601264594e-005</v>
+        <v>-2.9586486678764018e-005</v>
       </c>
       <c r="J21">
-        <v>0.00022916510365353533</v>
+        <v>0.00024471973266321917</v>
       </c>
       <c r="K21">
-        <v>0.0013933537367824961</v>
+        <v>0.0014262037967384157</v>
       </c>
       <c r="L21">
-        <v>-0.0010404921779257671</v>
+        <v>-0.0010346571724181948</v>
       </c>
       <c r="M21">
-        <v>0.00047173691168150497</v>
+        <v>0.00049057592197365111</v>
       </c>
       <c r="N21">
-        <v>0.0011255887985924442</v>
+        <v>0.0011480010080196033</v>
       </c>
       <c r="O21">
-        <v>0.0038981577274536227</v>
+        <v>0.0039131701462424562</v>
       </c>
       <c r="P21">
-        <v>-0.0015659852000441885</v>
+        <v>-0.0016097379399711894</v>
       </c>
       <c r="Q21">
-        <v>0.0083139227913300983</v>
+        <v>0.0083434891310330619</v>
       </c>
       <c r="R21">
-        <v>0.010869404466323286</v>
+        <v>0.010907253458070101</v>
       </c>
       <c r="S21">
-        <v>0.008067908033058218</v>
+        <v>0.0080970320675001449</v>
       </c>
       <c r="T21">
-        <v>0.008385861923436105</v>
+        <v>0.0084250071033311388</v>
       </c>
       <c r="U21">
-        <v>0.0075187466428319194</v>
+        <v>0.0075531615113648013</v>
       </c>
       <c r="V21">
-        <v>0.011430344020605825</v>
+        <v>0.0114182219107268</v>
       </c>
       <c r="W21">
-        <v>0.0080764754351377449</v>
+        <v>0.0081115791469375496</v>
       </c>
       <c r="X21">
-        <v>0.0085131962648552044</v>
+        <v>0.0085593884266802998</v>
       </c>
       <c r="Y21">
-        <v>0.0083792524259059045</v>
+        <v>0.0084039496213739826</v>
       </c>
       <c r="Z21">
-        <v>0.0084767744662138829</v>
+        <v>0.0085322311087242756</v>
       </c>
       <c r="AA21">
-        <v>0.0086954607747426749</v>
+        <v>0.008738544750882175</v>
       </c>
       <c r="AB21">
-        <v>3.4197688344012674e-005</v>
+        <v>3.4755112106159671e-005</v>
       </c>
       <c r="AC21">
-        <v>-0.00047170876806799282</v>
+        <v>-0.00045802014421133684</v>
       </c>
       <c r="AD21">
-        <v>-5.2651086661682951e-005</v>
+        <v>-2.8126417894573826e-005</v>
       </c>
       <c r="AE21">
-        <v>0.002762369541897236</v>
+        <v>0.0028257850570295082</v>
       </c>
       <c r="AF21">
-        <v>0.018787680812335873</v>
+        <v>0.018868807345236681</v>
       </c>
       <c r="AG21">
-        <v>0.0018136242033043935</v>
+        <v>0.0017769258453250866</v>
       </c>
       <c r="AH21">
-        <v>-0.01058383665308444</v>
+        <v>-0.010511309422409</v>
       </c>
     </row>
     <row r="22">
@@ -2706,103 +2709,103 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>0.029317512734062329</v>
+        <v>0.044814643536305251</v>
       </c>
       <c r="C22">
-        <v>-0.0011651105472551329</v>
+        <v>-0.0011201294848247753</v>
       </c>
       <c r="D22">
-        <v>0.00024540354067589115</v>
+        <v>0.00023916827055788653</v>
       </c>
       <c r="E22">
-        <v>-1.8458183713621523e-006</v>
+        <v>-1.8055250574175344e-006</v>
       </c>
       <c r="F22">
-        <v>0.0016368364146086846</v>
+        <v>0.0016427530023333783</v>
       </c>
       <c r="G22">
-        <v>0.0011853874084692369</v>
+        <v>0.0011602300072375798</v>
       </c>
       <c r="H22">
-        <v>-5.0885448607049699e-005</v>
+        <v>-5.1738093082695304e-005</v>
       </c>
       <c r="I22">
-        <v>-2.5793474328901394e-005</v>
+        <v>-2.6505567544639002e-005</v>
       </c>
       <c r="J22">
-        <v>-0.00025162216464428427</v>
+        <v>-0.00023721702735280542</v>
       </c>
       <c r="K22">
-        <v>0.0013676514308236208</v>
+        <v>0.0014231163195223169</v>
       </c>
       <c r="L22">
-        <v>-0.0010354109631354447</v>
+        <v>-0.0010613829057752305</v>
       </c>
       <c r="M22">
-        <v>0.00041492168375960401</v>
+        <v>0.00042688798961256109</v>
       </c>
       <c r="N22">
-        <v>0.0012271860738223995</v>
+        <v>0.0012347180459704159</v>
       </c>
       <c r="O22">
-        <v>0.0040970792814516224</v>
+        <v>0.0040911048381736606</v>
       </c>
       <c r="P22">
-        <v>-0.0013723409077312882</v>
+        <v>-0.0014207856719574349</v>
       </c>
       <c r="Q22">
-        <v>0.0084933485540305415</v>
+        <v>0.0084876444549209541</v>
       </c>
       <c r="R22">
-        <v>0.011109024813614896</v>
+        <v>0.011094008077860644</v>
       </c>
       <c r="S22">
-        <v>0.0082513825735067246</v>
+        <v>0.0082495293725753111</v>
       </c>
       <c r="T22">
-        <v>0.0085193590334098762</v>
+        <v>0.0085313157182222883</v>
       </c>
       <c r="U22">
-        <v>0.0076730695107854498</v>
+        <v>0.0076839211716017821</v>
       </c>
       <c r="V22">
-        <v>0.0080764754351377449</v>
+        <v>0.0081115791469375496</v>
       </c>
       <c r="W22">
-        <v>0.010780716220465517</v>
+        <v>0.010756736531311355</v>
       </c>
       <c r="X22">
-        <v>0.0087064667318983019</v>
+        <v>0.0087263727199244912</v>
       </c>
       <c r="Y22">
-        <v>0.0085424447697488026</v>
+        <v>0.0085306322110856106</v>
       </c>
       <c r="Z22">
-        <v>0.0086296860438483287</v>
+        <v>0.0086540406312121329</v>
       </c>
       <c r="AA22">
-        <v>0.008970751455051551</v>
+        <v>0.0089739555029591609</v>
       </c>
       <c r="AB22">
-        <v>3.6481387675536955e-005</v>
+        <v>3.4905993906154216e-005</v>
       </c>
       <c r="AC22">
-        <v>-0.00057980136222328957</v>
+        <v>-0.00053361324755466216</v>
       </c>
       <c r="AD22">
-        <v>-0.00047629088870295355</v>
+        <v>-0.00044848674161436638</v>
       </c>
       <c r="AE22">
-        <v>0.0030701358915969129</v>
+        <v>0.0031122143265927089</v>
       </c>
       <c r="AF22">
-        <v>0.019436020097634517</v>
+        <v>0.019366959854394676</v>
       </c>
       <c r="AG22">
-        <v>0.0025075037591700171</v>
+        <v>0.0024733326045847134</v>
       </c>
       <c r="AH22">
-        <v>-0.015496873487098994</v>
+        <v>-0.015203458809972654</v>
       </c>
     </row>
     <row r="23">
@@ -2810,103 +2813,103 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>0.1491551599409289</v>
+        <v>0.12448439974317975</v>
       </c>
       <c r="C23">
-        <v>-0.0012504886266040162</v>
+        <v>-0.0012167530673551398</v>
       </c>
       <c r="D23">
-        <v>0.00019990819128574977</v>
+        <v>0.00018580140151630564</v>
       </c>
       <c r="E23">
-        <v>-1.6632847674714316e-006</v>
+        <v>-1.5645936441537598e-006</v>
       </c>
       <c r="F23">
-        <v>0.0016565600036729299</v>
+        <v>0.0016618138205497365</v>
       </c>
       <c r="G23">
-        <v>0.0012776578192823657</v>
+        <v>0.0012500570311553977</v>
       </c>
       <c r="H23">
-        <v>-6.5752791562152376e-005</v>
+        <v>-6.6547871275548953e-005</v>
       </c>
       <c r="I23">
-        <v>-3.0154905424974887e-005</v>
+        <v>-3.0681303364604311e-005</v>
       </c>
       <c r="J23">
-        <v>-3.1429110547969569e-005</v>
+        <v>-4.134004719650794e-005</v>
       </c>
       <c r="K23">
-        <v>0.0012894169114943572</v>
+        <v>0.0012965759536112224</v>
       </c>
       <c r="L23">
-        <v>-0.00087222441246262742</v>
+        <v>-0.00087709621284273774</v>
       </c>
       <c r="M23">
-        <v>0.0007216616119481772</v>
+        <v>0.00072513678301753919</v>
       </c>
       <c r="N23">
-        <v>0.0011229311005690121</v>
+        <v>0.0011256431567068272</v>
       </c>
       <c r="O23">
-        <v>0.0047392744176341962</v>
+        <v>0.00471880520951839</v>
       </c>
       <c r="P23">
-        <v>-0.0016076731414765072</v>
+        <v>-0.0016299775716921185</v>
       </c>
       <c r="Q23">
-        <v>0.0089773806356036809</v>
+        <v>0.0089912499719344494</v>
       </c>
       <c r="R23">
-        <v>0.01202524052817433</v>
+        <v>0.012031490949979514</v>
       </c>
       <c r="S23">
-        <v>0.0087158000702584858</v>
+        <v>0.0087195192111342804</v>
       </c>
       <c r="T23">
-        <v>0.0090585285026948594</v>
+        <v>0.0090796609549258153</v>
       </c>
       <c r="U23">
-        <v>0.0080821693311308521</v>
+        <v>0.0080999325576045951</v>
       </c>
       <c r="V23">
-        <v>0.0085131962648552044</v>
+        <v>0.0085593884266802998</v>
       </c>
       <c r="W23">
-        <v>0.0087064667318983019</v>
+        <v>0.0087263727199244912</v>
       </c>
       <c r="X23">
-        <v>0.012410777677851613</v>
+        <v>0.012582688544460714</v>
       </c>
       <c r="Y23">
-        <v>0.0090862835919161451</v>
+        <v>0.0090937445826865734</v>
       </c>
       <c r="Z23">
-        <v>0.0091536237505884886</v>
+        <v>0.0091860794258958739</v>
       </c>
       <c r="AA23">
-        <v>0.0095084361350526638</v>
+        <v>0.0095099944799868011</v>
       </c>
       <c r="AB23">
-        <v>2.9535052134611319e-005</v>
+        <v>3.0082766915205455e-005</v>
       </c>
       <c r="AC23">
-        <v>-0.00063040660518152818</v>
+        <v>-0.00060861918659635113</v>
       </c>
       <c r="AD23">
-        <v>-0.00044830533209034911</v>
+        <v>-0.00043219941928339736</v>
       </c>
       <c r="AE23">
-        <v>0.0033379055743041927</v>
+        <v>0.0033791902485964852</v>
       </c>
       <c r="AF23">
-        <v>0.021950521843265722</v>
+        <v>0.021949440093433907</v>
       </c>
       <c r="AG23">
-        <v>0.0017281570354513356</v>
+        <v>0.0016420319603991543</v>
       </c>
       <c r="AH23">
-        <v>-0.013064084833337</v>
+        <v>-0.012537249224095021</v>
       </c>
     </row>
     <row r="24">
@@ -2914,103 +2917,103 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>0.23627610045932984</v>
+        <v>0.2293094856927996</v>
       </c>
       <c r="C24">
-        <v>-0.0012029536687807746</v>
+        <v>-0.0011614333715447708</v>
       </c>
       <c r="D24">
-        <v>0.0002419916374485423</v>
+        <v>0.00022742005357321432</v>
       </c>
       <c r="E24">
-        <v>-2.3368852439077182e-006</v>
+        <v>-2.2392598663084477e-006</v>
       </c>
       <c r="F24">
-        <v>0.0017337842293381077</v>
+        <v>0.0017502671913798978</v>
       </c>
       <c r="G24">
-        <v>0.0011113993454440962</v>
+        <v>0.0010840893212601536</v>
       </c>
       <c r="H24">
-        <v>-7.1502558393846618e-005</v>
+        <v>-7.2590005614538925e-005</v>
       </c>
       <c r="I24">
-        <v>-3.1306668815971953e-005</v>
+        <v>-3.2401057453457197e-005</v>
       </c>
       <c r="J24">
-        <v>0.00029756224487297554</v>
+        <v>0.00030256220723831433</v>
       </c>
       <c r="K24">
-        <v>0.0020648885878674743</v>
+        <v>0.0020974415751864976</v>
       </c>
       <c r="L24">
-        <v>-0.00021856463567221721</v>
+        <v>-0.00023091163573465013</v>
       </c>
       <c r="M24">
-        <v>0.00098612231806366902</v>
+        <v>0.0010010173519954353</v>
       </c>
       <c r="N24">
-        <v>0.0013446081250018602</v>
+        <v>0.001362299134006496</v>
       </c>
       <c r="O24">
-        <v>0.0049851303247434794</v>
+        <v>0.0049570218174363589</v>
       </c>
       <c r="P24">
-        <v>-0.0023205645084261334</v>
+        <v>-0.0023684915857274521</v>
       </c>
       <c r="Q24">
-        <v>0.008804808177287321</v>
+        <v>0.0087842592744820421</v>
       </c>
       <c r="R24">
-        <v>0.011870620532578998</v>
+        <v>0.011823294663066334</v>
       </c>
       <c r="S24">
-        <v>0.0085625338330146995</v>
+        <v>0.008546995349838736</v>
       </c>
       <c r="T24">
-        <v>0.0089336617462161625</v>
+        <v>0.0089297023710487346</v>
       </c>
       <c r="U24">
-        <v>0.0078746817836951814</v>
+        <v>0.0078663495401524383</v>
       </c>
       <c r="V24">
-        <v>0.0083792524259059045</v>
+        <v>0.0084039496213739826</v>
       </c>
       <c r="W24">
-        <v>0.0085424447697488026</v>
+        <v>0.0085306322110856106</v>
       </c>
       <c r="X24">
-        <v>0.0090862835919161451</v>
+        <v>0.0090937445826865734</v>
       </c>
       <c r="Y24">
-        <v>0.014184107828490625</v>
+        <v>0.014266779607128419</v>
       </c>
       <c r="Z24">
-        <v>0.008998554974331505</v>
+        <v>0.00901096233728833</v>
       </c>
       <c r="AA24">
-        <v>0.0093874522557453426</v>
+        <v>0.0093735944319363416</v>
       </c>
       <c r="AB24">
-        <v>6.818559688207145e-005</v>
+        <v>6.7147721322252619e-005</v>
       </c>
       <c r="AC24">
-        <v>-0.00077158390625835498</v>
+        <v>-0.00074690819442095688</v>
       </c>
       <c r="AD24">
-        <v>-0.00026437257025990063</v>
+        <v>-0.00022033927013885134</v>
       </c>
       <c r="AE24">
-        <v>0.0031303116867919946</v>
+        <v>0.0031595714632937357</v>
       </c>
       <c r="AF24">
-        <v>0.021522883047474725</v>
+        <v>0.021380737566154787</v>
       </c>
       <c r="AG24">
-        <v>0.0012765458465733232</v>
+        <v>0.0012204157632128604</v>
       </c>
       <c r="AH24">
-        <v>-0.01375684904388897</v>
+        <v>-0.013123495862244171</v>
       </c>
     </row>
     <row r="25">
@@ -3018,103 +3021,103 @@
         <v>39</v>
       </c>
       <c r="B25">
-        <v>0.12547677479830174</v>
+        <v>0.13741935489191337</v>
       </c>
       <c r="C25">
-        <v>-0.0012696358973717128</v>
+        <v>-0.0012249991792923562</v>
       </c>
       <c r="D25">
-        <v>0.0002018661999080365</v>
+        <v>0.00019214793354959542</v>
       </c>
       <c r="E25">
-        <v>-1.6745406098061188e-006</v>
+        <v>-1.6148000120130043e-006</v>
       </c>
       <c r="F25">
-        <v>0.0015005973632072228</v>
+        <v>0.0014903046442211864</v>
       </c>
       <c r="G25">
-        <v>0.0011640497673458096</v>
+        <v>0.0011387451358837071</v>
       </c>
       <c r="H25">
-        <v>-6.6562227124323977e-005</v>
+        <v>-6.9044194975464822e-005</v>
       </c>
       <c r="I25">
-        <v>-2.8200401075967056e-005</v>
+        <v>-2.8728158133201981e-005</v>
       </c>
       <c r="J25">
-        <v>0.00011721754681596683</v>
+        <v>0.00014507101567056736</v>
       </c>
       <c r="K25">
-        <v>0.0012435662337985237</v>
+        <v>0.001289816876460053</v>
       </c>
       <c r="L25">
-        <v>-0.00058302623406248245</v>
+        <v>-0.00058363907789705464</v>
       </c>
       <c r="M25">
-        <v>0.00057370392540132681</v>
+        <v>0.00060840625022605746</v>
       </c>
       <c r="N25">
-        <v>0.00095035372269357959</v>
+        <v>0.00098301849700627338</v>
       </c>
       <c r="O25">
-        <v>0.0043684391398301145</v>
+        <v>0.0044140177512378333</v>
       </c>
       <c r="P25">
-        <v>-0.001815047162828101</v>
+        <v>-0.0018724375429985248</v>
       </c>
       <c r="Q25">
-        <v>0.0089473005451822518</v>
+        <v>0.0089666734127294128</v>
       </c>
       <c r="R25">
-        <v>0.011894128707734463</v>
+        <v>0.011906488608960587</v>
       </c>
       <c r="S25">
-        <v>0.0086982243194381921</v>
+        <v>0.0087146935578089578</v>
       </c>
       <c r="T25">
-        <v>0.0090220954611212548</v>
+        <v>0.0090523164493679052</v>
       </c>
       <c r="U25">
-        <v>0.007994618366927022</v>
+        <v>0.0080194259064245797</v>
       </c>
       <c r="V25">
-        <v>0.0084767744662138829</v>
+        <v>0.0085322311087242756</v>
       </c>
       <c r="W25">
-        <v>0.0086296860438483287</v>
+        <v>0.0086540406312121329</v>
       </c>
       <c r="X25">
-        <v>0.0091536237505884886</v>
+        <v>0.0091860794258958739</v>
       </c>
       <c r="Y25">
-        <v>0.008998554974331505</v>
+        <v>0.00901096233728833</v>
       </c>
       <c r="Z25">
-        <v>0.01253606332211985</v>
+        <v>0.012547895097530386</v>
       </c>
       <c r="AA25">
-        <v>0.0094262713510005584</v>
+        <v>0.009336832061081872</v>
       </c>
       <c r="AB25">
-        <v>5.1368921463455655e-005</v>
+        <v>4.8601686065693735e-005</v>
       </c>
       <c r="AC25">
-        <v>-0.00058944714262951139</v>
+        <v>-0.00050459283227512934</v>
       </c>
       <c r="AD25">
-        <v>-0.00024496550387139056</v>
+        <v>-0.00021723139196046671</v>
       </c>
       <c r="AE25">
-        <v>0.0031968349241189584</v>
+        <v>0.0032384956945321862</v>
       </c>
       <c r="AF25">
-        <v>0.02141720139106619</v>
+        <v>0.02141195474291404</v>
       </c>
       <c r="AG25">
-        <v>0.0019764439580982622</v>
+        <v>0.0019460401187529688</v>
       </c>
       <c r="AH25">
-        <v>-0.013329572803080374</v>
+        <v>-0.012842634515539495</v>
       </c>
     </row>
     <row r="26">
@@ -3122,103 +3125,103 @@
         <v>40</v>
       </c>
       <c r="B26">
-        <v>-0.010081366701971852</v>
+        <v>0.09113124820965067</v>
       </c>
       <c r="C26">
-        <v>-0.0013049396121498627</v>
+        <v>-0.00076383403049597003</v>
       </c>
       <c r="D26">
-        <v>0.0002354384379023057</v>
+        <v>0.00010339785869942913</v>
       </c>
       <c r="E26">
-        <v>-2.0653474351856711e-006</v>
+        <v>-1.1530581094514351e-006</v>
       </c>
       <c r="F26">
-        <v>0.0017652699745315682</v>
+        <v>0.0020919809217895286</v>
       </c>
       <c r="G26">
-        <v>0.0010530299387262443</v>
+        <v>0.00062501823023430685</v>
       </c>
       <c r="H26">
-        <v>-7.1446983365581042e-005</v>
+        <v>-8.3551933869536037e-005</v>
       </c>
       <c r="I26">
-        <v>-3.2663576085892628e-005</v>
+        <v>-5.1641255890111471e-005</v>
       </c>
       <c r="J26">
-        <v>3.9340367327285464e-005</v>
+        <v>0.00029511794419327143</v>
       </c>
       <c r="K26">
-        <v>0.0012135917085831661</v>
+        <v>0.00094623897970569359</v>
       </c>
       <c r="L26">
-        <v>-0.00080385573704642955</v>
+        <v>-0.0014329705759947844</v>
       </c>
       <c r="M26">
-        <v>0.00053580282559772966</v>
+        <v>-1.1198313090052606e-005</v>
       </c>
       <c r="N26">
-        <v>0.0011291507480810621</v>
+        <v>0.00056322843189569871</v>
       </c>
       <c r="O26">
-        <v>0.0048157892808533284</v>
+        <v>0.0041347556970880491</v>
       </c>
       <c r="P26">
-        <v>-0.0020488255113744647</v>
+        <v>-0.0018284355101627035</v>
       </c>
       <c r="Q26">
-        <v>0.009205031423763629</v>
+        <v>0.0091152761538063325</v>
       </c>
       <c r="R26">
-        <v>0.012545731900847099</v>
+        <v>0.012389215922052992</v>
       </c>
       <c r="S26">
-        <v>0.0089432727769642121</v>
+        <v>0.0088718148999862891</v>
       </c>
       <c r="T26">
-        <v>0.0093464410830742216</v>
+        <v>0.0092788070255344305</v>
       </c>
       <c r="U26">
-        <v>0.0082109669940288663</v>
+        <v>0.0081321525518787564</v>
       </c>
       <c r="V26">
-        <v>0.0086954607747426749</v>
+        <v>0.008738544750882175</v>
       </c>
       <c r="W26">
-        <v>0.008970751455051551</v>
+        <v>0.0089739555029591609</v>
       </c>
       <c r="X26">
-        <v>0.0095084361350526638</v>
+        <v>0.0095099944799868011</v>
       </c>
       <c r="Y26">
-        <v>0.0093874522557453426</v>
+        <v>0.0093735944319363416</v>
       </c>
       <c r="Z26">
-        <v>0.0094262713510005584</v>
+        <v>0.009336832061081872</v>
       </c>
       <c r="AA26">
-        <v>0.013173749031890164</v>
+        <v>0.018429165285640349</v>
       </c>
       <c r="AB26">
-        <v>4.7136437917664727e-005</v>
+        <v>0.00012213332277693362</v>
       </c>
       <c r="AC26">
-        <v>-0.00084209343436258098</v>
+        <v>-0.0012132201252129078</v>
       </c>
       <c r="AD26">
-        <v>-0.00058922531025555787</v>
+        <v>-0.0011286571029210466</v>
       </c>
       <c r="AE26">
-        <v>0.0034915983954540543</v>
+        <v>0.0036191500832948569</v>
       </c>
       <c r="AF26">
-        <v>0.023365360667963166</v>
+        <v>0.022839675793075276</v>
       </c>
       <c r="AG26">
-        <v>0.0021327735263069201</v>
+        <v>0.0017713941572887403</v>
       </c>
       <c r="AH26">
-        <v>-0.013726776836336364</v>
+        <v>-0.0087284983230286814</v>
       </c>
     </row>
     <row r="27">
@@ -3226,103 +3229,103 @@
         <v>41</v>
       </c>
       <c r="B27">
-        <v>-0.017301022165564513</v>
+        <v>-0.016375314759421059</v>
       </c>
       <c r="C27">
-        <v>-1.0837861626690709e-005</v>
+        <v>-4.8573611273204685e-006</v>
       </c>
       <c r="D27">
-        <v>-6.3558936205868055e-006</v>
+        <v>-7.6627498660202659e-006</v>
       </c>
       <c r="E27">
-        <v>-7.1470426814859407e-009</v>
+        <v>3.2748816361093287e-009</v>
       </c>
       <c r="F27">
-        <v>3.1309100577320867e-005</v>
+        <v>3.5848400819587806e-005</v>
       </c>
       <c r="G27">
-        <v>5.694834711565558e-005</v>
+        <v>5.1210280682712145e-005</v>
       </c>
       <c r="H27">
-        <v>-8.1645105238659646e-007</v>
+        <v>-1.0073425169862895e-006</v>
       </c>
       <c r="I27">
-        <v>1.5297573586457972e-006</v>
+        <v>1.341448928771049e-006</v>
       </c>
       <c r="J27">
-        <v>6.8203794438068035e-005</v>
+        <v>6.8971472579786638e-005</v>
       </c>
       <c r="K27">
-        <v>-3.4244604967317675e-005</v>
+        <v>-3.7619499609088496e-005</v>
       </c>
       <c r="L27">
-        <v>4.432464497316959e-005</v>
+        <v>3.9903478823300875e-005</v>
       </c>
       <c r="M27">
-        <v>-3.4328722333352773e-005</v>
+        <v>-3.8332909936400397e-005</v>
       </c>
       <c r="N27">
-        <v>-5.9135188897123077e-005</v>
+        <v>-6.322045254284858e-005</v>
       </c>
       <c r="O27">
-        <v>3.390097998296317e-005</v>
+        <v>2.7354484483296197e-005</v>
       </c>
       <c r="P27">
-        <v>-6.2284167361647885e-005</v>
+        <v>-5.6782142819483466e-005</v>
       </c>
       <c r="Q27">
-        <v>3.0831965482488598e-005</v>
+        <v>2.7597326924099202e-005</v>
       </c>
       <c r="R27">
-        <v>0.00016871306860602388</v>
+        <v>0.00016233642999001073</v>
       </c>
       <c r="S27">
-        <v>2.3182877259147333e-005</v>
+        <v>2.2288423146303452e-005</v>
       </c>
       <c r="T27">
-        <v>4.5157096031500773e-005</v>
+        <v>4.3108872346140888e-005</v>
       </c>
       <c r="U27">
-        <v>9.4632973192917188e-006</v>
+        <v>1.5008214711442584e-005</v>
       </c>
       <c r="V27">
-        <v>3.4197688344012674e-005</v>
+        <v>3.4755112106159671e-005</v>
       </c>
       <c r="W27">
-        <v>3.6481387675536955e-005</v>
+        <v>3.4905993906154216e-005</v>
       </c>
       <c r="X27">
-        <v>2.9535052134611319e-005</v>
+        <v>3.0082766915205455e-005</v>
       </c>
       <c r="Y27">
-        <v>6.818559688207145e-005</v>
+        <v>6.7147721322252619e-005</v>
       </c>
       <c r="Z27">
-        <v>5.1368921463455655e-005</v>
+        <v>4.8601686065693735e-005</v>
       </c>
       <c r="AA27">
-        <v>4.7136437917664727e-005</v>
+        <v>0.00012213332277693362</v>
       </c>
       <c r="AB27">
-        <v>3.5505053951462275e-005</v>
+        <v>3.6175584646658734e-005</v>
       </c>
       <c r="AC27">
-        <v>-0.00014348204910188424</v>
+        <v>-0.00014737211756652785</v>
       </c>
       <c r="AD27">
-        <v>-0.00016563651021283442</v>
+        <v>-0.00017098155680536634</v>
       </c>
       <c r="AE27">
-        <v>-3.7562965777752751e-005</v>
+        <v>-3.620247333635079e-005</v>
       </c>
       <c r="AF27">
-        <v>0.00060449033596020395</v>
+        <v>0.00058805082859496316</v>
       </c>
       <c r="AG27">
-        <v>-3.8087857627298354e-006</v>
+        <v>-8.7350637835837396e-006</v>
       </c>
       <c r="AH27">
-        <v>-0.00025993279583076288</v>
+        <v>-0.0002122885250034933</v>
       </c>
     </row>
     <row r="28">
@@ -3330,103 +3333,103 @@
         <v>42</v>
       </c>
       <c r="B28">
-        <v>-0.11528568553283262</v>
+        <v>-0.1052951030089934</v>
       </c>
       <c r="C28">
-        <v>0.00020769286537899762</v>
+        <v>0.00016564790831333394</v>
       </c>
       <c r="D28">
-        <v>-4.0861739681288117e-005</v>
+        <v>-6.2915257272328634e-005</v>
       </c>
       <c r="E28">
-        <v>4.1900366571780514e-007</v>
+        <v>5.9240493379726514e-007</v>
       </c>
       <c r="F28">
-        <v>-0.00013298564714476807</v>
+        <v>-0.00018710326232145697</v>
       </c>
       <c r="G28">
-        <v>-7.7838087593856751e-005</v>
+        <v>-7.4405674213434475e-005</v>
       </c>
       <c r="H28">
-        <v>1.3799175931375203e-005</v>
+        <v>1.3133144856997245e-005</v>
       </c>
       <c r="I28">
-        <v>2.5734666512751886e-006</v>
+        <v>3.7435135247499801e-006</v>
       </c>
       <c r="J28">
-        <v>3.0286637043717285e-005</v>
+        <v>2.0365020453267171e-005</v>
       </c>
       <c r="K28">
-        <v>0.00024969659377241209</v>
+        <v>0.0002425105784918842</v>
       </c>
       <c r="L28">
-        <v>-0.0001081662740168637</v>
+        <v>-0.00013441061572493041</v>
       </c>
       <c r="M28">
-        <v>0.00042182770516867567</v>
+        <v>0.00039491453755743401</v>
       </c>
       <c r="N28">
-        <v>0.00050957952120194577</v>
+        <v>0.00049785346587575066</v>
       </c>
       <c r="O28">
-        <v>-0.00020927582428525125</v>
+        <v>-0.00020327894263164753</v>
       </c>
       <c r="P28">
-        <v>0.00064173792130792304</v>
+        <v>0.00056465180211935032</v>
       </c>
       <c r="Q28">
-        <v>-0.00061133373139175308</v>
+        <v>-0.00059094316174897838</v>
       </c>
       <c r="R28">
-        <v>-0.0015532990440511401</v>
+        <v>-0.001522242615115345</v>
       </c>
       <c r="S28">
-        <v>-0.00031360940995009282</v>
+        <v>-0.00034140819334361767</v>
       </c>
       <c r="T28">
-        <v>-0.00067196870663709671</v>
+        <v>-0.00063878496559814039</v>
       </c>
       <c r="U28">
-        <v>-4.8071714685039672e-005</v>
+        <v>-6.9585107433313594e-005</v>
       </c>
       <c r="V28">
-        <v>-0.00047170876806799282</v>
+        <v>-0.00045802014421133684</v>
       </c>
       <c r="W28">
-        <v>-0.00057980136222328957</v>
+        <v>-0.00053361324755466216</v>
       </c>
       <c r="X28">
-        <v>-0.00063040660518152818</v>
+        <v>-0.00060861918659635113</v>
       </c>
       <c r="Y28">
-        <v>-0.00077158390625835498</v>
+        <v>-0.00074690819442095688</v>
       </c>
       <c r="Z28">
-        <v>-0.00058944714262951139</v>
+        <v>-0.00050459283227512934</v>
       </c>
       <c r="AA28">
-        <v>-0.00084209343436258098</v>
+        <v>-0.0012132201252129078</v>
       </c>
       <c r="AB28">
-        <v>-0.00014348204910188424</v>
+        <v>-0.00014737211756652785</v>
       </c>
       <c r="AC28">
-        <v>0.0060489397999333441</v>
+        <v>0.0059920471835851995</v>
       </c>
       <c r="AD28">
-        <v>0.0011255298286859774</v>
+        <v>0.0011504325337428779</v>
       </c>
       <c r="AE28">
-        <v>4.5237584353519919e-005</v>
+        <v>5.745267140447083e-005</v>
       </c>
       <c r="AF28">
-        <v>-0.0046163417644467797</v>
+        <v>-0.0045750805548109424</v>
       </c>
       <c r="AG28">
-        <v>-0.00011740461382006116</v>
+        <v>-4.7263477844284653e-005</v>
       </c>
       <c r="AH28">
-        <v>0.0024192873633175644</v>
+        <v>0.0032139889691205669</v>
       </c>
     </row>
     <row r="29">
@@ -3434,103 +3437,103 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>-0.011539015250630284</v>
+        <v>-0.026689484910023837</v>
       </c>
       <c r="C29">
-        <v>0.00028285768138087476</v>
+        <v>0.00020477687701145266</v>
       </c>
       <c r="D29">
-        <v>7.7681341943691695e-007</v>
+        <v>-8.3291934343046603e-006</v>
       </c>
       <c r="E29">
-        <v>-4.8021962463094987e-008</v>
+        <v>2.3104758815428814e-008</v>
       </c>
       <c r="F29">
-        <v>-9.0621451984107624e-005</v>
+        <v>-0.00011999236476008452</v>
       </c>
       <c r="G29">
-        <v>0.00013103166652587701</v>
+        <v>0.00020963647012249478</v>
       </c>
       <c r="H29">
-        <v>1.1788040590183195e-005</v>
+        <v>1.3482190978086173e-005</v>
       </c>
       <c r="I29">
-        <v>-6.4819221573405e-007</v>
+        <v>9.2191196015677795e-007</v>
       </c>
       <c r="J29">
-        <v>0.00049079255918923169</v>
+        <v>0.0004645467348695833</v>
       </c>
       <c r="K29">
-        <v>0.00050336235269359333</v>
+        <v>0.00048964008701457909</v>
       </c>
       <c r="L29">
-        <v>-2.018571901147171e-005</v>
+        <v>4.5915408693277676e-005</v>
       </c>
       <c r="M29">
-        <v>0.0004898049848146846</v>
+        <v>0.00054097880569752791</v>
       </c>
       <c r="N29">
-        <v>0.00061444039903969534</v>
+        <v>0.00069399055150901404</v>
       </c>
       <c r="O29">
-        <v>-0.00014234426927734779</v>
+        <v>-4.3574259696491091e-005</v>
       </c>
       <c r="P29">
-        <v>0.00051835601033677937</v>
+        <v>0.00051581357157254488</v>
       </c>
       <c r="Q29">
-        <v>-0.00018762069956654087</v>
+        <v>-0.0001330654733918404</v>
       </c>
       <c r="R29">
-        <v>-0.0013019315159191807</v>
+        <v>-0.0012373644160117835</v>
       </c>
       <c r="S29">
-        <v>0.00019241120015423517</v>
+        <v>0.00017778054945115536</v>
       </c>
       <c r="T29">
-        <v>-0.00062754395268585419</v>
+        <v>-0.00060311079026196786</v>
       </c>
       <c r="U29">
-        <v>-0.00014633647626009424</v>
+        <v>-0.00018372963733182066</v>
       </c>
       <c r="V29">
-        <v>-5.2651086661682951e-005</v>
+        <v>-2.8126417894573826e-005</v>
       </c>
       <c r="W29">
-        <v>-0.00047629088870295355</v>
+        <v>-0.00044848674161436638</v>
       </c>
       <c r="X29">
-        <v>-0.00044830533209034911</v>
+        <v>-0.00043219941928339736</v>
       </c>
       <c r="Y29">
-        <v>-0.00026437257025990063</v>
+        <v>-0.00022033927013885134</v>
       </c>
       <c r="Z29">
-        <v>-0.00024496550387139056</v>
+        <v>-0.00021723139196046671</v>
       </c>
       <c r="AA29">
-        <v>-0.00058922531025555787</v>
+        <v>-0.0011286571029210466</v>
       </c>
       <c r="AB29">
-        <v>-0.00016563651021283442</v>
+        <v>-0.00017098155680536634</v>
       </c>
       <c r="AC29">
-        <v>0.0011255298286859774</v>
+        <v>0.0011504325337428779</v>
       </c>
       <c r="AD29">
-        <v>0.0056598352489327375</v>
+        <v>0.0058288669722099187</v>
       </c>
       <c r="AE29">
-        <v>3.5904037690984245e-005</v>
+        <v>-6.7399075294537853e-005</v>
       </c>
       <c r="AF29">
-        <v>-0.0047396072240183662</v>
+        <v>-0.0046124187742254477</v>
       </c>
       <c r="AG29">
-        <v>8.4532128964650763e-005</v>
+        <v>0.00015067442613239432</v>
       </c>
       <c r="AH29">
-        <v>0.0015961599921914746</v>
+        <v>0.0017901144137356453</v>
       </c>
     </row>
     <row r="30">
@@ -3538,103 +3541,103 @@
         <v>44</v>
       </c>
       <c r="B30">
-        <v>-0.13245458692188261</v>
+        <v>-0.16404981170361674</v>
       </c>
       <c r="C30">
-        <v>-0.00023457975492527968</v>
+        <v>-0.00020770196617954243</v>
       </c>
       <c r="D30">
-        <v>-0.00019995005730219159</v>
+        <v>-0.00022987420629791422</v>
       </c>
       <c r="E30">
-        <v>1.8416255608731604e-006</v>
+        <v>2.0589366338626049e-006</v>
       </c>
       <c r="F30">
-        <v>0.00058694872452894596</v>
+        <v>0.00062365683926954925</v>
       </c>
       <c r="G30">
-        <v>9.2320897361204994e-005</v>
+        <v>0.00010525128930708783</v>
       </c>
       <c r="H30">
-        <v>-2.1357885612250776e-005</v>
+        <v>-2.0425349189083405e-005</v>
       </c>
       <c r="I30">
-        <v>-1.8547965668594483e-005</v>
+        <v>-1.8325109982247564e-005</v>
       </c>
       <c r="J30">
-        <v>-0.00010350597873122654</v>
+        <v>-0.00010236073386521785</v>
       </c>
       <c r="K30">
-        <v>-0.00020574904950041405</v>
+        <v>-0.00022052215545302796</v>
       </c>
       <c r="L30">
-        <v>-0.00049334544350259019</v>
+        <v>-0.00053505122811268449</v>
       </c>
       <c r="M30">
-        <v>0.00010409762927640533</v>
+        <v>7.0063799912934918e-005</v>
       </c>
       <c r="N30">
-        <v>0.00030036812255119713</v>
+        <v>0.00026871663783613244</v>
       </c>
       <c r="O30">
-        <v>0.0013181510702984841</v>
+        <v>0.0012673440062318762</v>
       </c>
       <c r="P30">
-        <v>-8.5373684195128637e-005</v>
+        <v>-0.00010233236484238862</v>
       </c>
       <c r="Q30">
-        <v>0.0032216873693846175</v>
+        <v>0.0032543053553938822</v>
       </c>
       <c r="R30">
-        <v>0.0038605855805602671</v>
+        <v>0.0038934851761684352</v>
       </c>
       <c r="S30">
-        <v>0.00314865639819504</v>
+        <v>0.003179388566618575</v>
       </c>
       <c r="T30">
-        <v>0.00299342701996571</v>
+        <v>0.0030237732805300432</v>
       </c>
       <c r="U30">
-        <v>0.0024561704045603992</v>
+        <v>0.0024432313578488505</v>
       </c>
       <c r="V30">
-        <v>0.002762369541897236</v>
+        <v>0.0028257850570295082</v>
       </c>
       <c r="W30">
-        <v>0.0030701358915969129</v>
+        <v>0.0031122143265927089</v>
       </c>
       <c r="X30">
-        <v>0.0033379055743041927</v>
+        <v>0.0033791902485964852</v>
       </c>
       <c r="Y30">
-        <v>0.0031303116867919946</v>
+        <v>0.0031595714632937357</v>
       </c>
       <c r="Z30">
-        <v>0.0031968349241189584</v>
+        <v>0.0032384956945321862</v>
       </c>
       <c r="AA30">
-        <v>0.0034915983954540543</v>
+        <v>0.0036191500832948569</v>
       </c>
       <c r="AB30">
-        <v>-3.7562965777752751e-005</v>
+        <v>-3.620247333635079e-005</v>
       </c>
       <c r="AC30">
-        <v>4.5237584353519919e-005</v>
+        <v>5.745267140447083e-005</v>
       </c>
       <c r="AD30">
-        <v>3.5904037690984245e-005</v>
+        <v>-6.7399075294537853e-005</v>
       </c>
       <c r="AE30">
-        <v>0.0096614607768985353</v>
+        <v>0.00973639231745968</v>
       </c>
       <c r="AF30">
-        <v>0.0073302880920954154</v>
+        <v>0.0073122784514325495</v>
       </c>
       <c r="AG30">
-        <v>0.00092593066054541735</v>
+        <v>0.00091591828632587506</v>
       </c>
       <c r="AH30">
-        <v>0.0040413276908502771</v>
+        <v>0.0049615023110577122</v>
       </c>
     </row>
     <row r="31">
@@ -3642,103 +3645,103 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>0.15780309051619723</v>
+        <v>0.15490014479434369</v>
       </c>
       <c r="C31">
-        <v>-0.0043188796947387226</v>
+        <v>-0.0042528204499786039</v>
       </c>
       <c r="D31">
-        <v>8.3309638002571074e-005</v>
+        <v>8.9560178830605519e-005</v>
       </c>
       <c r="E31">
-        <v>-1.5878217143900503e-006</v>
+        <v>-1.616362332871029e-006</v>
       </c>
       <c r="F31">
-        <v>0.0075775285857005679</v>
+        <v>0.0076051332064854694</v>
       </c>
       <c r="G31">
-        <v>0.0068878668341587606</v>
+        <v>0.0068419731188036279</v>
       </c>
       <c r="H31">
-        <v>-0.00027252299930161919</v>
+        <v>-0.00027453029369290424</v>
       </c>
       <c r="I31">
-        <v>-4.4471930840121049e-005</v>
+        <v>-4.1991523566367898e-005</v>
       </c>
       <c r="J31">
-        <v>-0.00081374103940801135</v>
+        <v>-0.00087972050124497658</v>
       </c>
       <c r="K31">
-        <v>-0.00098769602388937283</v>
+        <v>-0.00085812201510315766</v>
       </c>
       <c r="L31">
-        <v>-0.0019950893497531486</v>
+        <v>-0.001920108174969952</v>
       </c>
       <c r="M31">
-        <v>-0.001281286184342173</v>
+        <v>-0.0010449402298654681</v>
       </c>
       <c r="N31">
-        <v>-0.00098828629553988911</v>
+        <v>-0.0007280852468784238</v>
       </c>
       <c r="O31">
-        <v>0.015616497237342264</v>
+        <v>0.015763465662252951</v>
       </c>
       <c r="P31">
-        <v>-0.0060385525283479166</v>
+        <v>-0.0060385697317993231</v>
       </c>
       <c r="Q31">
-        <v>0.021014660821962704</v>
+        <v>0.020985920751230513</v>
       </c>
       <c r="R31">
-        <v>0.037669316020384661</v>
+        <v>0.037532000438459528</v>
       </c>
       <c r="S31">
-        <v>0.019905540736617506</v>
+        <v>0.019783038964295299</v>
       </c>
       <c r="T31">
-        <v>0.020798059725050666</v>
+        <v>0.020772277039572795</v>
       </c>
       <c r="U31">
-        <v>0.016818532466912884</v>
+        <v>0.016749424720029788</v>
       </c>
       <c r="V31">
-        <v>0.018787680812335873</v>
+        <v>0.018868807345236681</v>
       </c>
       <c r="W31">
-        <v>0.019436020097634517</v>
+        <v>0.019366959854394676</v>
       </c>
       <c r="X31">
-        <v>0.021950521843265722</v>
+        <v>0.021949440093433907</v>
       </c>
       <c r="Y31">
-        <v>0.021522883047474725</v>
+        <v>0.021380737566154787</v>
       </c>
       <c r="Z31">
-        <v>0.02141720139106619</v>
+        <v>0.02141195474291404</v>
       </c>
       <c r="AA31">
-        <v>0.023365360667963166</v>
+        <v>0.022839675793075276</v>
       </c>
       <c r="AB31">
-        <v>0.00060449033596020395</v>
+        <v>0.00058805082859496316</v>
       </c>
       <c r="AC31">
-        <v>-0.0046163417644467797</v>
+        <v>-0.0045750805548109424</v>
       </c>
       <c r="AD31">
-        <v>-0.0047396072240183662</v>
+        <v>-0.0046124187742254477</v>
       </c>
       <c r="AE31">
-        <v>0.0073302880920954154</v>
+        <v>0.0073122784514325495</v>
       </c>
       <c r="AF31">
-        <v>0.10319724627653507</v>
+        <v>0.10324901738318812</v>
       </c>
       <c r="AG31">
-        <v>0.0031882060329019852</v>
+        <v>0.0031250014205897654</v>
       </c>
       <c r="AH31">
-        <v>-0.020455128412633462</v>
+        <v>-0.02060231482171955</v>
       </c>
     </row>
     <row r="32">
@@ -3746,103 +3749,103 @@
         <v>46</v>
       </c>
       <c r="B32">
-        <v>0.050406006448551539</v>
+        <v>0.048205239389574286</v>
       </c>
       <c r="C32">
-        <v>-0.00046669018835589996</v>
+        <v>-0.00047613401370413984</v>
       </c>
       <c r="D32">
-        <v>-3.7550285830118923e-005</v>
+        <v>-3.2768084042065945e-005</v>
       </c>
       <c r="E32">
-        <v>2.0702006994601949e-007</v>
+        <v>1.6358384404463319e-007</v>
       </c>
       <c r="F32">
-        <v>0.00038629382029089918</v>
+        <v>0.00038684777698520909</v>
       </c>
       <c r="G32">
-        <v>0.00050513243106583465</v>
+        <v>0.00052570244195466618</v>
       </c>
       <c r="H32">
-        <v>-1.1968489229544372e-005</v>
+        <v>-1.1501145960016873e-005</v>
       </c>
       <c r="I32">
-        <v>-2.5297699455864014e-006</v>
+        <v>-2.2058161436405055e-006</v>
       </c>
       <c r="J32">
-        <v>0.00052771063862498983</v>
+        <v>0.00053942006835001194</v>
       </c>
       <c r="K32">
-        <v>0.00024197441592081851</v>
+        <v>0.00028076574634784143</v>
       </c>
       <c r="L32">
-        <v>-0.00095763343029728885</v>
+        <v>-0.00096384816120811435</v>
       </c>
       <c r="M32">
-        <v>-0.00067480927845559274</v>
+        <v>-0.00067502637613636664</v>
       </c>
       <c r="N32">
-        <v>-0.00040193203087650835</v>
+        <v>-0.00039519406770707364</v>
       </c>
       <c r="O32">
-        <v>0.00014464836782914422</v>
+        <v>0.0001392365592525401</v>
       </c>
       <c r="P32">
-        <v>-0.00029551308040687632</v>
+        <v>-0.00036435477695407822</v>
       </c>
       <c r="Q32">
-        <v>0.0019943273614936663</v>
+        <v>0.001923505930538397</v>
       </c>
       <c r="R32">
-        <v>0.0021365357945701989</v>
+        <v>0.0020953449363210735</v>
       </c>
       <c r="S32">
-        <v>0.0018563111679848674</v>
+        <v>0.0018357515653340852</v>
       </c>
       <c r="T32">
-        <v>0.0020747033550684245</v>
+        <v>0.0020354251848845708</v>
       </c>
       <c r="U32">
-        <v>0.0014406140864632289</v>
+        <v>0.0013971580225515111</v>
       </c>
       <c r="V32">
-        <v>0.0018136242033043935</v>
+        <v>0.0017769258453250866</v>
       </c>
       <c r="W32">
-        <v>0.0025075037591700171</v>
+        <v>0.0024733326045847134</v>
       </c>
       <c r="X32">
-        <v>0.0017281570354513356</v>
+        <v>0.0016420319603991543</v>
       </c>
       <c r="Y32">
-        <v>0.0012765458465733232</v>
+        <v>0.0012204157632128604</v>
       </c>
       <c r="Z32">
-        <v>0.0019764439580982622</v>
+        <v>0.0019460401187529688</v>
       </c>
       <c r="AA32">
-        <v>0.0021327735263069201</v>
+        <v>0.0017713941572887403</v>
       </c>
       <c r="AB32">
-        <v>-3.8087857627298354e-006</v>
+        <v>-8.7350637835837396e-006</v>
       </c>
       <c r="AC32">
-        <v>-0.00011740461382006116</v>
+        <v>-4.7263477844284653e-005</v>
       </c>
       <c r="AD32">
-        <v>8.4532128964650763e-005</v>
+        <v>0.00015067442613239432</v>
       </c>
       <c r="AE32">
-        <v>0.00092593066054541735</v>
+        <v>0.00091591828632587506</v>
       </c>
       <c r="AF32">
-        <v>0.0031882060329019852</v>
+        <v>0.0031250014205897654</v>
       </c>
       <c r="AG32">
-        <v>0.017464513235543745</v>
+        <v>0.017588570108926321</v>
       </c>
       <c r="AH32">
-        <v>1.0486915204225224e-005</v>
+        <v>-3.3805314656840818e-005</v>
       </c>
     </row>
     <row r="33">
@@ -3850,103 +3853,103 @@
         <v>47</v>
       </c>
       <c r="B33">
-        <v>-19.823325668623607</v>
+        <v>-19.839038298331985</v>
       </c>
       <c r="C33">
-        <v>0.0043810667284545184</v>
+        <v>0.0052508962944459517</v>
       </c>
       <c r="D33">
-        <v>-0.05782008561684393</v>
+        <v>-0.057821831566868792</v>
       </c>
       <c r="E33">
-        <v>0.0004486540895328444</v>
+        <v>0.0004481165238095768</v>
       </c>
       <c r="F33">
-        <v>-0.0021060024442011351</v>
+        <v>-0.001819257928147436</v>
       </c>
       <c r="G33">
-        <v>-0.001022178401688883</v>
+        <v>-0.0019271281527377549</v>
       </c>
       <c r="H33">
-        <v>-0.00016605042849654169</v>
+        <v>-0.00014289522462295205</v>
       </c>
       <c r="I33">
-        <v>-0.00015490633307661469</v>
+        <v>-0.00019698256871113987</v>
       </c>
       <c r="J33">
-        <v>0.0085750512075545987</v>
+        <v>0.0094577726647311899</v>
       </c>
       <c r="K33">
-        <v>-0.033470072417077432</v>
+        <v>-0.03412094008345555</v>
       </c>
       <c r="L33">
-        <v>-0.008934837231091286</v>
+        <v>-0.010667054868792623</v>
       </c>
       <c r="M33">
-        <v>-0.017424527311906225</v>
+        <v>-0.018937269770477341</v>
       </c>
       <c r="N33">
-        <v>-0.019071146873178395</v>
+        <v>-0.020667478881348733</v>
       </c>
       <c r="O33">
-        <v>-0.025086934273075026</v>
+        <v>-0.027016199687477531</v>
       </c>
       <c r="P33">
-        <v>0.0075078597127437932</v>
+        <v>0.0076964253134643376</v>
       </c>
       <c r="Q33">
-        <v>-0.013885936811091605</v>
+        <v>-0.013568023619253699</v>
       </c>
       <c r="R33">
-        <v>-0.016202331294311794</v>
+        <v>-0.016097737061240205</v>
       </c>
       <c r="S33">
-        <v>-0.0092483266386816643</v>
+        <v>-0.0087718687944399049</v>
       </c>
       <c r="T33">
-        <v>-0.0092911804881646021</v>
+        <v>-0.0091502308541321978</v>
       </c>
       <c r="U33">
-        <v>-0.010566928649782013</v>
+        <v>-0.012308891839938624</v>
       </c>
       <c r="V33">
-        <v>-0.01058383665308444</v>
+        <v>-0.010511309422409</v>
       </c>
       <c r="W33">
-        <v>-0.015496873487098994</v>
+        <v>-0.015203458809972654</v>
       </c>
       <c r="X33">
-        <v>-0.013064084833337</v>
+        <v>-0.012537249224095021</v>
       </c>
       <c r="Y33">
-        <v>-0.01375684904388897</v>
+        <v>-0.013123495862244171</v>
       </c>
       <c r="Z33">
-        <v>-0.013329572803080374</v>
+        <v>-0.012842634515539495</v>
       </c>
       <c r="AA33">
-        <v>-0.013726776836336364</v>
+        <v>-0.0087284983230286814</v>
       </c>
       <c r="AB33">
-        <v>-0.00025993279583076288</v>
+        <v>-0.0002122885250034933</v>
       </c>
       <c r="AC33">
-        <v>0.0024192873633175644</v>
+        <v>0.0032139889691205669</v>
       </c>
       <c r="AD33">
-        <v>0.0015961599921914746</v>
+        <v>0.0017901144137356453</v>
       </c>
       <c r="AE33">
-        <v>0.0040413276908502771</v>
+        <v>0.0049615023110577122</v>
       </c>
       <c r="AF33">
-        <v>-0.020455128412633462</v>
+        <v>-0.02060231482171955</v>
       </c>
       <c r="AG33">
-        <v>1.0486915204225224e-005</v>
+        <v>-3.3805314656840818e-005</v>
       </c>
       <c r="AH33">
-        <v>1.8954912622876865</v>
+        <v>1.89851417860989</v>
       </c>
     </row>
   </sheetData>
@@ -3955,7 +3958,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI34"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3999,69 +4002,75 @@
         <v>54</v>
       </c>
       <c r="N1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" t="s">
         <v>25</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>28</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" t="s">
         <v>30</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>31</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>32</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>33</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>34</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>35</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>36</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>37</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>39</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>40</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>41</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>42</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>43</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>44</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>45</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>46</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4070,106 +4079,112 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>-0.027123883502378734</v>
+        <v>-0.01901373101032966</v>
       </c>
       <c r="C2">
-        <v>0.00056518005629362014</v>
+        <v>0.00057855367606914</v>
       </c>
       <c r="D2">
-        <v>8.7380939881536566e-005</v>
+        <v>0.0001026895326093241</v>
       </c>
       <c r="E2">
-        <v>-8.8122933010077735e-007</v>
+        <v>-1.008146329340194e-006</v>
       </c>
       <c r="F2">
-        <v>9.8669861943242597e-006</v>
+        <v>4.4002034543270062e-006</v>
       </c>
       <c r="G2">
-        <v>-3.1248431630102506e-005</v>
+        <v>-5.0608919815431992e-005</v>
       </c>
       <c r="H2">
-        <v>7.0428872444655952e-007</v>
+        <v>1.3940964237422162e-007</v>
       </c>
       <c r="I2">
-        <v>-1.973486725441935e-006</v>
+        <v>-2.4075719510340957e-006</v>
       </c>
       <c r="J2">
-        <v>0.00022484922352210615</v>
+        <v>0.00022797563171173625</v>
       </c>
       <c r="K2">
-        <v>-2.2844699341813612e-005</v>
+        <v>-3.6127163150396867e-005</v>
       </c>
       <c r="L2">
-        <v>0.00018036766291775399</v>
+        <v>0.00021268532048657863</v>
       </c>
       <c r="M2">
-        <v>5.1768047669436076e-005</v>
+        <v>-3.3476014094011131e-005</v>
       </c>
       <c r="N2">
-        <v>0.00017015958197514835</v>
+        <v>6.6372572271286207e-005</v>
       </c>
       <c r="O2">
-        <v>0.0001865180602222728</v>
+        <v>0.0001500312242889139</v>
       </c>
       <c r="P2">
-        <v>0.00016074610518020308</v>
+        <v>0.0001627438276777367</v>
       </c>
       <c r="Q2">
-        <v>0.00016930010338358476</v>
+        <v>0.0001180764192182775</v>
       </c>
       <c r="R2">
-        <v>-0.00012473586403946888</v>
+        <v>0.00012099409863297917</v>
       </c>
       <c r="S2">
-        <v>-0.00013284682717151514</v>
+        <v>-7.8999607762904152e-005</v>
       </c>
       <c r="T2">
-        <v>-0.00012239343187851038</v>
+        <v>-0.00014076749368187677</v>
       </c>
       <c r="U2">
-        <v>-0.00013760207191634155</v>
+        <v>-0.00013668876581117103</v>
       </c>
       <c r="V2">
-        <v>-0.00014185223728625302</v>
+        <v>-0.00012714384213254845</v>
       </c>
       <c r="W2">
-        <v>-8.0901872891486065e-005</v>
+        <v>-0.00014837370158889449</v>
       </c>
       <c r="X2">
-        <v>-8.9067750073194873e-005</v>
+        <v>-0.00013961418687945167</v>
       </c>
       <c r="Y2">
-        <v>-0.0001033904007670533</v>
+        <v>-7.9415749256403012e-005</v>
       </c>
       <c r="Z2">
-        <v>-0.00010718512696077554</v>
+        <v>-9.1012630208759813e-005</v>
       </c>
       <c r="AA2">
-        <v>-0.00013965411419945069</v>
+        <v>-0.0001061572727405456</v>
       </c>
       <c r="AB2">
-        <v>-0.00014598009143530755</v>
+        <v>-0.00010874415870808501</v>
       </c>
       <c r="AC2">
-        <v>1.0757101996857092e-005</v>
+        <v>-0.00013981323985725583</v>
       </c>
       <c r="AD2">
-        <v>-1.9125721984950141e-005</v>
+        <v>-0.00014487646141360237</v>
       </c>
       <c r="AE2">
-        <v>-3.5846723578941415e-005</v>
+        <v>1.0162128338978078e-005</v>
       </c>
       <c r="AF2">
-        <v>-0.00012605214527293548</v>
+        <v>-2.3453540408400979e-005</v>
       </c>
       <c r="AG2">
-        <v>-0.00010026604539497815</v>
+        <v>-2.7265291777788837e-005</v>
       </c>
       <c r="AH2">
-        <v>-6.8344389724043749e-005</v>
+        <v>-0.00016849243727414356</v>
       </c>
       <c r="AI2">
-        <v>-0.0026018159234982366</v>
+        <v>-0.00011026528545187288</v>
+      </c>
+      <c r="AJ2">
+        <v>-0.00010897269162518674</v>
+      </c>
+      <c r="AK2">
+        <v>-0.0029490861002779076</v>
       </c>
     </row>
     <row r="3">
@@ -4177,106 +4192,112 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>0.822824195539407</v>
+        <v>0.82256252466445767</v>
       </c>
       <c r="C3">
-        <v>8.7380939881536566e-005</v>
+        <v>0.0001026895326093241</v>
       </c>
       <c r="D3">
-        <v>0.001539040561760816</v>
+        <v>0.001567527050769952</v>
       </c>
       <c r="E3">
-        <v>-1.2418342372525288e-005</v>
+        <v>-1.2652534672863299e-005</v>
       </c>
       <c r="F3">
-        <v>-0.00010437355830106299</v>
+        <v>-9.9640347001503718e-005</v>
       </c>
       <c r="G3">
-        <v>-0.0002591239678506347</v>
+        <v>-0.00026161215203085106</v>
       </c>
       <c r="H3">
-        <v>2.7835071010932845e-006</v>
+        <v>3.2838898665401846e-007</v>
       </c>
       <c r="I3">
-        <v>1.157450647920567e-006</v>
+        <v>-1.4848909779281022e-008</v>
       </c>
       <c r="J3">
-        <v>0.00014497029304615561</v>
+        <v>0.00015074428807907814</v>
       </c>
       <c r="K3">
-        <v>0.00044921896241557771</v>
+        <v>0.00042847209230343361</v>
       </c>
       <c r="L3">
-        <v>0.00010299005829403048</v>
+        <v>0.0001749432507736075</v>
       </c>
       <c r="M3">
-        <v>1.6745291125759977e-005</v>
+        <v>8.7917412043719313e-006</v>
       </c>
       <c r="N3">
-        <v>0.00010810515898117311</v>
+        <v>1.5198222483276552e-005</v>
       </c>
       <c r="O3">
-        <v>3.9408488216551713e-005</v>
+        <v>8.1774750084958724e-005</v>
       </c>
       <c r="P3">
-        <v>-0.00010820770249454098</v>
+        <v>3.19103611081447e-006</v>
       </c>
       <c r="Q3">
-        <v>-4.9795937603351777e-005</v>
+        <v>-0.00015415253388564344</v>
       </c>
       <c r="R3">
-        <v>-0.00012961211520230026</v>
+        <v>-8.774625564149114e-005</v>
       </c>
       <c r="S3">
-        <v>-0.00012853304918095457</v>
+        <v>-0.00023405325425010504</v>
       </c>
       <c r="T3">
-        <v>-0.00013383022617576706</v>
+        <v>-0.00013800979010805334</v>
       </c>
       <c r="U3">
-        <v>-0.00037693048014793545</v>
+        <v>-0.00012911175610285687</v>
       </c>
       <c r="V3">
-        <v>-0.00017356139449096857</v>
+        <v>-0.00013068892299153076</v>
       </c>
       <c r="W3">
-        <v>-0.00021572885910388015</v>
+        <v>-0.00040177895602702901</v>
       </c>
       <c r="X3">
-        <v>-0.0001770721434475736</v>
+        <v>-0.00018408553891208559</v>
       </c>
       <c r="Y3">
-        <v>-0.00020736660551521485</v>
+        <v>-0.00021915515324403417</v>
       </c>
       <c r="Z3">
-        <v>-0.00018340364506168674</v>
+        <v>-0.00017850416467435695</v>
       </c>
       <c r="AA3">
-        <v>-0.00019266912914176273</v>
+        <v>-0.0001997532489986277</v>
       </c>
       <c r="AB3">
-        <v>-0.00015538617020148526</v>
+        <v>-0.00017735663802575727</v>
       </c>
       <c r="AC3">
-        <v>7.4015576265618749e-007</v>
+        <v>-0.00019137172784688961</v>
       </c>
       <c r="AD3">
-        <v>2.203390431719781e-005</v>
+        <v>-0.00015108562566046313</v>
       </c>
       <c r="AE3">
-        <v>8.3007693996061532e-005</v>
+        <v>7.8490127596204939e-008</v>
       </c>
       <c r="AF3">
-        <v>-0.00074931645815612402</v>
+        <v>2.2837210076902432e-005</v>
       </c>
       <c r="AG3">
-        <v>-0.00027093957249027176</v>
+        <v>8.0655170984315471e-005</v>
       </c>
       <c r="AH3">
-        <v>-4.8195586987582681e-005</v>
+        <v>-0.00083373485751388893</v>
       </c>
       <c r="AI3">
-        <v>-0.047356369255036612</v>
+        <v>-0.00027024915224356863</v>
+      </c>
+      <c r="AJ3">
+        <v>-5.6989290483304422e-005</v>
+      </c>
+      <c r="AK3">
+        <v>-0.047990293762680519</v>
       </c>
     </row>
     <row r="4">
@@ -4284,106 +4305,112 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>-0.0061944805266818679</v>
+        <v>-0.0062310959546821266</v>
       </c>
       <c r="C4">
-        <v>-8.8122933010077735e-007</v>
+        <v>-1.008146329340194e-006</v>
       </c>
       <c r="D4">
-        <v>-1.2418342372525288e-005</v>
+        <v>-1.2652534672863299e-005</v>
       </c>
       <c r="E4">
-        <v>1.0103591571231679e-007</v>
+        <v>1.0296347393529226e-007</v>
       </c>
       <c r="F4">
-        <v>8.2334240593729172e-007</v>
+        <v>7.9244808553391628e-007</v>
       </c>
       <c r="G4">
-        <v>1.9925383855494302e-006</v>
+        <v>2.0195718685215132e-006</v>
       </c>
       <c r="H4">
-        <v>-2.2994042667060913e-008</v>
+        <v>-2.9199975623346037e-009</v>
       </c>
       <c r="I4">
-        <v>-1.3670910496434266e-008</v>
+        <v>-4.0179976731923974e-009</v>
       </c>
       <c r="J4">
-        <v>-1.8846728857754397e-006</v>
+        <v>-1.9349634452060479e-006</v>
       </c>
       <c r="K4">
-        <v>-3.8114565113941585e-006</v>
+        <v>-3.639717442113358e-006</v>
       </c>
       <c r="L4">
-        <v>-8.5325597380032608e-007</v>
+        <v>-1.4506675460955997e-006</v>
       </c>
       <c r="M4">
-        <v>-3.9634192200474651e-007</v>
+        <v>-6.6156625567757705e-008</v>
       </c>
       <c r="N4">
-        <v>-9.6940445730978701e-007</v>
+        <v>-3.8191845753683173e-007</v>
       </c>
       <c r="O4">
-        <v>-4.137220546178899e-007</v>
+        <v>-7.5542472612553506e-007</v>
       </c>
       <c r="P4">
-        <v>7.6778152801248484e-007</v>
+        <v>-1.2266057893849688e-007</v>
       </c>
       <c r="Q4">
-        <v>3.6691823874396865e-007</v>
+        <v>1.138755200057927e-006</v>
       </c>
       <c r="R4">
-        <v>1.1362530714181481e-006</v>
+        <v>6.7278402651665877e-007</v>
       </c>
       <c r="S4">
-        <v>1.0844726933027587e-006</v>
+        <v>1.9240756818824229e-006</v>
       </c>
       <c r="T4">
-        <v>1.1177951544081612e-006</v>
+        <v>1.2042883777092285e-006</v>
       </c>
       <c r="U4">
-        <v>2.8987606162927129e-006</v>
+        <v>1.0868317942213334e-006</v>
       </c>
       <c r="V4">
-        <v>1.4818764227324239e-006</v>
+        <v>1.0945138266390468e-006</v>
       </c>
       <c r="W4">
-        <v>1.6941350038803904e-006</v>
+        <v>3.0954933934382882e-006</v>
       </c>
       <c r="X4">
-        <v>1.4068252950084599e-006</v>
+        <v>1.5634587434315458e-006</v>
       </c>
       <c r="Y4">
-        <v>1.6650975828502799e-006</v>
+        <v>1.7206505232030445e-006</v>
       </c>
       <c r="Z4">
-        <v>1.509623669916101e-006</v>
+        <v>1.4212110718511987e-006</v>
       </c>
       <c r="AA4">
-        <v>1.5542170826922819e-006</v>
+        <v>1.6106581665929558e-006</v>
       </c>
       <c r="AB4">
-        <v>1.2942573435059798e-006</v>
+        <v>1.46227999574906e-006</v>
       </c>
       <c r="AC4">
-        <v>-3.7422739852848103e-008</v>
+        <v>1.5439466580096674e-006</v>
       </c>
       <c r="AD4">
-        <v>-1.3769373115040149e-007</v>
+        <v>1.254863071481645e-006</v>
       </c>
       <c r="AE4">
-        <v>-6.1260719670860333e-007</v>
+        <v>-3.2511178059864692e-008</v>
       </c>
       <c r="AF4">
-        <v>5.589360719044956e-006</v>
+        <v>-1.3026563646434655e-007</v>
       </c>
       <c r="AG4">
-        <v>2.2034998496284772e-006</v>
+        <v>-5.8967962369185474e-007</v>
       </c>
       <c r="AH4">
-        <v>2.6661089844656218e-007</v>
+        <v>6.2912148195398807e-006</v>
       </c>
       <c r="AI4">
-        <v>0.00038024744874663393</v>
+        <v>2.2156793995731314e-006</v>
+      </c>
+      <c r="AJ4">
+        <v>3.6316603936619894e-007</v>
+      </c>
+      <c r="AK4">
+        <v>0.00038546273381666102</v>
       </c>
     </row>
     <row r="5">
@@ -4391,106 +4418,112 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>-0.098911932833299104</v>
+        <v>-0.071962484270412491</v>
       </c>
       <c r="C5">
-        <v>9.8669861943242597e-006</v>
+        <v>4.4002034543270062e-006</v>
       </c>
       <c r="D5">
-        <v>-0.00010437355830106299</v>
+        <v>-9.9640347001503718e-005</v>
       </c>
       <c r="E5">
-        <v>8.2334240593729172e-007</v>
+        <v>7.9244808553391628e-007</v>
       </c>
       <c r="F5">
-        <v>0.00072391171111247971</v>
+        <v>0.00073945051175888993</v>
       </c>
       <c r="G5">
-        <v>0.00053822134423225768</v>
+        <v>0.00055453980861260509</v>
       </c>
       <c r="H5">
-        <v>2.3013209138694432e-006</v>
+        <v>2.5418958212364867e-006</v>
       </c>
       <c r="I5">
-        <v>-5.8384245221162787e-007</v>
+        <v>-4.3169787681653082e-007</v>
       </c>
       <c r="J5">
-        <v>2.9155296899198106e-005</v>
+        <v>1.8527315345421448e-005</v>
       </c>
       <c r="K5">
-        <v>-3.3383391527034754e-005</v>
+        <v>-2.3169127920993694e-005</v>
       </c>
       <c r="L5">
-        <v>8.3649583232719815e-006</v>
+        <v>6.6535026404867536e-006</v>
       </c>
       <c r="M5">
-        <v>3.5050795575540456e-005</v>
+        <v>5.7165279475065315e-005</v>
       </c>
       <c r="N5">
-        <v>-2.3990231309877985e-005</v>
+        <v>1.6099549837480738e-005</v>
       </c>
       <c r="O5">
-        <v>-4.1888742458825698e-005</v>
+        <v>-4.7352021801317211e-006</v>
       </c>
       <c r="P5">
-        <v>6.929401069049877e-005</v>
+        <v>-1.3357144647109284e-005</v>
       </c>
       <c r="Q5">
-        <v>0.00014464472701272019</v>
+        <v>0.00012412674466991445</v>
       </c>
       <c r="R5">
-        <v>3.6042376147741174e-005</v>
+        <v>0.0002022333836954617</v>
       </c>
       <c r="S5">
-        <v>8.5320508958536072e-005</v>
+        <v>3.2375781224369877e-005</v>
       </c>
       <c r="T5">
-        <v>8.4648606087088469e-005</v>
+        <v>8.4834912260119003e-006</v>
       </c>
       <c r="U5">
-        <v>0.00013433188380059137</v>
+        <v>6.4646445108757866e-005</v>
       </c>
       <c r="V5">
-        <v>-5.4245227272604511e-006</v>
+        <v>6.6278471360875534e-005</v>
       </c>
       <c r="W5">
-        <v>6.6543972624315387e-005</v>
+        <v>0.000118374498966749</v>
       </c>
       <c r="X5">
-        <v>8.8183666551205946e-005</v>
+        <v>-3.4349306495866385e-005</v>
       </c>
       <c r="Y5">
-        <v>9.9318558468573375e-005</v>
+        <v>4.1107701361967769e-005</v>
       </c>
       <c r="Z5">
-        <v>0.00010175092415343689</v>
+        <v>6.5102817090578182e-005</v>
       </c>
       <c r="AA5">
-        <v>7.8870825370762278e-005</v>
+        <v>7.7103620104843258e-005</v>
       </c>
       <c r="AB5">
-        <v>7.1068503356952722e-005</v>
+        <v>7.673299550181283e-005</v>
       </c>
       <c r="AC5">
-        <v>-1.8121593840954287e-006</v>
+        <v>4.7783851454128991e-005</v>
       </c>
       <c r="AD5">
-        <v>5.8528350047081659e-005</v>
+        <v>4.7056397075119169e-005</v>
       </c>
       <c r="AE5">
-        <v>2.8411545305667394e-005</v>
+        <v>-1.3665483927623599e-006</v>
       </c>
       <c r="AF5">
-        <v>0.00043145831417775506</v>
+        <v>4.5176933080205687e-005</v>
       </c>
       <c r="AG5">
-        <v>0.00022910293064320244</v>
+        <v>1.5171779295661724e-005</v>
       </c>
       <c r="AH5">
-        <v>-7.7062222576483532e-005</v>
+        <v>0.00042789019717566653</v>
       </c>
       <c r="AI5">
-        <v>0.0025595776641213382</v>
+        <v>0.00023798470834860607</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.00010550372288871567</v>
+      </c>
+      <c r="AK5">
+        <v>0.0023108054479232692</v>
       </c>
     </row>
     <row r="6">
@@ -4498,106 +4531,112 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>-0.23755869980806238</v>
+        <v>-0.18756033825249671</v>
       </c>
       <c r="C6">
-        <v>-3.1248431630102506e-005</v>
+        <v>-5.0608919815431992e-005</v>
       </c>
       <c r="D6">
-        <v>-0.0002591239678506347</v>
+        <v>-0.00026161215203085106</v>
       </c>
       <c r="E6">
-        <v>1.9925383855494302e-006</v>
+        <v>2.0195718685215132e-006</v>
       </c>
       <c r="F6">
-        <v>0.00053822134423225768</v>
+        <v>0.00055453980861260509</v>
       </c>
       <c r="G6">
-        <v>0.0012491556306150485</v>
+        <v>0.0012771311909719975</v>
       </c>
       <c r="H6">
-        <v>4.3999166217908349e-006</v>
+        <v>4.9565205230097713e-006</v>
       </c>
       <c r="I6">
-        <v>1.0501180611669626e-006</v>
+        <v>1.2443653186704699e-006</v>
       </c>
       <c r="J6">
-        <v>2.7742463189380527e-005</v>
+        <v>1.2397300677142411e-005</v>
       </c>
       <c r="K6">
-        <v>-5.24323181102271e-005</v>
+        <v>-3.5334043642090387e-005</v>
       </c>
       <c r="L6">
-        <v>-7.7593694837428087e-005</v>
+        <v>-8.5324782116523413e-005</v>
       </c>
       <c r="M6">
-        <v>4.3560780283866677e-005</v>
+        <v>7.8299540956606065e-005</v>
       </c>
       <c r="N6">
-        <v>9.5234366694612192e-005</v>
+        <v>2.167004172672284e-005</v>
       </c>
       <c r="O6">
-        <v>0.00014936693868567976</v>
+        <v>0.00012508816418774191</v>
       </c>
       <c r="P6">
-        <v>0.00038477295305399219</v>
+        <v>0.0002032127963917542</v>
       </c>
       <c r="Q6">
-        <v>0.00044707853810032255</v>
+        <v>0.00047151846429400437</v>
       </c>
       <c r="R6">
-        <v>2.1643841292357836e-005</v>
+        <v>0.0005452979941012728</v>
       </c>
       <c r="S6">
-        <v>9.5504222521322385e-005</v>
+        <v>4.1922976390655809e-005</v>
       </c>
       <c r="T6">
-        <v>5.2768558557704558e-005</v>
+        <v>-2.0190861864260307e-005</v>
       </c>
       <c r="U6">
-        <v>0.00028624811553237871</v>
+        <v>6.3468463752193287e-005</v>
       </c>
       <c r="V6">
-        <v>-3.5641432288625896e-006</v>
+        <v>2.8008209233265473e-005</v>
       </c>
       <c r="W6">
-        <v>5.9824845184296453e-005</v>
+        <v>0.00026445483340923866</v>
       </c>
       <c r="X6">
-        <v>9.859275953512164e-005</v>
+        <v>-3.6329161594594081e-005</v>
       </c>
       <c r="Y6">
-        <v>0.00015529750680132984</v>
+        <v>3.011028794305435e-005</v>
       </c>
       <c r="Z6">
-        <v>8.5181963887258892e-005</v>
+        <v>6.2594767561201248e-005</v>
       </c>
       <c r="AA6">
-        <v>0.00012011072769537259</v>
+        <v>0.00012476559147287685</v>
       </c>
       <c r="AB6">
-        <v>5.3935616309982179e-005</v>
+        <v>5.6895061844752467e-005</v>
       </c>
       <c r="AC6">
-        <v>1.4922882402936991e-005</v>
+        <v>8.2262188763483949e-005</v>
       </c>
       <c r="AD6">
-        <v>2.8686236698006182e-005</v>
+        <v>2.2916174841617416e-005</v>
       </c>
       <c r="AE6">
-        <v>-3.5427229237905823e-005</v>
+        <v>1.5195564765366641e-005</v>
       </c>
       <c r="AF6">
-        <v>0.00094744247891125348</v>
+        <v>1.5078396633681066e-005</v>
       </c>
       <c r="AG6">
-        <v>0.00025333760111095015</v>
+        <v>-5.2653986414924316e-005</v>
       </c>
       <c r="AH6">
-        <v>-1.2690624718594606e-005</v>
+        <v>0.00092952403707881239</v>
       </c>
       <c r="AI6">
-        <v>0.0068555571938108597</v>
+        <v>0.00025544460762169348</v>
+      </c>
+      <c r="AJ6">
+        <v>-4.6184744436537808e-005</v>
+      </c>
+      <c r="AK6">
+        <v>0.0067893510814081952</v>
       </c>
     </row>
     <row r="7">
@@ -4605,106 +4644,112 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>0.00065231320143568894</v>
+        <v>-0.00036417009746713357</v>
       </c>
       <c r="C7">
-        <v>7.0428872444655952e-007</v>
+        <v>1.3940964237422162e-007</v>
       </c>
       <c r="D7">
-        <v>2.7835071010932845e-006</v>
+        <v>3.2838898665401846e-007</v>
       </c>
       <c r="E7">
-        <v>-2.2994042667060913e-008</v>
+        <v>-2.9199975623346037e-009</v>
       </c>
       <c r="F7">
-        <v>2.3013209138694432e-006</v>
+        <v>2.5418958212364867e-006</v>
       </c>
       <c r="G7">
-        <v>4.3999166217908349e-006</v>
+        <v>4.9565205230097713e-006</v>
       </c>
       <c r="H7">
-        <v>1.3381054027168557e-006</v>
+        <v>1.5725693770662504e-006</v>
       </c>
       <c r="I7">
-        <v>4.462400639624753e-010</v>
+        <v>1.0634739702069093e-007</v>
       </c>
       <c r="J7">
-        <v>9.2288536126733528e-007</v>
+        <v>2.7208257071696722e-007</v>
       </c>
       <c r="K7">
-        <v>-4.2433995597963834e-006</v>
+        <v>-2.5142369465606676e-006</v>
       </c>
       <c r="L7">
-        <v>1.2677878351608129e-005</v>
+        <v>5.9161855622901538e-006</v>
       </c>
       <c r="M7">
-        <v>6.2326136668041761e-007</v>
+        <v>-2.0336531362796326e-006</v>
       </c>
       <c r="N7">
-        <v>-1.7638143299715796e-006</v>
+        <v>1.2341773283920544e-006</v>
       </c>
       <c r="O7">
-        <v>-1.033448668602293e-006</v>
+        <v>1.34008376161417e-006</v>
       </c>
       <c r="P7">
-        <v>-1.4012815480891663e-006</v>
+        <v>2.5667475584841711e-006</v>
       </c>
       <c r="Q7">
-        <v>-4.6207985294992716e-006</v>
+        <v>3.1330688131292449e-006</v>
       </c>
       <c r="R7">
-        <v>3.417718297771426e-006</v>
+        <v>-1.0842198061939254e-006</v>
       </c>
       <c r="S7">
-        <v>2.0047565096316481e-006</v>
+        <v>2.2168626291516049e-005</v>
       </c>
       <c r="T7">
-        <v>1.5288537335830988e-006</v>
+        <v>4.2094297733758499e-006</v>
       </c>
       <c r="U7">
-        <v>4.3100539056203792e-006</v>
+        <v>2.5762402972119962e-006</v>
       </c>
       <c r="V7">
-        <v>7.9112014952082538e-007</v>
+        <v>1.6621315743166329e-006</v>
       </c>
       <c r="W7">
-        <v>1.2528941564498989e-007</v>
+        <v>6.2493865846285919e-006</v>
       </c>
       <c r="X7">
-        <v>-4.3669573867337254e-007</v>
+        <v>1.6992154877552626e-006</v>
       </c>
       <c r="Y7">
-        <v>6.3556457574389931e-007</v>
+        <v>3.2024434566479227e-007</v>
       </c>
       <c r="Z7">
-        <v>1.1027372775355493e-006</v>
+        <v>-2.864511432750579e-007</v>
       </c>
       <c r="AA7">
-        <v>7.5869502460215634e-007</v>
+        <v>6.8239239650322097e-007</v>
       </c>
       <c r="AB7">
-        <v>4.6284250450050082e-007</v>
+        <v>9.8633617700483363e-007</v>
       </c>
       <c r="AC7">
-        <v>4.9584317198554442e-007</v>
+        <v>3.3446114646777333e-007</v>
       </c>
       <c r="AD7">
-        <v>-6.6556787565047945e-007</v>
+        <v>-2.3231426097495688e-007</v>
       </c>
       <c r="AE7">
-        <v>-1.5239124116388125e-006</v>
+        <v>4.9097869274816836e-007</v>
       </c>
       <c r="AF7">
-        <v>9.8812600891750463e-006</v>
+        <v>-4.9007674781459265e-007</v>
       </c>
       <c r="AG7">
-        <v>-2.0139276771387023e-006</v>
+        <v>-1.0194135377096504e-006</v>
       </c>
       <c r="AH7">
-        <v>-3.8906844382527288e-006</v>
+        <v>1.8140153537579785e-005</v>
       </c>
       <c r="AI7">
-        <v>-0.00016045622788399711</v>
+        <v>-1.4376216278117864e-006</v>
+      </c>
+      <c r="AJ7">
+        <v>-3.1762043045340701e-006</v>
+      </c>
+      <c r="AK7">
+        <v>-0.00010677581451937798</v>
       </c>
     </row>
     <row r="8">
@@ -4712,106 +4757,112 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>0.00099004176943802121</v>
+        <v>0.00054314256151540279</v>
       </c>
       <c r="C8">
-        <v>-1.973486725441935e-006</v>
+        <v>-2.4075719510340957e-006</v>
       </c>
       <c r="D8">
-        <v>1.157450647920567e-006</v>
+        <v>-1.4848909779281022e-008</v>
       </c>
       <c r="E8">
-        <v>-1.3670910496434266e-008</v>
+        <v>-4.0179976731923974e-009</v>
       </c>
       <c r="F8">
-        <v>-5.8384245221162787e-007</v>
+        <v>-4.3169787681653082e-007</v>
       </c>
       <c r="G8">
-        <v>1.0501180611669626e-006</v>
+        <v>1.2443653186704699e-006</v>
       </c>
       <c r="H8">
-        <v>4.462400639624753e-010</v>
+        <v>1.0634739702069093e-007</v>
       </c>
       <c r="I8">
-        <v>1.8256470917123219e-006</v>
+        <v>1.8809729432746954e-006</v>
       </c>
       <c r="J8">
-        <v>5.0493078644099913e-007</v>
+        <v>1.1761910565441183e-007</v>
       </c>
       <c r="K8">
-        <v>-3.210106072602492e-006</v>
+        <v>-1.8838158885153887e-006</v>
       </c>
       <c r="L8">
-        <v>9.1884181527844632e-006</v>
+        <v>5.8287792716727549e-006</v>
       </c>
       <c r="M8">
-        <v>-1.0141561532141217e-006</v>
+        <v>-1.0892889210006935e-006</v>
       </c>
       <c r="N8">
-        <v>-1.8092789006474185e-006</v>
+        <v>-8.6443179241310163e-007</v>
       </c>
       <c r="O8">
-        <v>-3.2577223790174533e-006</v>
+        <v>-2.3437022820491319e-007</v>
       </c>
       <c r="P8">
-        <v>-4.3737762733021622e-006</v>
+        <v>-1.2268116491959967e-006</v>
       </c>
       <c r="Q8">
-        <v>-6.416611085955022e-006</v>
+        <v>-1.9197576394821566e-006</v>
       </c>
       <c r="R8">
-        <v>-1.6493818058706827e-006</v>
+        <v>-4.718261160033589e-006</v>
       </c>
       <c r="S8">
-        <v>-4.9220095449921072e-007</v>
+        <v>1.0319359679861464e-005</v>
       </c>
       <c r="T8">
-        <v>-1.5301729357961093e-006</v>
+        <v>-1.3386246033057558e-006</v>
       </c>
       <c r="U8">
-        <v>5.5041403622002141e-006</v>
+        <v>4.9063744253384007e-007</v>
       </c>
       <c r="V8">
-        <v>-1.8718837537051952e-006</v>
+        <v>-1.1274124815514831e-006</v>
       </c>
       <c r="W8">
-        <v>-3.8379733825500155e-006</v>
+        <v>7.5110763818905227e-006</v>
       </c>
       <c r="X8">
-        <v>-2.2857895989284666e-006</v>
+        <v>-9.0576174486004253e-007</v>
       </c>
       <c r="Y8">
-        <v>-2.9715102029703082e-006</v>
+        <v>-3.0332340447509221e-006</v>
       </c>
       <c r="Z8">
-        <v>7.8645614953344448e-007</v>
+        <v>-1.51026731611473e-006</v>
       </c>
       <c r="AA8">
-        <v>-1.4623334001327517e-006</v>
+        <v>-2.3193086197211918e-006</v>
       </c>
       <c r="AB8">
-        <v>-2.7048146629664061e-006</v>
+        <v>1.3339695296634032e-006</v>
       </c>
       <c r="AC8">
-        <v>8.5152924257893961e-007</v>
+        <v>-7.5960542783472788e-007</v>
       </c>
       <c r="AD8">
-        <v>-7.1992948288189141e-008</v>
+        <v>-2.5852090172695465e-006</v>
       </c>
       <c r="AE8">
-        <v>-6.5460525714277075e-007</v>
+        <v>8.369742555848611e-007</v>
       </c>
       <c r="AF8">
-        <v>1.7844018055202611e-005</v>
+        <v>1.3910729597229638e-007</v>
       </c>
       <c r="AG8">
-        <v>-2.0515068257652869e-006</v>
+        <v>-1.626799172442547e-007</v>
       </c>
       <c r="AH8">
-        <v>2.7878766389719569e-006</v>
+        <v>2.2607428132705593e-005</v>
       </c>
       <c r="AI8">
-        <v>-0.00012066156077618898</v>
+        <v>-2.2315121399743223e-006</v>
+      </c>
+      <c r="AJ8">
+        <v>5.7675289488952577e-006</v>
+      </c>
+      <c r="AK8">
+        <v>-9.5657141478404373e-005</v>
       </c>
     </row>
     <row r="9">
@@ -4819,106 +4870,112 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>0.50413546804019083</v>
+        <v>0.53066151700602748</v>
       </c>
       <c r="C9">
-        <v>0.00022484922352210615</v>
+        <v>0.00022797563171173625</v>
       </c>
       <c r="D9">
-        <v>0.00014497029304615561</v>
+        <v>0.00015074428807907814</v>
       </c>
       <c r="E9">
-        <v>-1.8846728857754397e-006</v>
+        <v>-1.9349634452060479e-006</v>
       </c>
       <c r="F9">
-        <v>2.9155296899198106e-005</v>
+        <v>1.8527315345421448e-005</v>
       </c>
       <c r="G9">
-        <v>2.7742463189380527e-005</v>
+        <v>1.2397300677142411e-005</v>
       </c>
       <c r="H9">
-        <v>9.2288536126733528e-007</v>
+        <v>2.7208257071696722e-007</v>
       </c>
       <c r="I9">
-        <v>5.0493078644099913e-007</v>
+        <v>1.1761910565441183e-007</v>
       </c>
       <c r="J9">
-        <v>0.0014954809686691716</v>
+        <v>0.0015012083188285757</v>
       </c>
       <c r="K9">
-        <v>-0.00049573040948672285</v>
+        <v>-0.00050227633906987966</v>
       </c>
       <c r="L9">
-        <v>0.00031450390483039946</v>
+        <v>0.00033483680608175612</v>
       </c>
       <c r="M9">
-        <v>-8.8742274613608273e-005</v>
+        <v>-1.3003580127849429e-005</v>
       </c>
       <c r="N9">
-        <v>0.00010414494020706627</v>
+        <v>-8.3740730874562011e-005</v>
       </c>
       <c r="O9">
-        <v>8.0986599275678344e-005</v>
+        <v>0.00010544629590651459</v>
       </c>
       <c r="P9">
-        <v>0.00011736641837806008</v>
+        <v>7.7749149916322673e-005</v>
       </c>
       <c r="Q9">
-        <v>0.00011510227382623115</v>
+        <v>0.00010345135674760862</v>
       </c>
       <c r="R9">
-        <v>3.5547247414538866e-005</v>
+        <v>9.9000694178825473e-005</v>
       </c>
       <c r="S9">
-        <v>2.6655314361790608e-005</v>
+        <v>-6.6622054521533894e-005</v>
       </c>
       <c r="T9">
-        <v>3.8749848492285253e-005</v>
+        <v>3.882683491167392e-005</v>
       </c>
       <c r="U9">
-        <v>0.00011470057251645804</v>
+        <v>2.9191038006409352e-005</v>
       </c>
       <c r="V9">
-        <v>1.6513891884790098e-005</v>
+        <v>3.4304499260704802e-005</v>
       </c>
       <c r="W9">
-        <v>8.3396757667501126e-005</v>
+        <v>0.0001191258776018779</v>
       </c>
       <c r="X9">
-        <v>5.0983675350075772e-005</v>
+        <v>2.8717874604741321e-005</v>
       </c>
       <c r="Y9">
-        <v>5.2192697499616283e-005</v>
+        <v>8.5722453964595939e-005</v>
       </c>
       <c r="Z9">
-        <v>3.2200966735094561e-005</v>
+        <v>4.765347992586981e-005</v>
       </c>
       <c r="AA9">
-        <v>7.4201247151035291e-005</v>
+        <v>4.9357137702018498e-005</v>
       </c>
       <c r="AB9">
-        <v>3.0037009563946108e-005</v>
+        <v>3.7810867106729835e-005</v>
       </c>
       <c r="AC9">
-        <v>3.24274352044204e-005</v>
+        <v>7.2013749749916017e-005</v>
       </c>
       <c r="AD9">
-        <v>4.8386266530427537e-006</v>
+        <v>3.2203629062025523e-005</v>
       </c>
       <c r="AE9">
-        <v>-2.5157208389153975e-005</v>
+        <v>3.2893393993980844e-005</v>
       </c>
       <c r="AF9">
-        <v>0.00019538804627333164</v>
+        <v>-6.7645972862828024e-006</v>
       </c>
       <c r="AG9">
-        <v>1.4181185925644935e-005</v>
+        <v>-3.1980213818294872e-005</v>
       </c>
       <c r="AH9">
-        <v>-3.136951976794207e-006</v>
+        <v>0.00014749057540722308</v>
       </c>
       <c r="AI9">
-        <v>-0.0031361455917476035</v>
+        <v>-1.1640705395844862e-005</v>
+      </c>
+      <c r="AJ9">
+        <v>-6.1074970152520105e-005</v>
+      </c>
+      <c r="AK9">
+        <v>-0.0032316150663422136</v>
       </c>
     </row>
     <row r="10">
@@ -4926,106 +4983,112 @@
         <v>53</v>
       </c>
       <c r="B10">
-        <v>0.51599076049359927</v>
+        <v>0.5236562176187064</v>
       </c>
       <c r="C10">
-        <v>-2.2844699341813612e-005</v>
+        <v>-3.6127163150396867e-005</v>
       </c>
       <c r="D10">
-        <v>0.00044921896241557771</v>
+        <v>0.00042847209230343361</v>
       </c>
       <c r="E10">
-        <v>-3.8114565113941585e-006</v>
+        <v>-3.639717442113358e-006</v>
       </c>
       <c r="F10">
-        <v>-3.3383391527034754e-005</v>
+        <v>-2.3169127920993694e-005</v>
       </c>
       <c r="G10">
-        <v>-5.24323181102271e-005</v>
+        <v>-3.5334043642090387e-005</v>
       </c>
       <c r="H10">
-        <v>-4.2433995597963834e-006</v>
+        <v>-2.5142369465606676e-006</v>
       </c>
       <c r="I10">
-        <v>-3.210106072602492e-006</v>
+        <v>-1.8838158885153887e-006</v>
       </c>
       <c r="J10">
-        <v>-0.00049573040948672285</v>
+        <v>-0.00050227633906987966</v>
       </c>
       <c r="K10">
-        <v>0.0042619755788999188</v>
+        <v>0.0042707620770000513</v>
       </c>
       <c r="L10">
-        <v>-0.0012131374485708445</v>
+        <v>-0.0012499233549150921</v>
       </c>
       <c r="M10">
-        <v>6.5845888895060156e-005</v>
+        <v>2.7185690264145096e-005</v>
       </c>
       <c r="N10">
-        <v>-0.00024413245925431924</v>
+        <v>4.2044293673498327e-005</v>
       </c>
       <c r="O10">
-        <v>-0.00018650156686627175</v>
+        <v>-0.0002228827317367081</v>
       </c>
       <c r="P10">
-        <v>-0.0002621087189666868</v>
+        <v>-0.0001520535101863737</v>
       </c>
       <c r="Q10">
-        <v>-0.00034714773505726258</v>
+        <v>-0.00019739396594225221</v>
       </c>
       <c r="R10">
-        <v>6.1944220602377052e-005</v>
+        <v>-0.00027887613640673633</v>
       </c>
       <c r="S10">
-        <v>-6.0499985665909452e-005</v>
+        <v>0.00018185199231155282</v>
       </c>
       <c r="T10">
-        <v>-5.0562373627803699e-005</v>
+        <v>8.8171849764416554e-005</v>
       </c>
       <c r="U10">
-        <v>3.7266536009045084e-005</v>
+        <v>-4.4218989795487273e-005</v>
       </c>
       <c r="V10">
-        <v>-1.0313951203637199e-005</v>
+        <v>-2.4626665145160119e-005</v>
       </c>
       <c r="W10">
-        <v>5.8910943560204487e-006</v>
+        <v>6.4951568678874114e-005</v>
       </c>
       <c r="X10">
-        <v>-2.4207415427884849e-006</v>
+        <v>-1.4630701368773674e-005</v>
       </c>
       <c r="Y10">
-        <v>-1.3800391551015145e-006</v>
+        <v>2.51605504856681e-005</v>
       </c>
       <c r="Z10">
-        <v>2.9056553107347644e-005</v>
+        <v>1.1722927100996268e-005</v>
       </c>
       <c r="AA10">
-        <v>2.9081518428253697e-005</v>
+        <v>1.8441950736204291e-005</v>
       </c>
       <c r="AB10">
-        <v>-0.00011855490676589142</v>
+        <v>3.0336478610223233e-005</v>
       </c>
       <c r="AC10">
-        <v>8.2794383970707409e-006</v>
+        <v>3.4194373802697541e-005</v>
       </c>
       <c r="AD10">
-        <v>5.1943963856602212e-006</v>
+        <v>-0.00012523633482637402</v>
       </c>
       <c r="AE10">
-        <v>6.0870941943884903e-005</v>
+        <v>6.7686322227449545e-006</v>
       </c>
       <c r="AF10">
-        <v>0.00028131380842008787</v>
+        <v>1.1182533078298723e-005</v>
       </c>
       <c r="AG10">
-        <v>-9.1159538738705068e-005</v>
+        <v>9.2664659280258539e-005</v>
       </c>
       <c r="AH10">
-        <v>0.00021094883279077978</v>
+        <v>0.00033231486574715995</v>
       </c>
       <c r="AI10">
-        <v>-0.012405799874938707</v>
+        <v>-7.7980453200177102e-005</v>
+      </c>
+      <c r="AJ10">
+        <v>0.00024653306091413328</v>
+      </c>
+      <c r="AK10">
+        <v>-0.011995536506347854</v>
       </c>
     </row>
     <row r="11">
@@ -5033,106 +5096,112 @@
         <v>24</v>
       </c>
       <c r="B11">
-        <v>0.5373207978498945</v>
+        <v>0.61574466111473847</v>
       </c>
       <c r="C11">
-        <v>0.00018036766291775399</v>
+        <v>0.00021268532048657863</v>
       </c>
       <c r="D11">
-        <v>0.00010299005829403048</v>
+        <v>0.0001749432507736075</v>
       </c>
       <c r="E11">
-        <v>-8.5325597380032608e-007</v>
+        <v>-1.4506675460955997e-006</v>
       </c>
       <c r="F11">
-        <v>8.3649583232719815e-006</v>
+        <v>6.6535026404867536e-006</v>
       </c>
       <c r="G11">
-        <v>-7.7593694837428087e-005</v>
+        <v>-8.5324782116523413e-005</v>
       </c>
       <c r="H11">
-        <v>1.2677878351608129e-005</v>
+        <v>5.9161855622901538e-006</v>
       </c>
       <c r="I11">
-        <v>9.1884181527844632e-006</v>
+        <v>5.8287792716727549e-006</v>
       </c>
       <c r="J11">
-        <v>0.00031450390483039946</v>
+        <v>0.00033483680608175612</v>
       </c>
       <c r="K11">
-        <v>-0.0012131374485708445</v>
+        <v>-0.0012499233549150921</v>
       </c>
       <c r="L11">
-        <v>0.0017887056584688079</v>
+        <v>0.0019501108060936676</v>
       </c>
       <c r="M11">
-        <v>7.6211431268606241e-005</v>
+        <v>0.00012104456289233355</v>
       </c>
       <c r="N11">
-        <v>0.00047243706719711449</v>
+        <v>2.9029789988330363e-005</v>
       </c>
       <c r="O11">
-        <v>0.0009198770556651147</v>
+        <v>0.00043966024066323785</v>
       </c>
       <c r="P11">
-        <v>0.0010646970291754135</v>
+        <v>0.00087804091176139172</v>
       </c>
       <c r="Q11">
-        <v>0.0011626397619998918</v>
+        <v>0.00098636302361785168</v>
       </c>
       <c r="R11">
-        <v>-0.00023784900976675386</v>
+        <v>0.0011165517307033235</v>
       </c>
       <c r="S11">
-        <v>-7.2289437977537171e-005</v>
+        <v>-0.00060349552476584819</v>
       </c>
       <c r="T11">
-        <v>-8.5941907597138472e-005</v>
+        <v>-0.00030723825526723231</v>
       </c>
       <c r="U11">
-        <v>-0.00017366086447253453</v>
+        <v>-0.00012995938998674669</v>
       </c>
       <c r="V11">
-        <v>-0.00010503336607094898</v>
+        <v>-0.00014625030057526228</v>
       </c>
       <c r="W11">
-        <v>-0.00015664228510992983</v>
+        <v>-0.00028454128640589924</v>
       </c>
       <c r="X11">
-        <v>-0.000162348371194743</v>
+        <v>-0.00014913357607569027</v>
       </c>
       <c r="Y11">
-        <v>-0.00011882902009951925</v>
+        <v>-0.0002192357688889637</v>
       </c>
       <c r="Z11">
-        <v>-0.00013471596579144301</v>
+        <v>-0.00022545123333635175</v>
       </c>
       <c r="AA11">
-        <v>-0.00020670628322890959</v>
+        <v>-0.00016942530092480153</v>
       </c>
       <c r="AB11">
-        <v>-0.00012210270485595292</v>
+        <v>-0.00017605170800144565</v>
       </c>
       <c r="AC11">
-        <v>6.2810062800766273e-006</v>
+        <v>-0.00024402787920398778</v>
       </c>
       <c r="AD11">
-        <v>-3.5715038406500276e-005</v>
+        <v>-0.00015217333784082847</v>
       </c>
       <c r="AE11">
-        <v>-2.3392753837021217e-005</v>
+        <v>6.2210124049624132e-006</v>
       </c>
       <c r="AF11">
-        <v>-0.00053246665431641148</v>
+        <v>-4.1269067807895286e-005</v>
       </c>
       <c r="AG11">
-        <v>-0.00010553471583823418</v>
+        <v>-4.542638416967583e-005</v>
       </c>
       <c r="AH11">
-        <v>-0.00041212219826475033</v>
+        <v>-0.00078044436726910828</v>
       </c>
       <c r="AI11">
-        <v>-0.0056018039096679215</v>
+        <v>-0.00014083739086847517</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.00054224554898046418</v>
+      </c>
+      <c r="AK11">
+        <v>-0.0071665992587352234</v>
       </c>
     </row>
     <row r="12">
@@ -5140,2460 +5209,2824 @@
         <v>54</v>
       </c>
       <c r="B12">
-        <v>0.16254733062698279</v>
+        <v>0.32592073721252457</v>
       </c>
       <c r="C12">
-        <v>5.1768047669436076e-005</v>
+        <v>-3.3476014094011131e-005</v>
       </c>
       <c r="D12">
-        <v>1.6745291125759977e-005</v>
+        <v>8.7917412043719313e-006</v>
       </c>
       <c r="E12">
-        <v>-3.9634192200474651e-007</v>
+        <v>-6.6156625567757705e-008</v>
       </c>
       <c r="F12">
-        <v>3.5050795575540456e-005</v>
+        <v>5.7165279475065315e-005</v>
       </c>
       <c r="G12">
-        <v>4.3560780283866677e-005</v>
+        <v>7.8299540956606065e-005</v>
       </c>
       <c r="H12">
-        <v>6.2326136668041761e-007</v>
+        <v>-2.0336531362796326e-006</v>
       </c>
       <c r="I12">
-        <v>-1.0141561532141217e-006</v>
+        <v>-1.0892889210006935e-006</v>
       </c>
       <c r="J12">
-        <v>-8.8742274613608273e-005</v>
+        <v>-1.3003580127849429e-005</v>
       </c>
       <c r="K12">
-        <v>6.5845888895060156e-005</v>
+        <v>2.7185690264145096e-005</v>
       </c>
       <c r="L12">
-        <v>7.6211431268606241e-005</v>
+        <v>0.00012104456289233355</v>
       </c>
       <c r="M12">
-        <v>0.00080983833381268009</v>
+        <v>0.00077651967695976248</v>
       </c>
       <c r="N12">
-        <v>-8.9886767466042499e-005</v>
+        <v>-0.00027221834312236869</v>
       </c>
       <c r="O12">
-        <v>-7.4364411024950534e-006</v>
+        <v>0.00026123441047042479</v>
       </c>
       <c r="P12">
-        <v>9.6819141114994143e-005</v>
+        <v>0.00042458341760226854</v>
       </c>
       <c r="Q12">
-        <v>0.00013093655569822613</v>
+        <v>0.00058956115966741563</v>
       </c>
       <c r="R12">
-        <v>1.1944816037371417e-005</v>
+        <v>0.00071975703391031728</v>
       </c>
       <c r="S12">
-        <v>-4.8993215194675525e-006</v>
+        <v>-4.2202537117885874e-005</v>
       </c>
       <c r="T12">
-        <v>4.2320152643338373e-005</v>
+        <v>-0.00013811153794394612</v>
       </c>
       <c r="U12">
-        <v>6.6701574437604279e-005</v>
+        <v>-0.00011524769736950371</v>
       </c>
       <c r="V12">
-        <v>-2.1915267383472876e-005</v>
+        <v>-0.00011007560033896198</v>
       </c>
       <c r="W12">
-        <v>1.8236164385261635e-005</v>
+        <v>-0.00018552773687463046</v>
       </c>
       <c r="X12">
-        <v>1.9360840316061192e-005</v>
+        <v>-0.00010414758561621744</v>
       </c>
       <c r="Y12">
-        <v>-1.0445026162038016e-005</v>
+        <v>-0.00011102932411283324</v>
       </c>
       <c r="Z12">
-        <v>-1.6710313691300685e-005</v>
+        <v>-0.00012523563364044555</v>
       </c>
       <c r="AA12">
-        <v>1.9775638306248196e-005</v>
+        <v>-9.3759870109040057e-005</v>
       </c>
       <c r="AB12">
-        <v>5.1618479677651433e-005</v>
+        <v>-0.00012689619076027277</v>
       </c>
       <c r="AC12">
-        <v>1.1190321824007842e-005</v>
+        <v>-0.00013581781385477477</v>
       </c>
       <c r="AD12">
-        <v>-2.9150621036744221e-005</v>
+        <v>-0.000164133149487915</v>
       </c>
       <c r="AE12">
-        <v>-5.561860396686106e-006</v>
+        <v>-6.8730494535539602e-006</v>
       </c>
       <c r="AF12">
-        <v>2.6264724935737082e-005</v>
+        <v>1.8514119337445652e-005</v>
       </c>
       <c r="AG12">
-        <v>-3.0109652078284875e-005</v>
+        <v>-3.2029852000093111e-005</v>
       </c>
       <c r="AH12">
-        <v>0.00010664136150301574</v>
+        <v>-0.00043101120499286797</v>
       </c>
       <c r="AI12">
-        <v>-9.0842652349912745e-005</v>
+        <v>7.3520470893190639e-007</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.00016500221787909191</v>
+      </c>
+      <c r="AK12">
+        <v>-0.00074034499519242173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B13">
-        <v>0.018304477148311907</v>
+        <v>0.062798697014280355</v>
       </c>
       <c r="C13">
-        <v>0.00017015958197514835</v>
+        <v>6.6372572271286207e-005</v>
       </c>
       <c r="D13">
-        <v>0.00010810515898117311</v>
+        <v>1.5198222483276552e-005</v>
       </c>
       <c r="E13">
-        <v>-9.6940445730978701e-007</v>
+        <v>-3.8191845753683173e-007</v>
       </c>
       <c r="F13">
-        <v>-2.3990231309877985e-005</v>
+        <v>1.6099549837480738e-005</v>
       </c>
       <c r="G13">
-        <v>9.5234366694612192e-005</v>
+        <v>2.167004172672284e-005</v>
       </c>
       <c r="H13">
-        <v>-1.7638143299715796e-006</v>
+        <v>1.2341773283920544e-006</v>
       </c>
       <c r="I13">
-        <v>-1.8092789006474185e-006</v>
+        <v>-8.6443179241310163e-007</v>
       </c>
       <c r="J13">
-        <v>0.00010414494020706627</v>
+        <v>-8.3740730874562011e-005</v>
       </c>
       <c r="K13">
-        <v>-0.00024413245925431924</v>
+        <v>4.2044293673498327e-005</v>
       </c>
       <c r="L13">
-        <v>0.00047243706719711449</v>
+        <v>2.9029789988330363e-005</v>
       </c>
       <c r="M13">
-        <v>-8.9886767466042499e-005</v>
+        <v>-0.00027221834312236869</v>
       </c>
       <c r="N13">
-        <v>0.0044518606069433942</v>
+        <v>0.00090320343275387992</v>
       </c>
       <c r="O13">
-        <v>0.0033244438376233156</v>
+        <v>-0.00018707761538748762</v>
       </c>
       <c r="P13">
-        <v>0.0033802099882491621</v>
+        <v>-0.00017139077040279337</v>
       </c>
       <c r="Q13">
-        <v>0.0033942788092608095</v>
+        <v>-0.00012368857022247462</v>
       </c>
       <c r="R13">
-        <v>-8.5792487571932381e-005</v>
+        <v>-0.00012911378613674</v>
       </c>
       <c r="S13">
-        <v>-6.0514578049949497e-005</v>
+        <v>2.6777805357495636e-005</v>
       </c>
       <c r="T13">
-        <v>2.6334249249960117e-005</v>
+        <v>5.2790524405165431e-005</v>
       </c>
       <c r="U13">
-        <v>-0.0001816198357893783</v>
+        <v>2.4611789095094197e-005</v>
       </c>
       <c r="V13">
-        <v>-7.6548426446733028e-005</v>
+        <v>6.5619370777193057e-005</v>
       </c>
       <c r="W13">
-        <v>-6.4545147024309664e-005</v>
+        <v>0.0001169979279241833</v>
       </c>
       <c r="X13">
-        <v>-6.3330314032122902e-005</v>
+        <v>7.1584492738275133e-006</v>
       </c>
       <c r="Y13">
-        <v>-4.6129710149909586e-005</v>
+        <v>4.1785545165508623e-005</v>
       </c>
       <c r="Z13">
-        <v>-8.7040156537711647e-005</v>
+        <v>5.2478640290093902e-005</v>
       </c>
       <c r="AA13">
-        <v>8.929874682799422e-005</v>
+        <v>3.5417719214549776e-006</v>
       </c>
       <c r="AB13">
-        <v>4.0935214005216516e-005</v>
+        <v>1.5676241696744382e-005</v>
       </c>
       <c r="AC13">
-        <v>-1.4738327642749012e-006</v>
+        <v>5.6823563094016945e-005</v>
       </c>
       <c r="AD13">
-        <v>-5.8656846685189762e-005</v>
+        <v>9.8704348400166324e-005</v>
       </c>
       <c r="AE13">
-        <v>4.8742835585605606e-005</v>
+        <v>1.3348089037231718e-005</v>
       </c>
       <c r="AF13">
-        <v>8.4230186007159136e-005</v>
+        <v>-4.3856560160834948e-005</v>
       </c>
       <c r="AG13">
-        <v>-6.5978869608990243e-005</v>
+        <v>-8.6046620779482732e-008</v>
       </c>
       <c r="AH13">
-        <v>-0.00013058468868706939</v>
+        <v>0.00017930030439288462</v>
       </c>
       <c r="AI13">
-        <v>-0.0062329811192573152</v>
+        <v>-2.8752949195567711e-005</v>
+      </c>
+      <c r="AJ13">
+        <v>0.00016789346649559702</v>
+      </c>
+      <c r="AK13">
+        <v>0.00014817325938999519</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>0.016474994309802829</v>
+        <v>0.12108493865355374</v>
       </c>
       <c r="C14">
-        <v>0.0001865180602222728</v>
+        <v>0.0001500312242889139</v>
       </c>
       <c r="D14">
-        <v>3.9408488216551713e-005</v>
+        <v>8.1774750084958724e-005</v>
       </c>
       <c r="E14">
-        <v>-4.137220546178899e-007</v>
+        <v>-7.5542472612553506e-007</v>
       </c>
       <c r="F14">
-        <v>-4.1888742458825698e-005</v>
+        <v>-4.7352021801317211e-006</v>
       </c>
       <c r="G14">
-        <v>0.00014936693868567976</v>
+        <v>0.00012508816418774191</v>
       </c>
       <c r="H14">
-        <v>-1.033448668602293e-006</v>
+        <v>1.34008376161417e-006</v>
       </c>
       <c r="I14">
-        <v>-3.2577223790174533e-006</v>
+        <v>-2.3437022820491319e-007</v>
       </c>
       <c r="J14">
-        <v>8.0986599275678344e-005</v>
+        <v>0.00010544629590651459</v>
       </c>
       <c r="K14">
-        <v>-0.00018650156686627175</v>
+        <v>-0.0002228827317367081</v>
       </c>
       <c r="L14">
-        <v>0.0009198770556651147</v>
+        <v>0.00043966024066323785</v>
       </c>
       <c r="M14">
-        <v>-7.4364411024950534e-006</v>
+        <v>0.00026123441047042479</v>
       </c>
       <c r="N14">
-        <v>0.0033244438376233156</v>
+        <v>-0.00018707761538748762</v>
       </c>
       <c r="O14">
-        <v>0.004316729711531758</v>
+        <v>0.0045371037515756617</v>
       </c>
       <c r="P14">
-        <v>0.0038214232513860257</v>
+        <v>0.0035129371669255422</v>
       </c>
       <c r="Q14">
-        <v>0.0038592550337984031</v>
+        <v>0.0036413311482099255</v>
       </c>
       <c r="R14">
-        <v>-0.00038465143705119229</v>
+        <v>0.0036842700849785545</v>
       </c>
       <c r="S14">
-        <v>-0.00026145101450957952</v>
+        <v>0.00032140224443571254</v>
       </c>
       <c r="T14">
-        <v>-0.00016998095906175636</v>
+        <v>-9.3641285997161927e-005</v>
       </c>
       <c r="U14">
-        <v>-0.00029351392241655928</v>
+        <v>-9.0858665272306512e-005</v>
       </c>
       <c r="V14">
-        <v>-0.00025242003082682129</v>
+        <v>6.2202904672163922e-006</v>
       </c>
       <c r="W14">
-        <v>-0.00021264213547563166</v>
+        <v>-0.0002099137124137461</v>
       </c>
       <c r="X14">
-        <v>-0.00023429739230048274</v>
+        <v>-9.6796145963695245e-005</v>
       </c>
       <c r="Y14">
-        <v>-0.00019500415995378322</v>
+        <v>-9.5540126501064042e-005</v>
       </c>
       <c r="Z14">
-        <v>-0.00022153838142827164</v>
+        <v>-9.0112602034827637e-005</v>
       </c>
       <c r="AA14">
-        <v>-0.00015710577472179544</v>
+        <v>-6.6994065652757227e-005</v>
       </c>
       <c r="AB14">
-        <v>-7.8498527567157257e-005</v>
+        <v>-0.00011458018415532074</v>
       </c>
       <c r="AC14">
-        <v>2.5655069970472637e-006</v>
+        <v>3.8640425591614843e-005</v>
       </c>
       <c r="AD14">
-        <v>-0.00016959015108934596</v>
+        <v>-1.9091847918614388e-005</v>
       </c>
       <c r="AE14">
-        <v>-7.3456793302783743e-005</v>
+        <v>-3.7604504412725565e-006</v>
       </c>
       <c r="AF14">
-        <v>0.00011297976707745757</v>
+        <v>-6.4192070363883582e-005</v>
       </c>
       <c r="AG14">
-        <v>-9.0994551676016992e-005</v>
+        <v>4.0625830921731403e-005</v>
       </c>
       <c r="AH14">
-        <v>-0.00015113606187354823</v>
+        <v>8.315910487289354e-005</v>
       </c>
       <c r="AI14">
-        <v>-0.0044920274218082732</v>
+        <v>-6.707838256518172e-005</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.0001860429349241795</v>
+      </c>
+      <c r="AK14">
+        <v>-0.0059383850126287184</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15">
-        <v>0.032749366752514601</v>
+        <v>0.20245439514755942</v>
       </c>
       <c r="C15">
-        <v>0.00016074610518020308</v>
+        <v>0.0001627438276777367</v>
       </c>
       <c r="D15">
-        <v>-0.00010820770249454098</v>
+        <v>3.19103611081447e-006</v>
       </c>
       <c r="E15">
-        <v>7.6778152801248484e-007</v>
+        <v>-1.2266057893849688e-007</v>
       </c>
       <c r="F15">
-        <v>6.929401069049877e-005</v>
+        <v>-1.3357144647109284e-005</v>
       </c>
       <c r="G15">
-        <v>0.00038477295305399219</v>
+        <v>0.0002032127963917542</v>
       </c>
       <c r="H15">
-        <v>-1.4012815480891663e-006</v>
+        <v>2.5667475584841711e-006</v>
       </c>
       <c r="I15">
-        <v>-4.3737762733021622e-006</v>
+        <v>-1.2268116491959967e-006</v>
       </c>
       <c r="J15">
-        <v>0.00011736641837806008</v>
+        <v>7.7749149916322673e-005</v>
       </c>
       <c r="K15">
-        <v>-0.0002621087189666868</v>
+        <v>-0.0001520535101863737</v>
       </c>
       <c r="L15">
-        <v>0.0010646970291754135</v>
+        <v>0.00087804091176139172</v>
       </c>
       <c r="M15">
-        <v>9.6819141114994143e-005</v>
+        <v>0.00042458341760226854</v>
       </c>
       <c r="N15">
-        <v>0.0033802099882491621</v>
+        <v>-0.00017139077040279337</v>
       </c>
       <c r="O15">
-        <v>0.0038214232513860257</v>
+        <v>0.0035129371669255422</v>
       </c>
       <c r="P15">
-        <v>0.0045528071449425439</v>
+        <v>0.0046682470964600504</v>
       </c>
       <c r="Q15">
-        <v>0.0041721090164951865</v>
+        <v>0.0042838229952859236</v>
       </c>
       <c r="R15">
-        <v>-0.00013174823901727396</v>
+        <v>0.0043706784446059087</v>
       </c>
       <c r="S15">
-        <v>2.522864768892373e-005</v>
+        <v>0.00049315082723549336</v>
       </c>
       <c r="T15">
-        <v>9.2019164235814877e-005</v>
+        <v>-0.00044232775130330338</v>
       </c>
       <c r="U15">
-        <v>0.00016603667447870818</v>
+        <v>-0.00033371187303885626</v>
       </c>
       <c r="V15">
-        <v>4.3314609607175312e-005</v>
+        <v>-0.00023344381561099439</v>
       </c>
       <c r="W15">
-        <v>2.8709367303298913e-005</v>
+        <v>-0.00037183109864927195</v>
       </c>
       <c r="X15">
-        <v>8.2042663924878668e-006</v>
+        <v>-0.00029485352161907842</v>
       </c>
       <c r="Y15">
-        <v>0.00012255827602129397</v>
+        <v>-0.00028681225117831795</v>
       </c>
       <c r="Z15">
-        <v>4.5074773237518051e-005</v>
+        <v>-0.00030986130662663362</v>
       </c>
       <c r="AA15">
-        <v>0.00013096012647028765</v>
+        <v>-0.00025141624604917731</v>
       </c>
       <c r="AB15">
-        <v>0.00024512405614879936</v>
+        <v>-0.00029485208585204744</v>
       </c>
       <c r="AC15">
-        <v>6.2271597606688663e-006</v>
+        <v>-0.00025312978662154432</v>
       </c>
       <c r="AD15">
-        <v>-0.00016636604617742317</v>
+        <v>-0.0002009896121758217</v>
       </c>
       <c r="AE15">
-        <v>-3.1720818733399424e-005</v>
+        <v>-1.4608143271239646e-006</v>
       </c>
       <c r="AF15">
-        <v>0.0010541385312058471</v>
+        <v>-0.00017809960616802981</v>
       </c>
       <c r="AG15">
-        <v>5.5099331251598277e-005</v>
+        <v>-7.5715752952604267e-005</v>
       </c>
       <c r="AH15">
-        <v>-0.00021124588930835665</v>
+        <v>6.126086069432532e-005</v>
       </c>
       <c r="AI15">
-        <v>-0.00059193638340618738</v>
+        <v>-8.4708434244003348e-005</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.00023942519875688371</v>
+      </c>
+      <c r="AK15">
+        <v>-0.0041149042660478001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>0.16375790091328499</v>
+        <v>0.27561583669022</v>
       </c>
       <c r="C16">
-        <v>0.00016930010338358476</v>
+        <v>0.0001180764192182775</v>
       </c>
       <c r="D16">
-        <v>-4.9795937603351777e-005</v>
+        <v>-0.00015415253388564344</v>
       </c>
       <c r="E16">
-        <v>3.6691823874396865e-007</v>
+        <v>1.138755200057927e-006</v>
       </c>
       <c r="F16">
-        <v>0.00014464472701272019</v>
+        <v>0.00012412674466991445</v>
       </c>
       <c r="G16">
-        <v>0.00044707853810032255</v>
+        <v>0.00047151846429400437</v>
       </c>
       <c r="H16">
-        <v>-4.6207985294992716e-006</v>
+        <v>3.1330688131292449e-006</v>
       </c>
       <c r="I16">
-        <v>-6.416611085955022e-006</v>
+        <v>-1.9197576394821566e-006</v>
       </c>
       <c r="J16">
-        <v>0.00011510227382623115</v>
+        <v>0.00010345135674760862</v>
       </c>
       <c r="K16">
-        <v>-0.00034714773505726258</v>
+        <v>-0.00019739396594225221</v>
       </c>
       <c r="L16">
-        <v>0.0011626397619998918</v>
+        <v>0.00098636302361785168</v>
       </c>
       <c r="M16">
-        <v>0.00013093655569822613</v>
+        <v>0.00058956115966741563</v>
       </c>
       <c r="N16">
-        <v>0.0033942788092608095</v>
+        <v>-0.00012368857022247462</v>
       </c>
       <c r="O16">
-        <v>0.0038592550337984031</v>
+        <v>0.0036413311482099255</v>
       </c>
       <c r="P16">
-        <v>0.0041721090164951865</v>
+        <v>0.0042838229952859236</v>
       </c>
       <c r="Q16">
-        <v>0.0045945610828381622</v>
+        <v>0.0051783515176515808</v>
       </c>
       <c r="R16">
-        <v>-0.00013472121095259044</v>
+        <v>0.0048683648552572062</v>
       </c>
       <c r="S16">
-        <v>4.3145975352665679e-005</v>
+        <v>0.00064543762346347909</v>
       </c>
       <c r="T16">
-        <v>0.00013094767927848043</v>
+        <v>-0.00022300408294189647</v>
       </c>
       <c r="U16">
-        <v>-1.5183794007086527e-005</v>
+        <v>-8.3042309582709154e-005</v>
       </c>
       <c r="V16">
-        <v>6.533630654959998e-005</v>
+        <v>3.0410350107863303e-006</v>
       </c>
       <c r="W16">
-        <v>-2.6812677861626395e-006</v>
+        <v>6.0487965490296834e-005</v>
       </c>
       <c r="X16">
-        <v>-4.8490020366518142e-005</v>
+        <v>-2.9222699179646877e-005</v>
       </c>
       <c r="Y16">
-        <v>9.0918259537705942e-005</v>
+        <v>-7.5020845969721544e-005</v>
       </c>
       <c r="Z16">
-        <v>2.7276838169165273e-005</v>
+        <v>-9.8629989278121153e-005</v>
       </c>
       <c r="AA16">
-        <v>0.00011970838287186578</v>
+        <v>3.4494869863869017e-005</v>
       </c>
       <c r="AB16">
-        <v>0.00023844233614318724</v>
+        <v>-5.8376146036528964e-005</v>
       </c>
       <c r="AC16">
-        <v>4.8605946112651507e-007</v>
+        <v>-7.1926177295426972e-006</v>
       </c>
       <c r="AD16">
-        <v>-0.00013438628429898297</v>
+        <v>8.147210400611467e-005</v>
       </c>
       <c r="AE16">
-        <v>-1.1866144334434186e-005</v>
+        <v>1.3458493275421153e-006</v>
       </c>
       <c r="AF16">
-        <v>0.00036877255136581136</v>
+        <v>-0.00017842705781973516</v>
       </c>
       <c r="AG16">
-        <v>0.00014556421072917406</v>
+        <v>-3.9876368257422124e-005</v>
       </c>
       <c r="AH16">
-        <v>-0.00011434257502930382</v>
+        <v>0.00098969571091831235</v>
       </c>
       <c r="AI16">
-        <v>-0.0024342805204184779</v>
+        <v>6.2118339098118838e-005</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.00031926678645715354</v>
+      </c>
+      <c r="AK16">
+        <v>-0.00015958110675594762</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17">
-        <v>0.24156949430565319</v>
+        <v>0.44594745078483866</v>
       </c>
       <c r="C17">
-        <v>-0.00012473586403946888</v>
+        <v>0.00012099409863297917</v>
       </c>
       <c r="D17">
-        <v>-0.00012961211520230026</v>
+        <v>-8.774625564149114e-005</v>
       </c>
       <c r="E17">
-        <v>1.1362530714181481e-006</v>
+        <v>6.7278402651665877e-007</v>
       </c>
       <c r="F17">
-        <v>3.6042376147741174e-005</v>
+        <v>0.0002022333836954617</v>
       </c>
       <c r="G17">
-        <v>2.1643841292357836e-005</v>
+        <v>0.0005452979941012728</v>
       </c>
       <c r="H17">
-        <v>3.417718297771426e-006</v>
+        <v>-1.0842198061939254e-006</v>
       </c>
       <c r="I17">
-        <v>-1.6493818058706827e-006</v>
+        <v>-4.718261160033589e-006</v>
       </c>
       <c r="J17">
-        <v>3.5547247414538866e-005</v>
+        <v>9.9000694178825473e-005</v>
       </c>
       <c r="K17">
-        <v>6.1944220602377052e-005</v>
+        <v>-0.00027887613640673633</v>
       </c>
       <c r="L17">
-        <v>-0.00023784900976675386</v>
+        <v>0.0011165517307033235</v>
       </c>
       <c r="M17">
-        <v>1.1944816037371417e-005</v>
+        <v>0.00071975703391031728</v>
       </c>
       <c r="N17">
-        <v>-8.5792487571932381e-005</v>
+        <v>-0.00012911378613674</v>
       </c>
       <c r="O17">
-        <v>-0.00038465143705119229</v>
+        <v>0.0036842700849785545</v>
       </c>
       <c r="P17">
-        <v>-0.00013174823901727396</v>
+        <v>0.0043706784446059087</v>
       </c>
       <c r="Q17">
-        <v>-0.00013472121095259044</v>
+        <v>0.0048683648552572062</v>
       </c>
       <c r="R17">
-        <v>0.0054408400399495599</v>
+        <v>0.0053897579116494853</v>
       </c>
       <c r="S17">
-        <v>0.0027613881411792758</v>
+        <v>0.00056217258446161148</v>
       </c>
       <c r="T17">
-        <v>0.0027431853146946995</v>
+        <v>-0.00023614587122211105</v>
       </c>
       <c r="U17">
-        <v>0.0029878914048334735</v>
+        <v>-7.9041762989169855e-005</v>
       </c>
       <c r="V17">
-        <v>0.0027531758203599172</v>
+        <v>2.4091122710191573e-005</v>
       </c>
       <c r="W17">
-        <v>0.0027402145866067375</v>
+        <v>-0.00016248782668856385</v>
       </c>
       <c r="X17">
-        <v>0.0027471697257639314</v>
+        <v>-1.4483381370454778e-005</v>
       </c>
       <c r="Y17">
-        <v>0.0027741932968846457</v>
+        <v>-0.00012548256158406192</v>
       </c>
       <c r="Z17">
-        <v>0.0027847551897491238</v>
+        <v>-0.00017717369935453964</v>
       </c>
       <c r="AA17">
-        <v>0.0027985047459124068</v>
+        <v>-1.378192709660872e-005</v>
       </c>
       <c r="AB17">
-        <v>0.0028203804180448105</v>
+        <v>-9.0813976172197681e-005</v>
       </c>
       <c r="AC17">
-        <v>-2.4872122837802052e-005</v>
+        <v>-2.9188270194577086e-005</v>
       </c>
       <c r="AD17">
-        <v>2.5269982705932326e-007</v>
+        <v>5.378228008637298e-005</v>
       </c>
       <c r="AE17">
-        <v>0.0001579249552385689</v>
+        <v>-6.3393396944794221e-006</v>
       </c>
       <c r="AF17">
-        <v>0.0017304849141529272</v>
+        <v>-0.00013073894500762481</v>
       </c>
       <c r="AG17">
-        <v>0.001353765284608194</v>
+        <v>-3.0022754991559524e-005</v>
       </c>
       <c r="AH17">
-        <v>-0.00019752710633223357</v>
+        <v>0.0002055424646331622</v>
       </c>
       <c r="AI17">
-        <v>0.0014380997370608221</v>
+        <v>0.00016045009566016373</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.00022480670849015123</v>
+      </c>
+      <c r="AK17">
+        <v>-0.0022204445184796136</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18">
-        <v>0.12681577344587083</v>
+        <v>-0.12867559418656024</v>
       </c>
       <c r="C18">
-        <v>-0.00013284682717151514</v>
+        <v>-7.8999607762904152e-005</v>
       </c>
       <c r="D18">
-        <v>-0.00012853304918095457</v>
+        <v>-0.00023405325425010504</v>
       </c>
       <c r="E18">
-        <v>1.0844726933027587e-006</v>
+        <v>1.9240756818824229e-006</v>
       </c>
       <c r="F18">
-        <v>8.5320508958536072e-005</v>
+        <v>3.2375781224369877e-005</v>
       </c>
       <c r="G18">
-        <v>9.5504222521322385e-005</v>
+        <v>4.1922976390655809e-005</v>
       </c>
       <c r="H18">
-        <v>2.0047565096316481e-006</v>
+        <v>2.2168626291516049e-005</v>
       </c>
       <c r="I18">
-        <v>-4.9220095449921072e-007</v>
+        <v>1.0319359679861464e-005</v>
       </c>
       <c r="J18">
-        <v>2.6655314361790608e-005</v>
+        <v>-6.6622054521533894e-005</v>
       </c>
       <c r="K18">
-        <v>-6.0499985665909452e-005</v>
+        <v>0.00018185199231155282</v>
       </c>
       <c r="L18">
-        <v>-7.2289437977537171e-005</v>
+        <v>-0.00060349552476584819</v>
       </c>
       <c r="M18">
-        <v>-4.8993215194675525e-006</v>
+        <v>-4.2202537117885874e-005</v>
       </c>
       <c r="N18">
-        <v>-6.0514578049949497e-005</v>
+        <v>2.6777805357495636e-005</v>
       </c>
       <c r="O18">
-        <v>-0.00026145101450957952</v>
+        <v>0.00032140224443571254</v>
       </c>
       <c r="P18">
-        <v>2.522864768892373e-005</v>
+        <v>0.00049315082723549336</v>
       </c>
       <c r="Q18">
-        <v>4.3145975352665679e-005</v>
+        <v>0.00064543762346347909</v>
       </c>
       <c r="R18">
-        <v>0.0027613881411792758</v>
+        <v>0.00056217258446161148</v>
       </c>
       <c r="S18">
-        <v>0.0038409847444403171</v>
+        <v>0.0022852743602280547</v>
       </c>
       <c r="T18">
-        <v>0.0026890135596450244</v>
+        <v>5.546521660156783e-005</v>
       </c>
       <c r="U18">
-        <v>0.0029156329764217529</v>
+        <v>7.8724558804471297e-005</v>
       </c>
       <c r="V18">
-        <v>0.0026976433061034139</v>
+        <v>5.4240235728675616e-005</v>
       </c>
       <c r="W18">
-        <v>0.0026872378493284213</v>
+        <v>0.00021668946437121764</v>
       </c>
       <c r="X18">
-        <v>0.0027011499477352396</v>
+        <v>9.7402159643090102e-005</v>
       </c>
       <c r="Y18">
-        <v>0.0027288855931214811</v>
+        <v>6.2735443432025435e-005</v>
       </c>
       <c r="Z18">
-        <v>0.002723878433540142</v>
+        <v>6.5107524138756931e-005</v>
       </c>
       <c r="AA18">
-        <v>0.002733860608948294</v>
+        <v>3.7339325410253163e-005</v>
       </c>
       <c r="AB18">
-        <v>0.0027517468440106368</v>
+        <v>2.9730759393105204e-005</v>
       </c>
       <c r="AC18">
-        <v>-2.0633625786224588e-005</v>
+        <v>-1.6620461376627618e-005</v>
       </c>
       <c r="AD18">
-        <v>1.9069354714326193e-005</v>
+        <v>-5.7833840809134746e-005</v>
       </c>
       <c r="AE18">
-        <v>2.0168762158152319e-005</v>
+        <v>-3.4904252157705079e-006</v>
       </c>
       <c r="AF18">
-        <v>0.0015625812156786589</v>
+        <v>2.0587389307758961e-005</v>
       </c>
       <c r="AG18">
-        <v>0.0012403488599521558</v>
+        <v>5.8612399539937512e-005</v>
       </c>
       <c r="AH18">
-        <v>-0.00038030263126034164</v>
+        <v>0.00076673545360437124</v>
       </c>
       <c r="AI18">
-        <v>0.001378502729192049</v>
+        <v>6.2689569632612234e-005</v>
+      </c>
+      <c r="AJ18">
+        <v>0.00024263108876943678</v>
+      </c>
+      <c r="AK18">
+        <v>0.004841919194682201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B19">
-        <v>0.16542658095090529</v>
+        <v>0.23393749477395775</v>
       </c>
       <c r="C19">
-        <v>-0.00012239343187851038</v>
+        <v>-0.00014076749368187677</v>
       </c>
       <c r="D19">
-        <v>-0.00013383022617576706</v>
+        <v>-0.00013800979010805334</v>
       </c>
       <c r="E19">
-        <v>1.1177951544081612e-006</v>
+        <v>1.2042883777092285e-006</v>
       </c>
       <c r="F19">
-        <v>8.4648606087088469e-005</v>
+        <v>8.4834912260119003e-006</v>
       </c>
       <c r="G19">
-        <v>5.2768558557704558e-005</v>
+        <v>-2.0190861864260307e-005</v>
       </c>
       <c r="H19">
-        <v>1.5288537335830988e-006</v>
+        <v>4.2094297733758499e-006</v>
       </c>
       <c r="I19">
-        <v>-1.5301729357961093e-006</v>
+        <v>-1.3386246033057558e-006</v>
       </c>
       <c r="J19">
-        <v>3.8749848492285253e-005</v>
+        <v>3.882683491167392e-005</v>
       </c>
       <c r="K19">
-        <v>-5.0562373627803699e-005</v>
+        <v>8.8171849764416554e-005</v>
       </c>
       <c r="L19">
-        <v>-8.5941907597138472e-005</v>
+        <v>-0.00030723825526723231</v>
       </c>
       <c r="M19">
-        <v>4.2320152643338373e-005</v>
+        <v>-0.00013811153794394612</v>
       </c>
       <c r="N19">
-        <v>2.6334249249960117e-005</v>
+        <v>5.2790524405165431e-005</v>
       </c>
       <c r="O19">
-        <v>-0.00016998095906175636</v>
+        <v>-9.3641285997161927e-005</v>
       </c>
       <c r="P19">
-        <v>9.2019164235814877e-005</v>
+        <v>-0.00044232775130330338</v>
       </c>
       <c r="Q19">
-        <v>0.00013094767927848043</v>
+        <v>-0.00022300408294189647</v>
       </c>
       <c r="R19">
-        <v>0.0027431853146946995</v>
+        <v>-0.00023614587122211105</v>
       </c>
       <c r="S19">
-        <v>0.0026890135596450244</v>
+        <v>5.546521660156783e-005</v>
       </c>
       <c r="T19">
-        <v>0.0040893845159734737</v>
+        <v>0.0054477216533581185</v>
       </c>
       <c r="U19">
-        <v>0.0028592423718067912</v>
+        <v>0.0027230228607281019</v>
       </c>
       <c r="V19">
-        <v>0.0026921086570248646</v>
+        <v>0.0027102442082332554</v>
       </c>
       <c r="W19">
-        <v>0.0026719372363228728</v>
+        <v>0.0029642706256497267</v>
       </c>
       <c r="X19">
-        <v>0.002680665562796343</v>
+        <v>0.0027187087908356264</v>
       </c>
       <c r="Y19">
-        <v>0.0027064354854307851</v>
+        <v>0.0026989598828957295</v>
       </c>
       <c r="Z19">
-        <v>0.0027016984127009869</v>
+        <v>0.0027048991247228945</v>
       </c>
       <c r="AA19">
-        <v>0.0027162057656988994</v>
+        <v>0.0027345489303218103</v>
       </c>
       <c r="AB19">
-        <v>0.0027474685332156698</v>
+        <v>0.0027466961563768124</v>
       </c>
       <c r="AC19">
-        <v>-1.6650835314747518e-005</v>
+        <v>0.0027648862610188439</v>
       </c>
       <c r="AD19">
-        <v>8.4133969033229922e-005</v>
+        <v>0.0027965008556145119</v>
       </c>
       <c r="AE19">
-        <v>5.3651654672277427e-006</v>
+        <v>-2.0558988138085383e-005</v>
       </c>
       <c r="AF19">
-        <v>0.0013424356178338309</v>
+        <v>-1.9156243986151802e-005</v>
       </c>
       <c r="AG19">
-        <v>0.0012811466820745903</v>
+        <v>0.0001376457475656626</v>
       </c>
       <c r="AH19">
-        <v>-0.00038930831986717332</v>
+        <v>0.0017317893508796659</v>
       </c>
       <c r="AI19">
-        <v>0.0015102532530236728</v>
+        <v>0.0013329598505165885</v>
+      </c>
+      <c r="AJ19">
+        <v>-0.00029392263015029865</v>
+      </c>
+      <c r="AK19">
+        <v>0.0017674576858222818</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20">
-        <v>0.1073666572723221</v>
+        <v>0.12446776990065339</v>
       </c>
       <c r="C20">
-        <v>-0.00013760207191634155</v>
+        <v>-0.00013668876581117103</v>
       </c>
       <c r="D20">
-        <v>-0.00037693048014793545</v>
+        <v>-0.00012911175610285687</v>
       </c>
       <c r="E20">
-        <v>2.8987606162927129e-006</v>
+        <v>1.0868317942213334e-006</v>
       </c>
       <c r="F20">
-        <v>0.00013433188380059137</v>
+        <v>6.4646445108757866e-005</v>
       </c>
       <c r="G20">
-        <v>0.00028624811553237871</v>
+        <v>6.3468463752193287e-005</v>
       </c>
       <c r="H20">
-        <v>4.3100539056203792e-006</v>
+        <v>2.5762402972119962e-006</v>
       </c>
       <c r="I20">
-        <v>5.5041403622002141e-006</v>
+        <v>4.9063744253384007e-007</v>
       </c>
       <c r="J20">
-        <v>0.00011470057251645804</v>
+        <v>2.9191038006409352e-005</v>
       </c>
       <c r="K20">
-        <v>3.7266536009045084e-005</v>
+        <v>-4.4218989795487273e-005</v>
       </c>
       <c r="L20">
-        <v>-0.00017366086447253453</v>
+        <v>-0.00012995938998674669</v>
       </c>
       <c r="M20">
-        <v>6.6701574437604279e-005</v>
+        <v>-0.00011524769736950371</v>
       </c>
       <c r="N20">
-        <v>-0.0001816198357893783</v>
+        <v>2.4611789095094197e-005</v>
       </c>
       <c r="O20">
-        <v>-0.00029351392241655928</v>
+        <v>-9.0858665272306512e-005</v>
       </c>
       <c r="P20">
-        <v>0.00016603667447870818</v>
+        <v>-0.00033371187303885626</v>
       </c>
       <c r="Q20">
-        <v>-1.5183794007086527e-005</v>
+        <v>-8.3042309582709154e-005</v>
       </c>
       <c r="R20">
-        <v>0.0029878914048334735</v>
+        <v>-7.9041762989169855e-005</v>
       </c>
       <c r="S20">
-        <v>0.0029156329764217529</v>
+        <v>7.8724558804471297e-005</v>
       </c>
       <c r="T20">
-        <v>0.0028592423718067912</v>
+        <v>0.0027230228607281019</v>
       </c>
       <c r="U20">
-        <v>0.0049322397940719451</v>
+        <v>0.003799550883834147</v>
       </c>
       <c r="V20">
-        <v>0.0028755660316172474</v>
+        <v>0.0026519618105022339</v>
       </c>
       <c r="W20">
-        <v>0.002903267162897735</v>
+        <v>0.0028860588946789415</v>
       </c>
       <c r="X20">
-        <v>0.0029276874660915022</v>
+        <v>0.0026567615928784058</v>
       </c>
       <c r="Y20">
-        <v>0.0029792264151586576</v>
+        <v>0.0026459158801001781</v>
       </c>
       <c r="Z20">
-        <v>0.0029541321259471402</v>
+        <v>0.0026596177963680652</v>
       </c>
       <c r="AA20">
-        <v>0.0029807183298781841</v>
+        <v>0.0026878339639631972</v>
       </c>
       <c r="AB20">
-        <v>0.0029969887267279815</v>
+        <v>0.0026842296685982547</v>
       </c>
       <c r="AC20">
-        <v>6.1945039668564485e-006</v>
+        <v>0.0026954153209061381</v>
       </c>
       <c r="AD20">
-        <v>-4.9470969061283149e-005</v>
+        <v>0.0027200988268549445</v>
       </c>
       <c r="AE20">
-        <v>-0.00013800337409936321</v>
+        <v>-1.7079525334424159e-005</v>
       </c>
       <c r="AF20">
-        <v>0.0035967017150546417</v>
+        <v>6.1763610492837216e-006</v>
       </c>
       <c r="AG20">
-        <v>0.0013665818075972742</v>
+        <v>-2.601776545945139e-005</v>
       </c>
       <c r="AH20">
-        <v>-0.000317491095778839</v>
+        <v>0.0015637610695035642</v>
       </c>
       <c r="AI20">
-        <v>0.0085298484397225913</v>
+        <v>0.0012143158811348496</v>
+      </c>
+      <c r="AJ20">
+        <v>-0.00047648176891071543</v>
+      </c>
+      <c r="AK20">
+        <v>0.0014682143272505693</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21">
-        <v>0.10780599612417958</v>
+        <v>0.15885390355878248</v>
       </c>
       <c r="C21">
-        <v>-0.00014185223728625302</v>
+        <v>-0.00012714384213254845</v>
       </c>
       <c r="D21">
-        <v>-0.00017356139449096857</v>
+        <v>-0.00013068892299153076</v>
       </c>
       <c r="E21">
-        <v>1.4818764227324239e-006</v>
+        <v>1.0945138266390468e-006</v>
       </c>
       <c r="F21">
-        <v>-5.4245227272604511e-006</v>
+        <v>6.6278471360875534e-005</v>
       </c>
       <c r="G21">
-        <v>-3.5641432288625896e-006</v>
+        <v>2.8008209233265473e-005</v>
       </c>
       <c r="H21">
-        <v>7.9112014952082538e-007</v>
+        <v>1.6621315743166329e-006</v>
       </c>
       <c r="I21">
-        <v>-1.8718837537051952e-006</v>
+        <v>-1.1274124815514831e-006</v>
       </c>
       <c r="J21">
-        <v>1.6513891884790098e-005</v>
+        <v>3.4304499260704802e-005</v>
       </c>
       <c r="K21">
-        <v>-1.0313951203637199e-005</v>
+        <v>-2.4626665145160119e-005</v>
       </c>
       <c r="L21">
-        <v>-0.00010503336607094898</v>
+        <v>-0.00014625030057526228</v>
       </c>
       <c r="M21">
-        <v>-2.1915267383472876e-005</v>
+        <v>-0.00011007560033896198</v>
       </c>
       <c r="N21">
-        <v>-7.6548426446733028e-005</v>
+        <v>6.5619370777193057e-005</v>
       </c>
       <c r="O21">
-        <v>-0.00025242003082682129</v>
+        <v>6.2202904672163922e-006</v>
       </c>
       <c r="P21">
-        <v>4.3314609607175312e-005</v>
+        <v>-0.00023344381561099439</v>
       </c>
       <c r="Q21">
-        <v>6.533630654959998e-005</v>
+        <v>3.0410350107863303e-006</v>
       </c>
       <c r="R21">
-        <v>0.0027531758203599172</v>
+        <v>2.4091122710191573e-005</v>
       </c>
       <c r="S21">
-        <v>0.0026976433061034139</v>
+        <v>5.4240235728675616e-005</v>
       </c>
       <c r="T21">
-        <v>0.0026921086570248646</v>
+        <v>0.0027102442082332554</v>
       </c>
       <c r="U21">
-        <v>0.0028755660316172474</v>
+        <v>0.0026519618105022339</v>
       </c>
       <c r="V21">
-        <v>0.0042915602460420364</v>
+        <v>0.0040961506580381377</v>
       </c>
       <c r="W21">
-        <v>0.0026802270226468231</v>
+        <v>0.0028385543468549134</v>
       </c>
       <c r="X21">
-        <v>0.002684869470136444</v>
+        <v>0.0026571336606716319</v>
       </c>
       <c r="Y21">
-        <v>0.002712246752070031</v>
+        <v>0.0026363398773641632</v>
       </c>
       <c r="Z21">
-        <v>0.0027160134159586679</v>
+        <v>0.0026446131724438531</v>
       </c>
       <c r="AA21">
-        <v>0.0027202866063005507</v>
+        <v>0.0026710170338987869</v>
       </c>
       <c r="AB21">
-        <v>0.0027458560393004566</v>
+        <v>0.0026676071152200876</v>
       </c>
       <c r="AC21">
-        <v>-2.6884173788616035e-005</v>
+        <v>0.0026836880510053484</v>
       </c>
       <c r="AD21">
-        <v>0.00013093537572943283</v>
+        <v>0.0027202911049568467</v>
       </c>
       <c r="AE21">
-        <v>0.00014450041225832287</v>
+        <v>-1.2617337533954215e-005</v>
       </c>
       <c r="AF21">
-        <v>0.00132496767768376</v>
+        <v>6.7605234115890615e-005</v>
       </c>
       <c r="AG21">
-        <v>0.0010436267381622511</v>
+        <v>-3.364244881887894e-005</v>
       </c>
       <c r="AH21">
-        <v>-0.00044167514466559216</v>
+        <v>0.0013617784303921938</v>
       </c>
       <c r="AI21">
-        <v>0.0029348913460538529</v>
+        <v>0.0012686456158567975</v>
+      </c>
+      <c r="AJ21">
+        <v>-0.00046013430799218152</v>
+      </c>
+      <c r="AK21">
+        <v>0.0014925912019428181</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B22">
-        <v>0.056568120894725224</v>
+        <v>0.10190559241708566</v>
       </c>
       <c r="C22">
-        <v>-8.0901872891486065e-005</v>
+        <v>-0.00014837370158889449</v>
       </c>
       <c r="D22">
-        <v>-0.00021572885910388015</v>
+        <v>-0.00040177895602702901</v>
       </c>
       <c r="E22">
-        <v>1.6941350038803904e-006</v>
+        <v>3.0954933934382882e-006</v>
       </c>
       <c r="F22">
-        <v>6.6543972624315387e-005</v>
+        <v>0.000118374498966749</v>
       </c>
       <c r="G22">
-        <v>5.9824845184296453e-005</v>
+        <v>0.00026445483340923866</v>
       </c>
       <c r="H22">
-        <v>1.2528941564498989e-007</v>
+        <v>6.2493865846285919e-006</v>
       </c>
       <c r="I22">
-        <v>-3.8379733825500155e-006</v>
+        <v>7.5110763818905227e-006</v>
       </c>
       <c r="J22">
-        <v>8.3396757667501126e-005</v>
+        <v>0.0001191258776018779</v>
       </c>
       <c r="K22">
-        <v>5.8910943560204487e-006</v>
+        <v>6.4951568678874114e-005</v>
       </c>
       <c r="L22">
-        <v>-0.00015664228510992983</v>
+        <v>-0.00028454128640589924</v>
       </c>
       <c r="M22">
-        <v>1.8236164385261635e-005</v>
+        <v>-0.00018552773687463046</v>
       </c>
       <c r="N22">
-        <v>-6.4545147024309664e-005</v>
+        <v>0.0001169979279241833</v>
       </c>
       <c r="O22">
-        <v>-0.00021264213547563166</v>
+        <v>-0.0002099137124137461</v>
       </c>
       <c r="P22">
-        <v>2.8709367303298913e-005</v>
+        <v>-0.00037183109864927195</v>
       </c>
       <c r="Q22">
-        <v>-2.6812677861626395e-006</v>
+        <v>6.0487965490296834e-005</v>
       </c>
       <c r="R22">
-        <v>0.0027402145866067375</v>
+        <v>-0.00016248782668856385</v>
       </c>
       <c r="S22">
-        <v>0.0026872378493284213</v>
+        <v>0.00021668946437121764</v>
       </c>
       <c r="T22">
-        <v>0.0026719372363228728</v>
+        <v>0.0029642706256497267</v>
       </c>
       <c r="U22">
-        <v>0.002903267162897735</v>
+        <v>0.0028860588946789415</v>
       </c>
       <c r="V22">
-        <v>0.0026802270226468231</v>
+        <v>0.0028385543468549134</v>
       </c>
       <c r="W22">
-        <v>0.00384206059246115</v>
+        <v>0.0049961825414943824</v>
       </c>
       <c r="X22">
-        <v>0.0026983831579630697</v>
+        <v>0.0028424956779678793</v>
       </c>
       <c r="Y22">
-        <v>0.0027227557488387496</v>
+        <v>0.0028752440246965533</v>
       </c>
       <c r="Z22">
-        <v>0.0027129003550870039</v>
+        <v>0.0029007632452119712</v>
       </c>
       <c r="AA22">
-        <v>0.0027230838691242754</v>
+        <v>0.0029561806413237581</v>
       </c>
       <c r="AB22">
-        <v>0.0027500310018968989</v>
+        <v>0.0029306384085303386</v>
       </c>
       <c r="AC22">
-        <v>-1.609824243489549e-005</v>
+        <v>0.0029585602227152254</v>
       </c>
       <c r="AD22">
-        <v>3.8827352207354386e-005</v>
+        <v>0.0029859186866155697</v>
       </c>
       <c r="AE22">
-        <v>1.890006113553019e-005</v>
+        <v>1.2983038494071694e-005</v>
       </c>
       <c r="AF22">
-        <v>0.0015695317699623429</v>
+        <v>-8.1814080730243033e-005</v>
       </c>
       <c r="AG22">
-        <v>0.0013123891354770139</v>
+        <v>-0.00018108981637578528</v>
       </c>
       <c r="AH22">
-        <v>-0.00038107275521368877</v>
+        <v>0.0037453478749548087</v>
       </c>
       <c r="AI22">
-        <v>0.0045939672281012939</v>
+        <v>0.0013508951173299068</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.00041290270972204251</v>
+      </c>
+      <c r="AK22">
+        <v>0.0092081598150843234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23">
-        <v>0.038688998059802339</v>
+        <v>0.10899814890846771</v>
       </c>
       <c r="C23">
-        <v>-8.9067750073194873e-005</v>
+        <v>-0.00013961418687945167</v>
       </c>
       <c r="D23">
-        <v>-0.0001770721434475736</v>
+        <v>-0.00018408553891208559</v>
       </c>
       <c r="E23">
-        <v>1.4068252950084599e-006</v>
+        <v>1.5634587434315458e-006</v>
       </c>
       <c r="F23">
-        <v>8.8183666551205946e-005</v>
+        <v>-3.4349306495866385e-005</v>
       </c>
       <c r="G23">
-        <v>9.859275953512164e-005</v>
+        <v>-3.6329161594594081e-005</v>
       </c>
       <c r="H23">
-        <v>-4.3669573867337254e-007</v>
+        <v>1.6992154877552626e-006</v>
       </c>
       <c r="I23">
-        <v>-2.2857895989284666e-006</v>
+        <v>-9.0576174486004253e-007</v>
       </c>
       <c r="J23">
-        <v>5.0983675350075772e-005</v>
+        <v>2.8717874604741321e-005</v>
       </c>
       <c r="K23">
-        <v>-2.4207415427884849e-006</v>
+        <v>-1.4630701368773674e-005</v>
       </c>
       <c r="L23">
-        <v>-0.000162348371194743</v>
+        <v>-0.00014913357607569027</v>
       </c>
       <c r="M23">
-        <v>1.9360840316061192e-005</v>
+        <v>-0.00010414758561621744</v>
       </c>
       <c r="N23">
-        <v>-6.3330314032122902e-005</v>
+        <v>7.1584492738275133e-006</v>
       </c>
       <c r="O23">
-        <v>-0.00023429739230048274</v>
+        <v>-9.6796145963695245e-005</v>
       </c>
       <c r="P23">
-        <v>8.2042663924878668e-006</v>
+        <v>-0.00029485352161907842</v>
       </c>
       <c r="Q23">
-        <v>-4.8490020366518142e-005</v>
+        <v>-2.9222699179646877e-005</v>
       </c>
       <c r="R23">
-        <v>0.0027471697257639314</v>
+        <v>-1.4483381370454778e-005</v>
       </c>
       <c r="S23">
-        <v>0.0027011499477352396</v>
+        <v>9.7402159643090102e-005</v>
       </c>
       <c r="T23">
-        <v>0.002680665562796343</v>
+        <v>0.0027187087908356264</v>
       </c>
       <c r="U23">
-        <v>0.0029276874660915022</v>
+        <v>0.0026567615928784058</v>
       </c>
       <c r="V23">
-        <v>0.002684869470136444</v>
+        <v>0.0026571336606716319</v>
       </c>
       <c r="W23">
-        <v>0.0026983831579630697</v>
+        <v>0.0028424956779678793</v>
       </c>
       <c r="X23">
-        <v>0.0035546323065746583</v>
+        <v>0.0042369274299728487</v>
       </c>
       <c r="Y23">
-        <v>0.0027378426933235759</v>
+        <v>0.0026383029892533632</v>
       </c>
       <c r="Z23">
-        <v>0.0027251140349415321</v>
+        <v>0.0026421903158761464</v>
       </c>
       <c r="AA23">
-        <v>0.0027374432370574431</v>
+        <v>0.0026701947193479864</v>
       </c>
       <c r="AB23">
-        <v>0.0027538849731410771</v>
+        <v>0.0026768624960499471</v>
       </c>
       <c r="AC23">
-        <v>-1.7209393499203183e-005</v>
+        <v>0.0026823517245824673</v>
       </c>
       <c r="AD23">
-        <v>3.8464296926776179e-005</v>
+        <v>0.0027122020813314229</v>
       </c>
       <c r="AE23">
-        <v>1.0408331795507626e-005</v>
+        <v>-2.4090436641729116e-005</v>
       </c>
       <c r="AF23">
-        <v>0.0016500817270290373</v>
+        <v>0.00012783688745070763</v>
       </c>
       <c r="AG23">
-        <v>0.0011955455656553382</v>
+        <v>0.00010932404209869229</v>
       </c>
       <c r="AH23">
-        <v>-0.00039342577640071529</v>
+        <v>0.0013124002318400771</v>
       </c>
       <c r="AI23">
-        <v>0.0032889782916181946</v>
+        <v>0.001046505536183667</v>
+      </c>
+      <c r="AJ23">
+        <v>-0.00053204761849445109</v>
+      </c>
+      <c r="AK23">
+        <v>0.0032862067796679086</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24">
-        <v>0.035889257682964353</v>
+        <v>0.053409472160713706</v>
       </c>
       <c r="C24">
-        <v>-0.0001033904007670533</v>
+        <v>-7.9415749256403012e-005</v>
       </c>
       <c r="D24">
-        <v>-0.00020736660551521485</v>
+        <v>-0.00021915515324403417</v>
       </c>
       <c r="E24">
-        <v>1.6650975828502799e-006</v>
+        <v>1.7206505232030445e-006</v>
       </c>
       <c r="F24">
-        <v>9.9318558468573375e-005</v>
+        <v>4.1107701361967769e-005</v>
       </c>
       <c r="G24">
-        <v>0.00015529750680132984</v>
+        <v>3.011028794305435e-005</v>
       </c>
       <c r="H24">
-        <v>6.3556457574389931e-007</v>
+        <v>3.2024434566479227e-007</v>
       </c>
       <c r="I24">
-        <v>-2.9715102029703082e-006</v>
+        <v>-3.0332340447509221e-006</v>
       </c>
       <c r="J24">
-        <v>5.2192697499616283e-005</v>
+        <v>8.5722453964595939e-005</v>
       </c>
       <c r="K24">
-        <v>-1.3800391551015145e-006</v>
+        <v>2.51605504856681e-005</v>
       </c>
       <c r="L24">
-        <v>-0.00011882902009951925</v>
+        <v>-0.0002192357688889637</v>
       </c>
       <c r="M24">
-        <v>-1.0445026162038016e-005</v>
+        <v>-0.00011102932411283324</v>
       </c>
       <c r="N24">
-        <v>-4.6129710149909586e-005</v>
+        <v>4.1785545165508623e-005</v>
       </c>
       <c r="O24">
-        <v>-0.00019500415995378322</v>
+        <v>-9.5540126501064042e-005</v>
       </c>
       <c r="P24">
-        <v>0.00012255827602129397</v>
+        <v>-0.00028681225117831795</v>
       </c>
       <c r="Q24">
-        <v>9.0918259537705942e-005</v>
+        <v>-7.5020845969721544e-005</v>
       </c>
       <c r="R24">
-        <v>0.0027741932968846457</v>
+        <v>-0.00012548256158406192</v>
       </c>
       <c r="S24">
-        <v>0.0027288855931214811</v>
+        <v>6.2735443432025435e-005</v>
       </c>
       <c r="T24">
-        <v>0.0027064354854307851</v>
+        <v>0.0026989598828957295</v>
       </c>
       <c r="U24">
-        <v>0.0029792264151586576</v>
+        <v>0.0026459158801001781</v>
       </c>
       <c r="V24">
-        <v>0.002712246752070031</v>
+        <v>0.0026363398773641632</v>
       </c>
       <c r="W24">
-        <v>0.0027227557488387496</v>
+        <v>0.0028752440246965533</v>
       </c>
       <c r="X24">
-        <v>0.0027378426933235759</v>
+        <v>0.0026383029892533632</v>
       </c>
       <c r="Y24">
-        <v>0.0038361225872164868</v>
+        <v>0.0037976587452227227</v>
       </c>
       <c r="Z24">
-        <v>0.0027496273130582817</v>
+        <v>0.0026573339096362097</v>
       </c>
       <c r="AA24">
-        <v>0.0027623640250496835</v>
+        <v>0.0026820281831748298</v>
       </c>
       <c r="AB24">
-        <v>0.0027874887796035608</v>
+        <v>0.0026729043309092269</v>
       </c>
       <c r="AC24">
-        <v>-1.8839947502663609e-005</v>
+        <v>0.0026845686526477406</v>
       </c>
       <c r="AD24">
-        <v>6.81543764299961e-005</v>
+        <v>0.0027173308446087428</v>
       </c>
       <c r="AE24">
-        <v>1.4075018332390398e-005</v>
+        <v>-1.1858944326786371e-005</v>
       </c>
       <c r="AF24">
-        <v>0.0017984884824380639</v>
+        <v>2.0033731522924378e-005</v>
       </c>
       <c r="AG24">
-        <v>0.0013316997680248516</v>
+        <v>-2.9668392257857382e-005</v>
       </c>
       <c r="AH24">
-        <v>-0.00036703461929624642</v>
+        <v>0.0015588593586346616</v>
       </c>
       <c r="AI24">
-        <v>0.0040464432672078715</v>
+        <v>0.001299774179940278</v>
+      </c>
+      <c r="AJ24">
+        <v>-0.00048572794048193455</v>
+      </c>
+      <c r="AK24">
+        <v>0.0047835545734878759</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25">
-        <v>0.11962522024015435</v>
+        <v>0.036483824597415337</v>
       </c>
       <c r="C25">
-        <v>-0.00010718512696077554</v>
+        <v>-9.1012630208759813e-005</v>
       </c>
       <c r="D25">
-        <v>-0.00018340364506168674</v>
+        <v>-0.00017850416467435695</v>
       </c>
       <c r="E25">
-        <v>1.509623669916101e-006</v>
+        <v>1.4212110718511987e-006</v>
       </c>
       <c r="F25">
-        <v>0.00010175092415343689</v>
+        <v>6.5102817090578182e-005</v>
       </c>
       <c r="G25">
-        <v>8.5181963887258892e-005</v>
+        <v>6.2594767561201248e-005</v>
       </c>
       <c r="H25">
-        <v>1.1027372775355493e-006</v>
+        <v>-2.864511432750579e-007</v>
       </c>
       <c r="I25">
-        <v>7.8645614953344448e-007</v>
+        <v>-1.51026731611473e-006</v>
       </c>
       <c r="J25">
-        <v>3.2200966735094561e-005</v>
+        <v>4.765347992586981e-005</v>
       </c>
       <c r="K25">
-        <v>2.9056553107347644e-005</v>
+        <v>1.1722927100996268e-005</v>
       </c>
       <c r="L25">
-        <v>-0.00013471596579144301</v>
+        <v>-0.00022545123333635175</v>
       </c>
       <c r="M25">
-        <v>-1.6710313691300685e-005</v>
+        <v>-0.00012523563364044555</v>
       </c>
       <c r="N25">
-        <v>-8.7040156537711647e-005</v>
+        <v>5.2478640290093902e-005</v>
       </c>
       <c r="O25">
-        <v>-0.00022153838142827164</v>
+        <v>-9.0112602034827637e-005</v>
       </c>
       <c r="P25">
-        <v>4.5074773237518051e-005</v>
+        <v>-0.00030986130662663362</v>
       </c>
       <c r="Q25">
-        <v>2.7276838169165273e-005</v>
+        <v>-9.8629989278121153e-005</v>
       </c>
       <c r="R25">
-        <v>0.0027847551897491238</v>
+        <v>-0.00017717369935453964</v>
       </c>
       <c r="S25">
-        <v>0.002723878433540142</v>
+        <v>6.5107524138756931e-005</v>
       </c>
       <c r="T25">
-        <v>0.0027016984127009869</v>
+        <v>0.0027048991247228945</v>
       </c>
       <c r="U25">
-        <v>0.0029541321259471402</v>
+        <v>0.0026596177963680652</v>
       </c>
       <c r="V25">
-        <v>0.0027160134159586679</v>
+        <v>0.0026446131724438531</v>
       </c>
       <c r="W25">
-        <v>0.0027129003550870039</v>
+        <v>0.0029007632452119712</v>
       </c>
       <c r="X25">
-        <v>0.0027251140349415321</v>
+        <v>0.0026421903158761464</v>
       </c>
       <c r="Y25">
-        <v>0.0027496273130582817</v>
+        <v>0.0026573339096362097</v>
       </c>
       <c r="Z25">
-        <v>0.0042966549250086803</v>
+        <v>0.0035275245809829325</v>
       </c>
       <c r="AA25">
-        <v>0.0027600736838967826</v>
+        <v>0.0026961149925192117</v>
       </c>
       <c r="AB25">
-        <v>0.0027817802859547436</v>
+        <v>0.0026844619716202608</v>
       </c>
       <c r="AC25">
-        <v>-1.8111406711252367e-005</v>
+        <v>0.0026988093533894756</v>
       </c>
       <c r="AD25">
-        <v>2.7081704511278153e-005</v>
+        <v>0.0027227112168859806</v>
       </c>
       <c r="AE25">
-        <v>-1.4309176851486514e-005</v>
+        <v>-1.3132186507249026e-005</v>
       </c>
       <c r="AF25">
-        <v>0.0017234638599133499</v>
+        <v>1.9000062742784954e-005</v>
       </c>
       <c r="AG25">
-        <v>0.0013216588613496161</v>
+        <v>-3.472041142653758e-005</v>
       </c>
       <c r="AH25">
-        <v>-0.00024344984040492812</v>
+        <v>0.0016544608131339599</v>
       </c>
       <c r="AI25">
-        <v>0.0030356536200061798</v>
+        <v>0.0011585388197121213</v>
+      </c>
+      <c r="AJ25">
+        <v>-0.00047697517679799717</v>
+      </c>
+      <c r="AK25">
+        <v>0.0034180959073727476</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B26">
-        <v>0.094043971644993077</v>
+        <v>0.043423694246496253</v>
       </c>
       <c r="C26">
-        <v>-0.00013965411419945069</v>
+        <v>-0.0001061572727405456</v>
       </c>
       <c r="D26">
-        <v>-0.00019266912914176273</v>
+        <v>-0.0001997532489986277</v>
       </c>
       <c r="E26">
-        <v>1.5542170826922819e-006</v>
+        <v>1.6106581665929558e-006</v>
       </c>
       <c r="F26">
-        <v>7.8870825370762278e-005</v>
+        <v>7.7103620104843258e-005</v>
       </c>
       <c r="G26">
-        <v>0.00012011072769537259</v>
+        <v>0.00012476559147287685</v>
       </c>
       <c r="H26">
-        <v>7.5869502460215634e-007</v>
+        <v>6.8239239650322097e-007</v>
       </c>
       <c r="I26">
-        <v>-1.4623334001327517e-006</v>
+        <v>-2.3193086197211918e-006</v>
       </c>
       <c r="J26">
-        <v>7.4201247151035291e-005</v>
+        <v>4.9357137702018498e-005</v>
       </c>
       <c r="K26">
-        <v>2.9081518428253697e-005</v>
+        <v>1.8441950736204291e-005</v>
       </c>
       <c r="L26">
-        <v>-0.00020670628322890959</v>
+        <v>-0.00016942530092480153</v>
       </c>
       <c r="M26">
-        <v>1.9775638306248196e-005</v>
+        <v>-9.3759870109040057e-005</v>
       </c>
       <c r="N26">
-        <v>8.929874682799422e-005</v>
+        <v>3.5417719214549776e-006</v>
       </c>
       <c r="O26">
-        <v>-0.00015710577472179544</v>
+        <v>-6.6994065652757227e-005</v>
       </c>
       <c r="P26">
-        <v>0.00013096012647028765</v>
+        <v>-0.00025141624604917731</v>
       </c>
       <c r="Q26">
-        <v>0.00011970838287186578</v>
+        <v>3.4494869863869017e-005</v>
       </c>
       <c r="R26">
-        <v>0.0027985047459124068</v>
+        <v>-1.378192709660872e-005</v>
       </c>
       <c r="S26">
-        <v>0.002733860608948294</v>
+        <v>3.7339325410253163e-005</v>
       </c>
       <c r="T26">
-        <v>0.0027162057656988994</v>
+        <v>0.0027345489303218103</v>
       </c>
       <c r="U26">
-        <v>0.0029807183298781841</v>
+        <v>0.0026878339639631972</v>
       </c>
       <c r="V26">
-        <v>0.0027202866063005507</v>
+        <v>0.0026710170338987869</v>
       </c>
       <c r="W26">
-        <v>0.0027230838691242754</v>
+        <v>0.0029561806413237581</v>
       </c>
       <c r="X26">
-        <v>0.0027374432370574431</v>
+        <v>0.0026701947193479864</v>
       </c>
       <c r="Y26">
-        <v>0.0027623640250496835</v>
+        <v>0.0026820281831748298</v>
       </c>
       <c r="Z26">
-        <v>0.0027600736838967826</v>
+        <v>0.0026961149925192117</v>
       </c>
       <c r="AA26">
-        <v>0.0039621214117432375</v>
+        <v>0.0038154552365689169</v>
       </c>
       <c r="AB26">
-        <v>0.0028029433367551099</v>
+        <v>0.0027112782633658336</v>
       </c>
       <c r="AC26">
-        <v>-2.2045143772628483e-005</v>
+        <v>0.0027252014380673563</v>
       </c>
       <c r="AD26">
-        <v>0.0001606740798685947</v>
+        <v>0.0027558614623224937</v>
       </c>
       <c r="AE26">
-        <v>7.2627724166674889e-005</v>
+        <v>-1.4999001954861508e-005</v>
       </c>
       <c r="AF26">
-        <v>0.0017754293594784967</v>
+        <v>5.0811399663066746e-005</v>
       </c>
       <c r="AG26">
-        <v>0.0013430952599716929</v>
+        <v>-1.8269531918556358e-005</v>
       </c>
       <c r="AH26">
-        <v>-0.0002625511460004656</v>
+        <v>0.0018054228395033864</v>
       </c>
       <c r="AI26">
-        <v>0.003519833556493282</v>
+        <v>0.0013181614382234922</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.00045673625071830214</v>
+      </c>
+      <c r="AK26">
+        <v>0.0038667377617547594</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27">
-        <v>0.1133902484575184</v>
+        <v>0.11368541264941412</v>
       </c>
       <c r="C27">
-        <v>-0.00014598009143530755</v>
+        <v>-0.00010874415870808501</v>
       </c>
       <c r="D27">
-        <v>-0.00015538617020148526</v>
+        <v>-0.00017735663802575727</v>
       </c>
       <c r="E27">
-        <v>1.2942573435059798e-006</v>
+        <v>1.46227999574906e-006</v>
       </c>
       <c r="F27">
-        <v>7.1068503356952722e-005</v>
+        <v>7.673299550181283e-005</v>
       </c>
       <c r="G27">
-        <v>5.3935616309982179e-005</v>
+        <v>5.6895061844752467e-005</v>
       </c>
       <c r="H27">
-        <v>4.6284250450050082e-007</v>
+        <v>9.8633617700483363e-007</v>
       </c>
       <c r="I27">
-        <v>-2.7048146629664061e-006</v>
+        <v>1.3339695296634032e-006</v>
       </c>
       <c r="J27">
-        <v>3.0037009563946108e-005</v>
+        <v>3.7810867106729835e-005</v>
       </c>
       <c r="K27">
-        <v>-0.00011855490676589142</v>
+        <v>3.0336478610223233e-005</v>
       </c>
       <c r="L27">
-        <v>-0.00012210270485595292</v>
+        <v>-0.00017605170800144565</v>
       </c>
       <c r="M27">
-        <v>5.1618479677651433e-005</v>
+        <v>-0.00012689619076027277</v>
       </c>
       <c r="N27">
-        <v>4.0935214005216516e-005</v>
+        <v>1.5676241696744382e-005</v>
       </c>
       <c r="O27">
-        <v>-7.8498527567157257e-005</v>
+        <v>-0.00011458018415532074</v>
       </c>
       <c r="P27">
-        <v>0.00024512405614879936</v>
+        <v>-0.00029485208585204744</v>
       </c>
       <c r="Q27">
-        <v>0.00023844233614318724</v>
+        <v>-5.8376146036528964e-005</v>
       </c>
       <c r="R27">
-        <v>0.0028203804180448105</v>
+        <v>-9.0813976172197681e-005</v>
       </c>
       <c r="S27">
-        <v>0.0027517468440106368</v>
+        <v>2.9730759393105204e-005</v>
       </c>
       <c r="T27">
-        <v>0.0027474685332156698</v>
+        <v>0.0027466961563768124</v>
       </c>
       <c r="U27">
-        <v>0.0029969887267279815</v>
+        <v>0.0026842296685982547</v>
       </c>
       <c r="V27">
-        <v>0.0027458560393004566</v>
+        <v>0.0026676071152200876</v>
       </c>
       <c r="W27">
-        <v>0.0027500310018968989</v>
+        <v>0.0029306384085303386</v>
       </c>
       <c r="X27">
-        <v>0.0027538849731410771</v>
+        <v>0.0026768624960499471</v>
       </c>
       <c r="Y27">
-        <v>0.0027874887796035608</v>
+        <v>0.0026729043309092269</v>
       </c>
       <c r="Z27">
-        <v>0.0027817802859547436</v>
+        <v>0.0026844619716202608</v>
       </c>
       <c r="AA27">
-        <v>0.0028029433367551099</v>
+        <v>0.0027112782633658336</v>
       </c>
       <c r="AB27">
-        <v>0.0049023134549991947</v>
+        <v>0.0042852572713095024</v>
       </c>
       <c r="AC27">
-        <v>-2.263346765470756e-005</v>
+        <v>0.002726546021461215</v>
       </c>
       <c r="AD27">
-        <v>-1.9237543656549052e-006</v>
+        <v>0.0027545234794928704</v>
       </c>
       <c r="AE27">
-        <v>4.1885633157429789e-005</v>
+        <v>-1.3612021896296575e-005</v>
       </c>
       <c r="AF27">
-        <v>0.0018614818692002618</v>
+        <v>1.1882195007055607e-005</v>
       </c>
       <c r="AG27">
-        <v>0.0013491412295060104</v>
+        <v>-6.0013406593383104e-005</v>
       </c>
       <c r="AH27">
-        <v>-0.00026284152041082775</v>
+        <v>0.0017294492904997038</v>
       </c>
       <c r="AI27">
-        <v>0.0022232719655524095</v>
+        <v>0.0012974149043252421</v>
+      </c>
+      <c r="AJ27">
+        <v>-0.00035238215635413178</v>
+      </c>
+      <c r="AK27">
+        <v>0.0029465628022475971</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28">
-        <v>-0.001584801341690701</v>
+        <v>0.083279836171085947</v>
       </c>
       <c r="C28">
-        <v>1.0757101996857092e-005</v>
+        <v>-0.00013981323985725583</v>
       </c>
       <c r="D28">
-        <v>7.4015576265618749e-007</v>
+        <v>-0.00019137172784688961</v>
       </c>
       <c r="E28">
-        <v>-3.7422739852848103e-008</v>
+        <v>1.5439466580096674e-006</v>
       </c>
       <c r="F28">
-        <v>-1.8121593840954287e-006</v>
+        <v>4.7783851454128991e-005</v>
       </c>
       <c r="G28">
-        <v>1.4922882402936991e-005</v>
+        <v>8.2262188763483949e-005</v>
       </c>
       <c r="H28">
-        <v>4.9584317198554442e-007</v>
+        <v>3.3446114646777333e-007</v>
       </c>
       <c r="I28">
-        <v>8.5152924257893961e-007</v>
+        <v>-7.5960542783472788e-007</v>
       </c>
       <c r="J28">
-        <v>3.24274352044204e-005</v>
+        <v>7.2013749749916017e-005</v>
       </c>
       <c r="K28">
-        <v>8.2794383970707409e-006</v>
+        <v>3.4194373802697541e-005</v>
       </c>
       <c r="L28">
-        <v>6.2810062800766273e-006</v>
+        <v>-0.00024402787920398778</v>
       </c>
       <c r="M28">
-        <v>1.1190321824007842e-005</v>
+        <v>-0.00013581781385477477</v>
       </c>
       <c r="N28">
-        <v>-1.4738327642749012e-006</v>
+        <v>5.6823563094016945e-005</v>
       </c>
       <c r="O28">
-        <v>2.5655069970472637e-006</v>
+        <v>3.8640425591614843e-005</v>
       </c>
       <c r="P28">
-        <v>6.2271597606688663e-006</v>
+        <v>-0.00025312978662154432</v>
       </c>
       <c r="Q28">
-        <v>4.8605946112651507e-007</v>
+        <v>-7.1926177295426972e-006</v>
       </c>
       <c r="R28">
-        <v>-2.4872122837802052e-005</v>
+        <v>-2.9188270194577086e-005</v>
       </c>
       <c r="S28">
-        <v>-2.0633625786224588e-005</v>
+        <v>-1.6620461376627618e-005</v>
       </c>
       <c r="T28">
-        <v>-1.6650835314747518e-005</v>
+        <v>0.0027648862610188439</v>
       </c>
       <c r="U28">
-        <v>6.1945039668564485e-006</v>
+        <v>0.0026954153209061381</v>
       </c>
       <c r="V28">
-        <v>-2.6884173788616035e-005</v>
+        <v>0.0026836880510053484</v>
       </c>
       <c r="W28">
-        <v>-1.609824243489549e-005</v>
+        <v>0.0029585602227152254</v>
       </c>
       <c r="X28">
-        <v>-1.7209393499203183e-005</v>
+        <v>0.0026823517245824673</v>
       </c>
       <c r="Y28">
-        <v>-1.8839947502663609e-005</v>
+        <v>0.0026845686526477406</v>
       </c>
       <c r="Z28">
-        <v>-1.8111406711252367e-005</v>
+        <v>0.0026988093533894756</v>
       </c>
       <c r="AA28">
-        <v>-2.2045143772628483e-005</v>
+        <v>0.0027252014380673563</v>
       </c>
       <c r="AB28">
-        <v>-2.263346765470756e-005</v>
+        <v>0.002726546021461215</v>
       </c>
       <c r="AC28">
-        <v>1.2890718184170158e-005</v>
+        <v>0.0039490694182338446</v>
       </c>
       <c r="AD28">
-        <v>-4.6856123102434787e-005</v>
+        <v>0.0027797569940685861</v>
       </c>
       <c r="AE28">
-        <v>-5.9812586718804443e-005</v>
+        <v>-1.8493266869197463e-005</v>
       </c>
       <c r="AF28">
-        <v>6.7322041614008602e-005</v>
+        <v>0.00014282755771426059</v>
       </c>
       <c r="AG28">
-        <v>-3.9436098309689823e-005</v>
+        <v>3.5639970895610492e-005</v>
       </c>
       <c r="AH28">
-        <v>3.8234237904258088e-005</v>
+        <v>0.0017769958970957488</v>
       </c>
       <c r="AI28">
-        <v>-0.00018760574252675566</v>
+        <v>0.0013241254670822509</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.0003476578675115947</v>
+      </c>
+      <c r="AK28">
+        <v>0.0036431947301365985</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29">
-        <v>-0.05024050962304015</v>
+        <v>0.10173581851875015</v>
       </c>
       <c r="C29">
-        <v>-1.9125721984950141e-005</v>
+        <v>-0.00014487646141360237</v>
       </c>
       <c r="D29">
-        <v>2.203390431719781e-005</v>
+        <v>-0.00015108562566046313</v>
       </c>
       <c r="E29">
-        <v>-1.3769373115040149e-007</v>
+        <v>1.254863071481645e-006</v>
       </c>
       <c r="F29">
-        <v>5.8528350047081659e-005</v>
+        <v>4.7056397075119169e-005</v>
       </c>
       <c r="G29">
-        <v>2.8686236698006182e-005</v>
+        <v>2.2916174841617416e-005</v>
       </c>
       <c r="H29">
-        <v>-6.6556787565047945e-007</v>
+        <v>-2.3231426097495688e-007</v>
       </c>
       <c r="I29">
-        <v>-7.1992948288189141e-008</v>
+        <v>-2.5852090172695465e-006</v>
       </c>
       <c r="J29">
-        <v>4.8386266530427537e-006</v>
+        <v>3.2203629062025523e-005</v>
       </c>
       <c r="K29">
-        <v>5.1943963856602212e-006</v>
+        <v>-0.00012523633482637402</v>
       </c>
       <c r="L29">
-        <v>-3.5715038406500276e-005</v>
+        <v>-0.00015217333784082847</v>
       </c>
       <c r="M29">
-        <v>-2.9150621036744221e-005</v>
+        <v>-0.000164133149487915</v>
       </c>
       <c r="N29">
-        <v>-5.8656846685189762e-005</v>
+        <v>9.8704348400166324e-005</v>
       </c>
       <c r="O29">
-        <v>-0.00016959015108934596</v>
+        <v>-1.9091847918614388e-005</v>
       </c>
       <c r="P29">
-        <v>-0.00016636604617742317</v>
+        <v>-0.0002009896121758217</v>
       </c>
       <c r="Q29">
-        <v>-0.00013438628429898297</v>
+        <v>8.147210400611467e-005</v>
       </c>
       <c r="R29">
-        <v>2.5269982705932326e-007</v>
+        <v>5.378228008637298e-005</v>
       </c>
       <c r="S29">
-        <v>1.9069354714326193e-005</v>
+        <v>-5.7833840809134746e-005</v>
       </c>
       <c r="T29">
-        <v>8.4133969033229922e-005</v>
+        <v>0.0027965008556145119</v>
       </c>
       <c r="U29">
-        <v>-4.9470969061283149e-005</v>
+        <v>0.0027200988268549445</v>
       </c>
       <c r="V29">
-        <v>0.00013093537572943283</v>
+        <v>0.0027202911049568467</v>
       </c>
       <c r="W29">
-        <v>3.8827352207354386e-005</v>
+        <v>0.0029859186866155697</v>
       </c>
       <c r="X29">
-        <v>3.8464296926776179e-005</v>
+        <v>0.0027122020813314229</v>
       </c>
       <c r="Y29">
-        <v>6.81543764299961e-005</v>
+        <v>0.0027173308446087428</v>
       </c>
       <c r="Z29">
-        <v>2.7081704511278153e-005</v>
+        <v>0.0027227112168859806</v>
       </c>
       <c r="AA29">
-        <v>0.0001606740798685947</v>
+        <v>0.0027558614623224937</v>
       </c>
       <c r="AB29">
-        <v>-1.9237543656549052e-006</v>
+        <v>0.0027545234794928704</v>
       </c>
       <c r="AC29">
-        <v>-4.6856123102434787e-005</v>
+        <v>0.0027797569940685861</v>
       </c>
       <c r="AD29">
-        <v>0.0020599804504943197</v>
+        <v>0.0049445955437623507</v>
       </c>
       <c r="AE29">
-        <v>0.00035709959569437517</v>
+        <v>-1.8371290627885694e-005</v>
       </c>
       <c r="AF29">
-        <v>-0.00028880434953428773</v>
+        <v>-2.7115089940532263e-005</v>
       </c>
       <c r="AG29">
-        <v>8.6131334567909624e-005</v>
+        <v>2.6096834048657398e-006</v>
       </c>
       <c r="AH29">
-        <v>-0.00020215497563099235</v>
+        <v>0.0018859250006422706</v>
       </c>
       <c r="AI29">
-        <v>-8.1694966534162487e-005</v>
+        <v>0.0013376678045226909</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.0003716568843889573</v>
+      </c>
+      <c r="AK29">
+        <v>0.0023303695638439061</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30">
-        <v>0.050725867563412928</v>
+        <v>-0.001250326305429196</v>
       </c>
       <c r="C30">
-        <v>-3.5846723578941415e-005</v>
+        <v>1.0162128338978078e-005</v>
       </c>
       <c r="D30">
-        <v>8.3007693996061532e-005</v>
+        <v>7.8490127596204939e-008</v>
       </c>
       <c r="E30">
-        <v>-6.1260719670860333e-007</v>
+        <v>-3.2511178059864692e-008</v>
       </c>
       <c r="F30">
-        <v>2.8411545305667394e-005</v>
+        <v>-1.3665483927623599e-006</v>
       </c>
       <c r="G30">
-        <v>-3.5427229237905823e-005</v>
+        <v>1.5195564765366641e-005</v>
       </c>
       <c r="H30">
-        <v>-1.5239124116388125e-006</v>
+        <v>4.9097869274816836e-007</v>
       </c>
       <c r="I30">
-        <v>-6.5460525714277075e-007</v>
+        <v>8.369742555848611e-007</v>
       </c>
       <c r="J30">
-        <v>-2.5157208389153975e-005</v>
+        <v>3.2893393993980844e-005</v>
       </c>
       <c r="K30">
-        <v>6.0870941943884903e-005</v>
+        <v>6.7686322227449545e-006</v>
       </c>
       <c r="L30">
-        <v>-2.3392753837021217e-005</v>
+        <v>6.2210124049624132e-006</v>
       </c>
       <c r="M30">
-        <v>-5.561860396686106e-006</v>
+        <v>-6.8730494535539602e-006</v>
       </c>
       <c r="N30">
-        <v>4.8742835585605606e-005</v>
+        <v>1.3348089037231718e-005</v>
       </c>
       <c r="O30">
-        <v>-7.3456793302783743e-005</v>
+        <v>-3.7604504412725565e-006</v>
       </c>
       <c r="P30">
-        <v>-3.1720818733399424e-005</v>
+        <v>-1.4608143271239646e-006</v>
       </c>
       <c r="Q30">
-        <v>-1.1866144334434186e-005</v>
+        <v>1.3458493275421153e-006</v>
       </c>
       <c r="R30">
-        <v>0.0001579249552385689</v>
+        <v>-6.3393396944794221e-006</v>
       </c>
       <c r="S30">
-        <v>2.0168762158152319e-005</v>
+        <v>-3.4904252157705079e-006</v>
       </c>
       <c r="T30">
-        <v>5.3651654672277427e-006</v>
+        <v>-2.0558988138085383e-005</v>
       </c>
       <c r="U30">
-        <v>-0.00013800337409936321</v>
+        <v>-1.7079525334424159e-005</v>
       </c>
       <c r="V30">
-        <v>0.00014450041225832287</v>
+        <v>-1.2617337533954215e-005</v>
       </c>
       <c r="W30">
-        <v>1.890006113553019e-005</v>
+        <v>1.2983038494071694e-005</v>
       </c>
       <c r="X30">
-        <v>1.0408331795507626e-005</v>
+        <v>-2.4090436641729116e-005</v>
       </c>
       <c r="Y30">
-        <v>1.4075018332390398e-005</v>
+        <v>-1.1858944326786371e-005</v>
       </c>
       <c r="Z30">
-        <v>-1.4309176851486514e-005</v>
+        <v>-1.3132186507249026e-005</v>
       </c>
       <c r="AA30">
-        <v>7.2627724166674889e-005</v>
+        <v>-1.4999001954861508e-005</v>
       </c>
       <c r="AB30">
-        <v>4.1885633157429789e-005</v>
+        <v>-1.3612021896296575e-005</v>
       </c>
       <c r="AC30">
-        <v>-5.9812586718804443e-005</v>
+        <v>-1.8493266869197463e-005</v>
       </c>
       <c r="AD30">
-        <v>0.00035709959569437517</v>
+        <v>-1.8371290627885694e-005</v>
       </c>
       <c r="AE30">
-        <v>0.0022031855216616074</v>
+        <v>1.3004199413486788e-005</v>
       </c>
       <c r="AF30">
-        <v>-0.00034102315632095301</v>
+        <v>-4.7864226631999715e-005</v>
       </c>
       <c r="AG30">
-        <v>0.00010565641906156787</v>
+        <v>-6.0436197711771443e-005</v>
       </c>
       <c r="AH30">
-        <v>-0.00036875761657775917</v>
+        <v>7.3052885747356203e-005</v>
       </c>
       <c r="AI30">
-        <v>-0.0017994038506445064</v>
+        <v>-3.8700543223929969e-005</v>
+      </c>
+      <c r="AJ30">
+        <v>4.2802101195526583e-005</v>
+      </c>
+      <c r="AK30">
+        <v>-0.00016270687900734845</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31">
-        <v>-0.096931110264828313</v>
+        <v>-0.048458251214821196</v>
       </c>
       <c r="C31">
-        <v>-0.00012605214527293548</v>
+        <v>-2.3453540408400979e-005</v>
       </c>
       <c r="D31">
-        <v>-0.00074931645815612402</v>
+        <v>2.2837210076902432e-005</v>
       </c>
       <c r="E31">
-        <v>5.589360719044956e-006</v>
+        <v>-1.3026563646434655e-007</v>
       </c>
       <c r="F31">
-        <v>0.00043145831417775506</v>
+        <v>4.5176933080205687e-005</v>
       </c>
       <c r="G31">
-        <v>0.00094744247891125348</v>
+        <v>1.5078396633681066e-005</v>
       </c>
       <c r="H31">
-        <v>9.8812600891750463e-006</v>
+        <v>-4.9007674781459265e-007</v>
       </c>
       <c r="I31">
-        <v>1.7844018055202611e-005</v>
+        <v>1.3910729597229638e-007</v>
       </c>
       <c r="J31">
-        <v>0.00019538804627333164</v>
+        <v>-6.7645972862828024e-006</v>
       </c>
       <c r="K31">
-        <v>0.00028131380842008787</v>
+        <v>1.1182533078298723e-005</v>
       </c>
       <c r="L31">
-        <v>-0.00053246665431641148</v>
+        <v>-4.1269067807895286e-005</v>
       </c>
       <c r="M31">
-        <v>2.6264724935737082e-005</v>
+        <v>1.8514119337445652e-005</v>
       </c>
       <c r="N31">
-        <v>8.4230186007159136e-005</v>
+        <v>-4.3856560160834948e-005</v>
       </c>
       <c r="O31">
-        <v>0.00011297976707745757</v>
+        <v>-6.4192070363883582e-005</v>
       </c>
       <c r="P31">
-        <v>0.0010541385312058471</v>
+        <v>-0.00017809960616802981</v>
       </c>
       <c r="Q31">
-        <v>0.00036877255136581136</v>
+        <v>-0.00017842705781973516</v>
       </c>
       <c r="R31">
-        <v>0.0017304849141529272</v>
+        <v>-0.00013073894500762481</v>
       </c>
       <c r="S31">
-        <v>0.0015625812156786589</v>
+        <v>2.0587389307758961e-005</v>
       </c>
       <c r="T31">
-        <v>0.0013424356178338309</v>
+        <v>-1.9156243986151802e-005</v>
       </c>
       <c r="U31">
-        <v>0.0035967017150546417</v>
+        <v>6.1763610492837216e-006</v>
       </c>
       <c r="V31">
-        <v>0.00132496767768376</v>
+        <v>6.7605234115890615e-005</v>
       </c>
       <c r="W31">
-        <v>0.0015695317699623429</v>
+        <v>-8.1814080730243033e-005</v>
       </c>
       <c r="X31">
-        <v>0.0016500817270290373</v>
+        <v>0.00012783688745070763</v>
       </c>
       <c r="Y31">
-        <v>0.0017984884824380639</v>
+        <v>2.0033731522924378e-005</v>
       </c>
       <c r="Z31">
-        <v>0.0017234638599133499</v>
+        <v>1.9000062742784954e-005</v>
       </c>
       <c r="AA31">
-        <v>0.0017754293594784967</v>
+        <v>5.0811399663066746e-005</v>
       </c>
       <c r="AB31">
-        <v>0.0018614818692002618</v>
+        <v>1.1882195007055607e-005</v>
       </c>
       <c r="AC31">
-        <v>6.7322041614008602e-005</v>
+        <v>0.00014282755771426059</v>
       </c>
       <c r="AD31">
-        <v>-0.00028880434953428773</v>
+        <v>-2.7115089940532263e-005</v>
       </c>
       <c r="AE31">
-        <v>-0.00034102315632095301</v>
+        <v>-4.7864226631999715e-005</v>
       </c>
       <c r="AF31">
-        <v>0.01046408101320306</v>
+        <v>0.0020935115231285896</v>
       </c>
       <c r="AG31">
-        <v>0.00094799987243014976</v>
+        <v>0.00036035562474077498</v>
       </c>
       <c r="AH31">
-        <v>0.00012722348694307005</v>
+        <v>-0.0003289250101662553</v>
       </c>
       <c r="AI31">
-        <v>0.019656436259073561</v>
+        <v>6.4482656747824781e-005</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.00022079312222567332</v>
+      </c>
+      <c r="AK31">
+        <v>-0.00013084040521586327</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32">
-        <v>-0.51476234140409471</v>
+        <v>0.045910599123733915</v>
       </c>
       <c r="C32">
-        <v>-0.00010026604539497815</v>
+        <v>-2.7265291777788837e-005</v>
       </c>
       <c r="D32">
-        <v>-0.00027093957249027176</v>
+        <v>8.0655170984315471e-005</v>
       </c>
       <c r="E32">
-        <v>2.2034998496284772e-006</v>
+        <v>-5.8967962369185474e-007</v>
       </c>
       <c r="F32">
-        <v>0.00022910293064320244</v>
+        <v>1.5171779295661724e-005</v>
       </c>
       <c r="G32">
-        <v>0.00025333760111095015</v>
+        <v>-5.2653986414924316e-005</v>
       </c>
       <c r="H32">
-        <v>-2.0139276771387023e-006</v>
+        <v>-1.0194135377096504e-006</v>
       </c>
       <c r="I32">
-        <v>-2.0515068257652869e-006</v>
+        <v>-1.626799172442547e-007</v>
       </c>
       <c r="J32">
-        <v>1.4181185925644935e-005</v>
+        <v>-3.1980213818294872e-005</v>
       </c>
       <c r="K32">
-        <v>-9.1159538738705068e-005</v>
+        <v>9.2664659280258539e-005</v>
       </c>
       <c r="L32">
-        <v>-0.00010553471583823418</v>
+        <v>-4.542638416967583e-005</v>
       </c>
       <c r="M32">
-        <v>-3.0109652078284875e-005</v>
+        <v>-3.2029852000093111e-005</v>
       </c>
       <c r="N32">
-        <v>-6.5978869608990243e-005</v>
+        <v>-8.6046620779482732e-008</v>
       </c>
       <c r="O32">
-        <v>-9.0994551676016992e-005</v>
+        <v>4.0625830921731403e-005</v>
       </c>
       <c r="P32">
-        <v>5.5099331251598277e-005</v>
+        <v>-7.5715752952604267e-005</v>
       </c>
       <c r="Q32">
-        <v>0.00014556421072917406</v>
+        <v>-3.9876368257422124e-005</v>
       </c>
       <c r="R32">
-        <v>0.001353765284608194</v>
+        <v>-3.0022754991559524e-005</v>
       </c>
       <c r="S32">
-        <v>0.0012403488599521558</v>
+        <v>5.8612399539937512e-005</v>
       </c>
       <c r="T32">
-        <v>0.0012811466820745903</v>
+        <v>0.0001376457475656626</v>
       </c>
       <c r="U32">
-        <v>0.0013665818075972742</v>
+        <v>-2.601776545945139e-005</v>
       </c>
       <c r="V32">
-        <v>0.0010436267381622511</v>
+        <v>-3.364244881887894e-005</v>
       </c>
       <c r="W32">
-        <v>0.0013123891354770139</v>
+        <v>-0.00018108981637578528</v>
       </c>
       <c r="X32">
-        <v>0.0011955455656553382</v>
+        <v>0.00010932404209869229</v>
       </c>
       <c r="Y32">
-        <v>0.0013316997680248516</v>
+        <v>-2.9668392257857382e-005</v>
       </c>
       <c r="Z32">
-        <v>0.0013216588613496161</v>
+        <v>-3.472041142653758e-005</v>
       </c>
       <c r="AA32">
-        <v>0.0013430952599716929</v>
+        <v>-1.8269531918556358e-005</v>
       </c>
       <c r="AB32">
-        <v>0.0013491412295060104</v>
+        <v>-6.0013406593383104e-005</v>
       </c>
       <c r="AC32">
-        <v>-3.9436098309689823e-005</v>
+        <v>3.5639970895610492e-005</v>
       </c>
       <c r="AD32">
-        <v>8.6131334567909624e-005</v>
+        <v>2.6096834048657398e-006</v>
       </c>
       <c r="AE32">
-        <v>0.00010565641906156787</v>
+        <v>-6.0436197711771443e-005</v>
       </c>
       <c r="AF32">
-        <v>0.00094799987243014976</v>
+        <v>0.00036035562474077498</v>
       </c>
       <c r="AG32">
-        <v>0.014468800272516534</v>
+        <v>0.0023015827290327213</v>
       </c>
       <c r="AH32">
-        <v>-4.7301436572716834e-006</v>
+        <v>-0.00033582636053356622</v>
       </c>
       <c r="AI32">
-        <v>0.0076508009032758379</v>
+        <v>8.4352639747980931e-005</v>
+      </c>
+      <c r="AJ32">
+        <v>-0.00039593619588047368</v>
+      </c>
+      <c r="AK32">
+        <v>-0.0017173817088983489</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33">
-        <v>-0.086581076976814025</v>
+        <v>-0.10590208254224331</v>
       </c>
       <c r="C33">
-        <v>-6.8344389724043749e-005</v>
+        <v>-0.00016849243727414356</v>
       </c>
       <c r="D33">
-        <v>-4.8195586987582681e-005</v>
+        <v>-0.00083373485751388893</v>
       </c>
       <c r="E33">
-        <v>2.6661089844656218e-007</v>
+        <v>6.2912148195398807e-006</v>
       </c>
       <c r="F33">
-        <v>-7.7062222576483532e-005</v>
+        <v>0.00042789019717566653</v>
       </c>
       <c r="G33">
-        <v>-1.2690624718594606e-005</v>
+        <v>0.00092952403707881239</v>
       </c>
       <c r="H33">
-        <v>-3.8906844382527288e-006</v>
+        <v>1.8140153537579785e-005</v>
       </c>
       <c r="I33">
-        <v>2.7878766389719569e-006</v>
+        <v>2.2607428132705593e-005</v>
       </c>
       <c r="J33">
-        <v>-3.136951976794207e-006</v>
+        <v>0.00014749057540722308</v>
       </c>
       <c r="K33">
-        <v>0.00021094883279077978</v>
+        <v>0.00033231486574715995</v>
       </c>
       <c r="L33">
-        <v>-0.00041212219826475033</v>
+        <v>-0.00078044436726910828</v>
       </c>
       <c r="M33">
-        <v>0.00010664136150301574</v>
+        <v>-0.00043101120499286797</v>
       </c>
       <c r="N33">
-        <v>-0.00013058468868706939</v>
+        <v>0.00017930030439288462</v>
       </c>
       <c r="O33">
-        <v>-0.00015113606187354823</v>
+        <v>8.315910487289354e-005</v>
       </c>
       <c r="P33">
-        <v>-0.00021124588930835665</v>
+        <v>6.126086069432532e-005</v>
       </c>
       <c r="Q33">
-        <v>-0.00011434257502930382</v>
+        <v>0.00098969571091831235</v>
       </c>
       <c r="R33">
-        <v>-0.00019752710633223357</v>
+        <v>0.0002055424646331622</v>
       </c>
       <c r="S33">
-        <v>-0.00038030263126034164</v>
+        <v>0.00076673545360437124</v>
       </c>
       <c r="T33">
-        <v>-0.00038930831986717332</v>
+        <v>0.0017317893508796659</v>
       </c>
       <c r="U33">
-        <v>-0.000317491095778839</v>
+        <v>0.0015637610695035642</v>
       </c>
       <c r="V33">
-        <v>-0.00044167514466559216</v>
+        <v>0.0013617784303921938</v>
       </c>
       <c r="W33">
-        <v>-0.00038107275521368877</v>
+        <v>0.0037453478749548087</v>
       </c>
       <c r="X33">
-        <v>-0.00039342577640071529</v>
+        <v>0.0013124002318400771</v>
       </c>
       <c r="Y33">
-        <v>-0.00036703461929624642</v>
+        <v>0.0015588593586346616</v>
       </c>
       <c r="Z33">
-        <v>-0.00024344984040492812</v>
+        <v>0.0016544608131339599</v>
       </c>
       <c r="AA33">
-        <v>-0.0002625511460004656</v>
+        <v>0.0018054228395033864</v>
       </c>
       <c r="AB33">
-        <v>-0.00026284152041082775</v>
+        <v>0.0017294492904997038</v>
       </c>
       <c r="AC33">
-        <v>3.8234237904258088e-005</v>
+        <v>0.0017769958970957488</v>
       </c>
       <c r="AD33">
-        <v>-0.00020215497563099235</v>
+        <v>0.0018859250006422706</v>
       </c>
       <c r="AE33">
-        <v>-0.00036875761657775917</v>
+        <v>7.3052885747356203e-005</v>
       </c>
       <c r="AF33">
-        <v>0.00012722348694307005</v>
+        <v>-0.0003289250101662553</v>
       </c>
       <c r="AG33">
-        <v>-4.7301436572716834e-006</v>
+        <v>-0.00033582636053356622</v>
       </c>
       <c r="AH33">
-        <v>0.019072539594389804</v>
+        <v>0.010761279260889149</v>
       </c>
       <c r="AI33">
-        <v>0.0017861287970170037</v>
+        <v>0.00093661602946947637</v>
+      </c>
+      <c r="AJ33">
+        <v>0.00013163985147076859</v>
+      </c>
+      <c r="AK33">
+        <v>0.021662651637781787</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34">
+        <v>-0.496778825220408</v>
+      </c>
+      <c r="C34">
+        <v>-0.00011026528545187288</v>
+      </c>
+      <c r="D34">
+        <v>-0.00027024915224356863</v>
+      </c>
+      <c r="E34">
+        <v>2.2156793995731314e-006</v>
+      </c>
+      <c r="F34">
+        <v>0.00023798470834860607</v>
+      </c>
+      <c r="G34">
+        <v>0.00025544460762169348</v>
+      </c>
+      <c r="H34">
+        <v>-1.4376216278117864e-006</v>
+      </c>
+      <c r="I34">
+        <v>-2.2315121399743223e-006</v>
+      </c>
+      <c r="J34">
+        <v>-1.1640705395844862e-005</v>
+      </c>
+      <c r="K34">
+        <v>-7.7980453200177102e-005</v>
+      </c>
+      <c r="L34">
+        <v>-0.00014083739086847517</v>
+      </c>
+      <c r="M34">
+        <v>7.3520470893190639e-007</v>
+      </c>
+      <c r="N34">
+        <v>-2.8752949195567711e-005</v>
+      </c>
+      <c r="O34">
+        <v>-6.707838256518172e-005</v>
+      </c>
+      <c r="P34">
+        <v>-8.4708434244003348e-005</v>
+      </c>
+      <c r="Q34">
+        <v>6.2118339098118838e-005</v>
+      </c>
+      <c r="R34">
+        <v>0.00016045009566016373</v>
+      </c>
+      <c r="S34">
+        <v>6.2689569632612234e-005</v>
+      </c>
+      <c r="T34">
+        <v>0.0013329598505165885</v>
+      </c>
+      <c r="U34">
+        <v>0.0012143158811348496</v>
+      </c>
+      <c r="V34">
+        <v>0.0012686456158567975</v>
+      </c>
+      <c r="W34">
+        <v>0.0013508951173299068</v>
+      </c>
+      <c r="X34">
+        <v>0.001046505536183667</v>
+      </c>
+      <c r="Y34">
+        <v>0.001299774179940278</v>
+      </c>
+      <c r="Z34">
+        <v>0.0011585388197121213</v>
+      </c>
+      <c r="AA34">
+        <v>0.0013181614382234922</v>
+      </c>
+      <c r="AB34">
+        <v>0.0012974149043252421</v>
+      </c>
+      <c r="AC34">
+        <v>0.0013241254670822509</v>
+      </c>
+      <c r="AD34">
+        <v>0.0013376678045226909</v>
+      </c>
+      <c r="AE34">
+        <v>-3.8700543223929969e-005</v>
+      </c>
+      <c r="AF34">
+        <v>6.4482656747824781e-005</v>
+      </c>
+      <c r="AG34">
+        <v>8.4352639747980931e-005</v>
+      </c>
+      <c r="AH34">
+        <v>0.00093661602946947637</v>
+      </c>
+      <c r="AI34">
+        <v>0.014191463460206093</v>
+      </c>
+      <c r="AJ34">
+        <v>-7.0405906396886462e-005</v>
+      </c>
+      <c r="AK34">
+        <v>0.0075507556610548013</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35">
+        <v>-0.082511381363542233</v>
+      </c>
+      <c r="C35">
+        <v>-0.00010897269162518674</v>
+      </c>
+      <c r="D35">
+        <v>-5.6989290483304422e-005</v>
+      </c>
+      <c r="E35">
+        <v>3.6316603936619894e-007</v>
+      </c>
+      <c r="F35">
+        <v>-0.00010550372288871567</v>
+      </c>
+      <c r="G35">
+        <v>-4.6184744436537808e-005</v>
+      </c>
+      <c r="H35">
+        <v>-3.1762043045340701e-006</v>
+      </c>
+      <c r="I35">
+        <v>5.7675289488952577e-006</v>
+      </c>
+      <c r="J35">
+        <v>-6.1074970152520105e-005</v>
+      </c>
+      <c r="K35">
+        <v>0.00024653306091413328</v>
+      </c>
+      <c r="L35">
+        <v>-0.00054224554898046418</v>
+      </c>
+      <c r="M35">
+        <v>-0.00016500221787909191</v>
+      </c>
+      <c r="N35">
+        <v>0.00016789346649559702</v>
+      </c>
+      <c r="O35">
+        <v>-0.0001860429349241795</v>
+      </c>
+      <c r="P35">
+        <v>-0.00023942519875688371</v>
+      </c>
+      <c r="Q35">
+        <v>-0.00031926678645715354</v>
+      </c>
+      <c r="R35">
+        <v>-0.00022480670849015123</v>
+      </c>
+      <c r="S35">
+        <v>0.00024263108876943678</v>
+      </c>
+      <c r="T35">
+        <v>-0.00029392263015029865</v>
+      </c>
+      <c r="U35">
+        <v>-0.00047648176891071543</v>
+      </c>
+      <c r="V35">
+        <v>-0.00046013430799218152</v>
+      </c>
+      <c r="W35">
+        <v>-0.00041290270972204251</v>
+      </c>
+      <c r="X35">
+        <v>-0.00053204761849445109</v>
+      </c>
+      <c r="Y35">
+        <v>-0.00048572794048193455</v>
+      </c>
+      <c r="Z35">
+        <v>-0.00047697517679799717</v>
+      </c>
+      <c r="AA35">
+        <v>-0.00045673625071830214</v>
+      </c>
+      <c r="AB35">
+        <v>-0.00035238215635413178</v>
+      </c>
+      <c r="AC35">
+        <v>-0.0003476578675115947</v>
+      </c>
+      <c r="AD35">
+        <v>-0.0003716568843889573</v>
+      </c>
+      <c r="AE35">
+        <v>4.2802101195526583e-005</v>
+      </c>
+      <c r="AF35">
+        <v>-0.00022079312222567332</v>
+      </c>
+      <c r="AG35">
+        <v>-0.00039593619588047368</v>
+      </c>
+      <c r="AH35">
+        <v>0.00013163985147076859</v>
+      </c>
+      <c r="AI35">
+        <v>-7.0405906396886462e-005</v>
+      </c>
+      <c r="AJ35">
+        <v>0.019986789258916771</v>
+      </c>
+      <c r="AK35">
+        <v>0.0019880726238179752</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
         <v>47</v>
       </c>
-      <c r="B34">
-        <v>-28.752173152200839</v>
-      </c>
-      <c r="C34">
-        <v>-0.0026018159234982366</v>
-      </c>
-      <c r="D34">
-        <v>-0.047356369255036612</v>
-      </c>
-      <c r="E34">
-        <v>0.00038024744874663393</v>
-      </c>
-      <c r="F34">
-        <v>0.0025595776641213382</v>
-      </c>
-      <c r="G34">
-        <v>0.0068555571938108597</v>
-      </c>
-      <c r="H34">
-        <v>-0.00016045622788399711</v>
-      </c>
-      <c r="I34">
-        <v>-0.00012066156077618898</v>
-      </c>
-      <c r="J34">
-        <v>-0.0031361455917476035</v>
-      </c>
-      <c r="K34">
-        <v>-0.012405799874938707</v>
-      </c>
-      <c r="L34">
-        <v>-0.0056018039096679215</v>
-      </c>
-      <c r="M34">
-        <v>-9.0842652349912745e-005</v>
-      </c>
-      <c r="N34">
-        <v>-0.0062329811192573152</v>
-      </c>
-      <c r="O34">
-        <v>-0.0044920274218082732</v>
-      </c>
-      <c r="P34">
-        <v>-0.00059193638340618738</v>
-      </c>
-      <c r="Q34">
-        <v>-0.0024342805204184779</v>
-      </c>
-      <c r="R34">
-        <v>0.0014380997370608221</v>
-      </c>
-      <c r="S34">
-        <v>0.001378502729192049</v>
-      </c>
-      <c r="T34">
-        <v>0.0015102532530236728</v>
-      </c>
-      <c r="U34">
-        <v>0.0085298484397225913</v>
-      </c>
-      <c r="V34">
-        <v>0.0029348913460538529</v>
-      </c>
-      <c r="W34">
-        <v>0.0045939672281012939</v>
-      </c>
-      <c r="X34">
-        <v>0.0032889782916181946</v>
-      </c>
-      <c r="Y34">
-        <v>0.0040464432672078715</v>
-      </c>
-      <c r="Z34">
-        <v>0.0030356536200061798</v>
-      </c>
-      <c r="AA34">
-        <v>0.003519833556493282</v>
-      </c>
-      <c r="AB34">
-        <v>0.0022232719655524095</v>
-      </c>
-      <c r="AC34">
-        <v>-0.00018760574252675566</v>
-      </c>
-      <c r="AD34">
-        <v>-8.1694966534162487e-005</v>
-      </c>
-      <c r="AE34">
-        <v>-0.0017994038506445064</v>
-      </c>
-      <c r="AF34">
-        <v>0.019656436259073561</v>
-      </c>
-      <c r="AG34">
-        <v>0.0076508009032758379</v>
-      </c>
-      <c r="AH34">
-        <v>0.0017861287970170037</v>
-      </c>
-      <c r="AI34">
-        <v>1.4811858175039099</v>
+      <c r="B36">
+        <v>-28.895243439225112</v>
+      </c>
+      <c r="C36">
+        <v>-0.0029490861002779076</v>
+      </c>
+      <c r="D36">
+        <v>-0.047990293762680519</v>
+      </c>
+      <c r="E36">
+        <v>0.00038546273381666102</v>
+      </c>
+      <c r="F36">
+        <v>0.0023108054479232692</v>
+      </c>
+      <c r="G36">
+        <v>0.0067893510814081952</v>
+      </c>
+      <c r="H36">
+        <v>-0.00010677581451937798</v>
+      </c>
+      <c r="I36">
+        <v>-9.5657141478404373e-005</v>
+      </c>
+      <c r="J36">
+        <v>-0.0032316150663422136</v>
+      </c>
+      <c r="K36">
+        <v>-0.011995536506347854</v>
+      </c>
+      <c r="L36">
+        <v>-0.0071665992587352234</v>
+      </c>
+      <c r="M36">
+        <v>-0.00074034499519242173</v>
+      </c>
+      <c r="N36">
+        <v>0.00014817325938999519</v>
+      </c>
+      <c r="O36">
+        <v>-0.0059383850126287184</v>
+      </c>
+      <c r="P36">
+        <v>-0.0041149042660478001</v>
+      </c>
+      <c r="Q36">
+        <v>-0.00015958110675594762</v>
+      </c>
+      <c r="R36">
+        <v>-0.0022204445184796136</v>
+      </c>
+      <c r="S36">
+        <v>0.004841919194682201</v>
+      </c>
+      <c r="T36">
+        <v>0.0017674576858222818</v>
+      </c>
+      <c r="U36">
+        <v>0.0014682143272505693</v>
+      </c>
+      <c r="V36">
+        <v>0.0014925912019428181</v>
+      </c>
+      <c r="W36">
+        <v>0.0092081598150843234</v>
+      </c>
+      <c r="X36">
+        <v>0.0032862067796679086</v>
+      </c>
+      <c r="Y36">
+        <v>0.0047835545734878759</v>
+      </c>
+      <c r="Z36">
+        <v>0.0034180959073727476</v>
+      </c>
+      <c r="AA36">
+        <v>0.0038667377617547594</v>
+      </c>
+      <c r="AB36">
+        <v>0.0029465628022475971</v>
+      </c>
+      <c r="AC36">
+        <v>0.0036431947301365985</v>
+      </c>
+      <c r="AD36">
+        <v>0.0023303695638439061</v>
+      </c>
+      <c r="AE36">
+        <v>-0.00016270687900734845</v>
+      </c>
+      <c r="AF36">
+        <v>-0.00013084040521586327</v>
+      </c>
+      <c r="AG36">
+        <v>-0.0017173817088983489</v>
+      </c>
+      <c r="AH36">
+        <v>0.021662651637781787</v>
+      </c>
+      <c r="AI36">
+        <v>0.0075507556610548013</v>
+      </c>
+      <c r="AJ36">
+        <v>0.0019880726238179752</v>
+      </c>
+      <c r="AK36">
+        <v>1.4959338815265046</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_retirement.xlsx
+++ b/input/reg_retirement.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="57">
   <si>
     <t>Description:</t>
   </si>
@@ -193,7 +193,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -261,6 +261,76 @@
       <name val="Calibri"/>
       <b/>
     </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -270,7 +340,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -327,11 +397,60 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -361,6 +480,34 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -374,7 +521,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -395,10 +542,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="10" t="s">
         <v>0</v>
       </c>
     </row>
@@ -419,7 +566,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
@@ -441,12 +588,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
     </row>
@@ -479,7 +626,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>56</v>
       </c>
     </row>
